--- a/needs_location_verification.xlsx
+++ b/needs_location_verification.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI59"/>
+  <dimension ref="A1:BI56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8003,115 +8003,113 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>pin is ~1845 m estimated walk (1398 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRT️⚜️</t>
+          <t>pin is ~1850 m estimated walk (1401 m straight-line) from nearest target station; text mentions an unnamed metro: ایستگاه اتوبوس</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ga7-Iqt2</t>
+          <t>gah7cUQZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://divar.ir/v/ga7-Iqt2</t>
+          <t>https://divar.ir/v/gah7cUQZ</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>آپارتمان52متری/Pموتور/انباری/شیک و تمیز/جیحون</t>
+          <t>اجاره آپارتمان مسکونی.میدان بهاران.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>جیحون</t>
+          <t>سجاد</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>خ انصاری</t>
+          <t>خ پیک مردی</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>جیحون</t>
+          <t>سجاد</t>
         </is>
       </c>
       <c r="I33" t="b">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>500000000</v>
+        <v>350000000</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>15000000</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N33" t="n">
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>1390</v>
+        <v>1396</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2 از 4</t>
+          <t>2 از 5</t>
         </is>
       </c>
       <c r="Q33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>premium-panel</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>۷ مهر ۱۴۰۵، ۱۳:۵۰</t>
+          <t>۶ آبان ۱۴۰۵، ۱۳:۵۸</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="n">
-        <v>35.68184043442734</v>
+        <v>35.651067308615</v>
       </c>
       <c r="Y33" t="n">
-        <v>51.36460171655599</v>
+        <v>51.355485410454</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>FUZZY</t>
+          <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>APPROXIMATE</t>
+          <t>VALID</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>api_approximate</t>
-        </is>
-      </c>
-      <c r="AC33" t="n">
-        <v>500</v>
-      </c>
+          <t>api_exact_pin</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
+          <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
@@ -8119,10 +8117,10 @@
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>1845</v>
+        <v>1850</v>
       </c>
       <c r="AJ33" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
@@ -8132,11 +8130,11 @@
       <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>osm_n5190423570</t>
+          <t>osm_n14084275565</t>
         </is>
       </c>
       <c r="AN33" t="n">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -8151,33 +8149,33 @@
       <c r="AQ33" t="inlineStr"/>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>مترو و BRT️⚜️</t>
+          <t>ایستگاه اتوبوس</t>
         </is>
       </c>
       <c r="AS33" t="n">
-        <v>500000000</v>
+        <v>350000000</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>15000000</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
+          <t>‏۳۵۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>رایگان</t>
+          <t>‏۱۵,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
+          <t>ودیعه: ۳۵۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>رهن کامل</t>
+          <t>اجاره: ۱۵,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -8193,504 +8191,16 @@
       <c r="BE33" t="inlineStr"/>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>2026-10-30T13:50:19.909669</t>
+          <t>2026-11-28T13:58:38.633616</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr"/>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>{"osm_n5190423570": 1398, "osm_n5165422504": 1499, "beryanak": 1759, "osm_n5165422503": 1938, "osm_n5183625750": 2065, "osm_n14065977511": 2194, "osm_n14058146709": 2365, "osm_w671794339": 2482, "helal_ahmar": 2566, "osm_w1314615868": 2726, "osm_n14058145512": 2820, "osm_n14075053790": 2948, "osm_n14058145514": 3175, "osm_n11417054143": 3187, "osm_w1041344025": 3258, "osm_n5162910431": 3308, "moniriyeh": 3345, "osm_n14084275564": 3353, "osm_n5186234550": 3502, "mahdieh": 3539, "osm_n11417054161": 3783, "osm_n3635251445": 3889, "osm_w1169531671": 4056, "osm_n14058145515": 4144, "osm_n14084275565": 4197, "osm_n14058145513": 4253, "teatr_shahr": 4260, "osm_n5183520307": 4303, "osm_n10746895093": 4317, "osm_n4396461099": 4777, "osm_n5162855447": 4797, "osm_n14089610125": 4851, "osm_n6737096941": 4889, "osm_n5604727197": 5015, "osm_n5190423568": 5020, "vali_asr": 5058, "osm_n5186262276": 5093, "osm_n13380425834": 5242, "osm_n13202066659": 5389, "saadi": 5553, "osm_n14072135584": 5570, "osm_n5165462147": 5571, "osm_n14058409025": 5659, "osm_n13230313218": 5776, "osm_n13380425818": 5800, "osm_n14075284474": 5816, "osm_n13279314257": 5832, "jahad": 5849, "osm_n8890549263": 5865, "darvazeh_dowlat": 5965, "osm_n14071125007": 5968, "osm_n14072135585": 6120, "taleghani": 6178, "osm_n14058409026": 6301, "osm_n13380425728": 6435, "osm_n5165462148": 6597, "osm_n14059862414": 6634, "haft_tir": 6700, "osm_n14072135586": 6766, "osm_n5188341403": 6835, "osm_n5602579936": 6906, "mirza_shirazi": 6996, "osm_n14065945232": 7330, "osm_n12157511978": 7392, "mofatteh": 7415, "osm_n5183513583": 7417, "osm_n8243426038": 7431, "osm_n13284688255": 7482, "osm_n10861347776": 7531, "osm_n6390530109": 7536, "osm_n12659430599": 7543, "osm_n13426743990": 7681, "osm_n14060820580": 7699, "osm_n14071125009": 7764, "shahid_beheshti": 7825, "osm_n9149513248": 7962, "osm_n14075284475": 8075, "osm_n6444462277": 8315, "osm_n2169732971": 8382, "sohrevardi": 8518, "osm_n14058409027": 8532, "osm_n13381123730": 8644, "osm_n14064336782": 8779, "osm_n14059828792": 8973, "osm_n3778821747": 9095, "osm_n660658572": 9306, "osm_n8273593826": 9333, "osm_n14075125227": 9381, "osm_n13380418873": 9397, "osm_n14075284476": 9483, "osm_n14072135587": 9494, "osm_n14075125225": 9817, "osm_n14058409028": 9886, "osm_n13381123745": 10006, "osm_n5162910430": 10240, "osm_n14072135588": 10362, "osm_n14064708968": 10622, "osm_n14075284477": 10644, "osm_n13381123758": 10703, "osm_n8907277818": 10980, "osm_n3778861787": 11156, "osm_n14058409029": 11195, "osm_n5162910441": 11221, "osm_n6390530105": 11402, "osm_n11750922029": 11457, "osm_n13381123759": 11531, "osm_n5604726917": 11581, "osm_n14064708967": 11615, "osm_n2169380700": 12087, "osm_n14058409030": 12212, "osm_n5162910442": 12351, "osm_n13230283736": 12530, "osm_n14072135590": 12661, "osm_n13381123770": 13168, "osm_n14058409031": 13195, "osm_n13817588094": 13331, "osm_n11281445852": 13914, "osm_n13381264373": 13942, "osm_n14058409032": 13960, "osm_n3778822187": 14027, "osm_n5163103599": 14871, "osm_n14072135591": 14922, "osm_n13381264374": 15015, "osm_n5162855462": 15044, "osm_n5194776019": 15225, "osm_n14061094940": 15903, "osm_n5163103601": 16055, "osm_n8738914819": 17079, "osm_n5163103600": 17316, "osm_n5163103597": 18280, "osm_n5163103598": 19186}</t>
+          <t>{"osm_n14084275565": 1401, "osm_n14089610125": 1467, "osm_n14084275564": 1644, "osm_n5165462147": 2063, "osm_w1041344025": 3064, "osm_n5165462148": 3194, "beryanak": 3351, "helal_ahmar": 3408, "osm_n3635251445": 3930, "osm_n5190423570": 4033, "mahdieh": 4350, "osm_n5165422504": 4621, "osm_n11417054143": 4792, "osm_n5165422503": 5311, "osm_n14058146709": 5324, "moniriyeh": 5344, "osm_n13380425834": 5355, "osm_n11417054161": 5426, "osm_n14065977511": 5475, "osm_n13380425728": 5479, "osm_n13380425818": 5494, "osm_n5183625750": 5551, "osm_w1314615868": 5555, "osm_n14058145514": 5644, "osm_n6737096941": 5760, "osm_n5186234550": 5803, "osm_w671794339": 5939, "osm_n5183513583": 5941, "osm_n5162855447": 6046, "osm_n14058145512": 6081, "osm_n5183520307": 6168, "osm_n14058145515": 6294, "osm_n4396461099": 6353, "osm_n14075053790": 6443, "osm_n5162910431": 6495, "osm_n14071125007": 6927, "osm_n5186262276": 7054, "teatr_shahr": 7167, "osm_n14058145513": 7307, "osm_w1169531671": 7333, "osm_n13380418873": 7365, "osm_n13230313218": 7438, "osm_n14059862414": 7607, "osm_n14058409025": 7657, "osm_n10746895093": 7742, "osm_n5604727197": 7744, "saadi": 7803, "osm_n13202066659": 8033, "osm_n9149513248": 8053, "osm_n6444462277": 8081, "vali_asr": 8179, "osm_n12659430599": 8297, "osm_n14058409026": 8384, "osm_n13284688255": 8384, "darvazeh_dowlat": 8493, "osm_n5190423568": 8534, "osm_n8273593826": 8654, "osm_n8907277818": 8685, "osm_n5602579936": 8830, "taleghani": 8881, "osm_n13279314257": 8899, "osm_n8243426038": 8967, "osm_n14072135584": 9068, "jahad": 9088, "osm_n5188341403": 9110, "osm_n8890549263": 9276, "osm_n14075284474": 9333, "osm_n14072135585": 9347, "osm_n6390530109": 9370, "haft_tir": 9597, "osm_n14072135586": 9726, "osm_n14059828792": 9848, "osm_n10861347776": 9897, "osm_n13426743990": 9957, "osm_n14065945232": 10069, "osm_n2169732971": 10147, "osm_n14060820580": 10201, "mirza_shirazi": 10213, "mofatteh": 10449, "osm_n6390530105": 10454, "osm_n14071125009": 10470, "osm_n14075125225": 10734, "osm_n11281445852": 10882, "osm_n12157511978": 10906, "osm_n14058409027": 10911, "shahid_beheshti": 10956, "osm_n14075125227": 11080, "osm_n14064336782": 11197, "sohrevardi": 11543, "osm_n14075284475": 11546, "osm_n5162855462": 11793, "osm_n14072135587": 11864, "osm_n13381123730": 11875, "osm_n5194776019": 11890, "osm_n5162910430": 11895, "osm_n3778821747": 12030, "osm_n11750922029": 12276, "osm_n14058409028": 12360, "osm_n5604726917": 12462, "osm_n660658572": 12617, "osm_n5162910441": 12847, "osm_n14075284476": 12942, "osm_n14064708968": 12987, "osm_n14072135588": 13214, "osm_n13381123745": 13365, "osm_n14058409029": 13723, "osm_n13381123758": 14025, "osm_n14075284477": 14036, "osm_n14064708967": 14044, "osm_n5162910442": 14066, "osm_n3778861787": 14081, "osm_n13817588094": 14099, "osm_n14058409030": 14781, "osm_n13381123759": 14797, "osm_n13230283736": 14974, "osm_n2169380700": 15445, "osm_n14058409031": 15714, "osm_n14072135590": 15739, "osm_n14058409032": 16378, "osm_n13381123770": 16583, "osm_n3778822187": 17146, "osm_n5163103599": 17178, "osm_n13381264373": 17383, "osm_n14072135591": 18054, "osm_n5163103601": 18232, "osm_n13381264374": 18482, "osm_n14061094940": 19103, "osm_n5163103600": 19390, "osm_n8738914819": 20306, "osm_n5163103597": 21359, "osm_n5163103598": 22200}</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
-        <is>
-          <t>⚜️مشاورین املاک کندو⚜️
-         ⚜️️آپارتمان52 خوش نقشه تخلیه⚜️
-         ⚜️ ️دسترسی بی نظیر به مترو و BRT️⚜️
-    ⚜️ملک به شدت خوش نقشه و قابل چیدمان⚜️
-‼️زیر قیمت منطقه ‼️
-‼️بی نظیر در این منطقه‼️
-‼️سریعا تماس بگیرید‼️
-ـ
-دسترسی عالی به مراکز خرید و فضای سبز⚡
-دسترسی بی نظیر به اتوبان یادگار امام و نواب⚡
-⭕️فوری!!!⭕️
-عکس ها متعلق به واحد میباشد⚜️
-فول امکانات و اوکازیون ⚜️
-کابینت MDF TORK⚜️
-گازرومیزی⚜️
-هودلمسی⚜️
-پارکینگ موتور⚜️
-انباری ⚜️
-بالکن ⚜️
-درب ضد سرقت⚜️
-دوواحدی⚜️
-سرویس ایرانی فرنگی⚜️
-نورگیری فوق العاده⚜️
-کمد دیواری بزرگ⚜️
-سرمایش کولر آبی⚜️
-گرمایش شوفاژ و پکیج⚜️
-کف سرامیک⚜️
-تماس بگیرید⚜️
-آدرس املاک:خیابان رودکی،سلسبیل جنوبی،پایین ترازمرتضوی پلاک ۸۷
-دپارتمان بزرگ کندو
-مشاور تخصصی منطقه:احمدی</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>NEEDS_LOCATION_VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>pin is ~1847 m estimated walk (1399 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRT️⚜️</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>ga7qI_my</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://divar.ir/v/ga7qI_my</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>60متری/تک واحدی/آسانسور/پارکینگ موتور/جیحون</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>جیحون</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>خ باقرزاده</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>جیحون</t>
-        </is>
-      </c>
-      <c r="I34" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>350000000</v>
-      </c>
-      <c r="K34" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="L34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>60</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1400</v>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2 از 4</t>
-        </is>
-      </c>
-      <c r="Q34" t="b">
-        <v>1</v>
-      </c>
-      <c r="R34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S34" t="b">
-        <v>1</v>
-      </c>
-      <c r="T34" t="n">
-        <v>7</v>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>premium-panel</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>۷ مهر ۱۴۰۵، ۱۴:۳۶</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="n">
-        <v>35.68218738671275</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>51.36461284734688</v>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>FUZZY</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>APPROXIMATE</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>api_approximate</t>
-        </is>
-      </c>
-      <c r="AC34" t="n">
-        <v>500</v>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="n">
-        <v>1847</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Excluded (&gt;1500 m)</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>osm_n5190423570</t>
-        </is>
-      </c>
-      <c r="AN34" t="n">
-        <v>1399</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Secondary</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>not routed (estimate only)</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>مترو و BRT️⚜️</t>
-        </is>
-      </c>
-      <c r="AS34" t="n">
-        <v>350000000</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>RENT_SLIDER credit.value=350000000</t>
-        </is>
-      </c>
-      <c r="AV34" t="inlineStr">
-        <is>
-          <t>RENT_SLIDER rent.value=9000000</t>
-        </is>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>ودیعه: ۳۵۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>اجاره: ۹,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>credit 400000000 / rent 7500000</t>
-        </is>
-      </c>
-      <c r="AZ34" t="inlineStr"/>
-      <c r="BA34" t="inlineStr"/>
-      <c r="BB34" t="inlineStr"/>
-      <c r="BC34" t="inlineStr"/>
-      <c r="BD34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="BE34" t="inlineStr"/>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>2026-10-30T14:36:06.699326</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr"/>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>{"osm_n5190423570": 1399, "osm_n5165422504": 1482, "beryanak": 1780, "osm_n5165422503": 1909, "osm_n5183625750": 2027, "osm_n14065977511": 2158, "osm_n14058146709": 2348, "osm_w671794339": 2448, "helal_ahmar": 2589, "osm_w1314615868": 2698, "osm_n14058145512": 2784, "osm_n14075053790": 2912, "osm_n14058145514": 3167, "osm_n11417054143": 3179, "osm_n5162910431": 3282, "osm_w1041344025": 3287, "moniriyeh": 3345, "osm_n14084275564": 3390, "osm_n5186234550": 3481, "mahdieh": 3556, "osm_n11417054161": 3771, "osm_n3635251445": 3913, "osm_w1169531671": 4027, "osm_n14058145515": 4139, "osm_n14058145513": 4219, "osm_n14084275565": 4235, "teatr_shahr": 4240, "osm_n10746895093": 4284, "osm_n5183520307": 4287, "osm_n4396461099": 4779, "osm_n5162855447": 4804, "osm_n14089610125": 4890, "osm_n6737096941": 4901, "osm_n5190423568": 4982, "osm_n5604727197": 4985, "vali_asr": 5032, "osm_n5186262276": 5088, "osm_n13380425834": 5261, "osm_n13202066659": 5372, "osm_n14072135584": 5531, "saadi": 5543, "osm_n5165462147": 5608, "osm_n14058409025": 5654, "osm_n13230313218": 5760, "osm_n14075284474": 5779, "osm_n13279314257": 5806, "jahad": 5820, "osm_n13380425818": 5822, "osm_n8890549263": 5827, "darvazeh_dowlat": 5950, "osm_n14071125007": 5976, "osm_n14072135585": 6083, "taleghani": 6160, "osm_n14058409026": 6293, "osm_n13380425728": 6461, "osm_n5165462148": 6632, "osm_n14059862414": 6641, "haft_tir": 6678, "osm_n14072135586": 6732, "osm_n5188341403": 6824, "osm_n5602579936": 6884, "mirza_shirazi": 6967, "osm_n14065945232": 7299, "osm_n12157511978": 7354, "mofatteh": 7389, "osm_n8243426038": 7429, "osm_n5183513583": 7447, "osm_n13284688255": 7488, "osm_n10861347776": 7504, "osm_n6390530109": 7530, "osm_n12659430599": 7551, "osm_n13426743990": 7669, "osm_n14060820580": 7683, "osm_n14071125009": 7744, "shahid_beheshti": 7798, "osm_n9149513248": 7977, "osm_n14075284475": 8037, "osm_n6444462277": 8334, "osm_n2169732971": 8376, "sohrevardi": 8492, "osm_n14058409027": 8517, "osm_n13381123730": 8615, "osm_n14064336782": 8750, "osm_n14059828792": 8978, "osm_n3778821747": 9071, "osm_n660658572": 9275, "osm_n8273593826": 9354, "osm_n14075125227": 9376, "osm_n13380418873": 9429, "osm_n14075284476": 9444, "osm_n14072135587": 9466, "osm_n14075125225": 9822, "osm_n14058409028": 9869, "osm_n13381123745": 9973, "osm_n5162910430": 10235, "osm_n14072135588": 10339, "osm_n14064708968": 10594, "osm_n14075284477": 10605, "osm_n13381123758": 10671, "osm_n8907277818": 11013, "osm_n3778861787": 11132, "osm_n14058409029": 11177, "osm_n5162910441": 11216, "osm_n6390530105": 11425, "osm_n11750922029": 11462, "osm_n13381123759": 11500, "osm_n5604726917": 11569, "osm_n14064708967": 11585, "osm_n2169380700": 12054, "osm_n14058409030": 12193, "osm_n5162910442": 12344, "osm_n13230283736": 12501, "osm_n14072135590": 12634, "osm_n13381123770": 13134, "osm_n14058409031": 13177, "osm_n13817588094": 13336, "osm_n13381264373": 13907, "osm_n14058409032": 13943, "osm_n11281445852": 13952, "osm_n3778822187": 13999, "osm_n5163103599": 14856, "osm_n14072135591": 14894, "osm_n13381264374": 14979, "osm_n5162855462": 15082, "osm_n5194776019": 15264, "osm_n14061094940": 15873, "osm_n5163103601": 16041, "osm_n8738914819": 17048, "osm_n5163103600": 17303, "osm_n5163103597": 18252, "osm_n5163103598": 19159}</t>
-        </is>
-      </c>
-      <c r="BI34" t="inlineStr">
-        <is>
-          <t>⚜️مشاورین کندو⚜️
-     ⚜️️آپارتمان 60 متر خوش نقشه تخلیه️⚜️
-      ⚜️ ️دسترسی بی نظیر به مترو و BRT️⚜️
-    ⚜️ملک به شدت خوش نقشه و قابل چیدمان⚜️
-‼️زیر قیمت منطقه ‼️
-‼️بی نظیر در این منطقه‼️
-‼️سریعا تماس بگیرید‼️
-ـ
-دسترسی عالی به مراکز خرید و فضای سبز⚡
-دسترسی بی نظیر به اتوبان یادگار امام و نواب⚡
-⭕️فوری!!!⭕️
-عکس ها متعلق به واحد میباشد⚜️
-فول امکانات و اوکازیون ⚜️
-کابینت MDF TORK⚜️
-گازرومیزی⚜️
-هودلمسی⚜️
-آسانسور⚜️
-پارکینگ موتور⚜️
-انباری⚜
-بالکن⚜️
-درب ضد سرقت⚜️
-تک واحدی⚜️
-سرویس ایرانی فرنگی⚜️
-نورگیری فوق العاده⚜️
-کمد دیواری بزرگ⚜️
-سرمایش کولرآبی⚜️
-گرمایش شوفاژ و پکیج⚜️
-کف سرامیک⚜️
-تماس بگیرید⚜️
-آدرس دفتر: خیابان رودکی بالاتراز کمیل نرسیده به مرتضوی دپارتمان کندو پلاک ۸۷
-مشاور تخصصی منطقه: امیرتابان</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>NEEDS_LOCATION_VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>pin is ~1850 m estimated walk (1401 m straight-line) from nearest target station; text mentions an unnamed metro: ایستگاه اتوبوس</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>gah7cUQZ</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://divar.ir/v/gah7cUQZ</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>اجاره آپارتمان مسکونی.میدان بهاران.</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>سجاد</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>خ پیک مردی</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>سجاد</t>
-        </is>
-      </c>
-      <c r="I35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>350000000</v>
-      </c>
-      <c r="K35" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="L35" t="b">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>54</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1396</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>2 از 5</t>
-        </is>
-      </c>
-      <c r="Q35" t="b">
-        <v>1</v>
-      </c>
-      <c r="R35" t="b">
-        <v>0</v>
-      </c>
-      <c r="S35" t="b">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>personal</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>۶ آبان ۱۴۰۵، ۱۳:۵۸</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="n">
-        <v>35.651067308615</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>51.355485410454</v>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>EXACT_DATA_UNTYPED</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>api_exact_pin</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>sections[6].widgets[0].data.location.exact_data.point</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="n">
-        <v>1850</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Excluded (&gt;1500 m)</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>osm_n14084275565</t>
-        </is>
-      </c>
-      <c r="AN35" t="n">
-        <v>1401</v>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Secondary</t>
-        </is>
-      </c>
-      <c r="AP35" t="inlineStr">
-        <is>
-          <t>not routed (estimate only)</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr"/>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>ایستگاه اتوبوس</t>
-        </is>
-      </c>
-      <c r="AS35" t="n">
-        <v>350000000</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>‏۳۵۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AV35" t="inlineStr">
-        <is>
-          <t>‏۱۵,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>ودیعه: ۳۵۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>اجاره: ۱۵,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr"/>
-      <c r="BA35" t="inlineStr"/>
-      <c r="BB35" t="inlineStr"/>
-      <c r="BC35" t="inlineStr"/>
-      <c r="BD35" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="BE35" t="inlineStr"/>
-      <c r="BF35" t="inlineStr">
-        <is>
-          <t>2026-11-28T13:58:38.633616</t>
-        </is>
-      </c>
-      <c r="BG35" t="inlineStr"/>
-      <c r="BH35" t="inlineStr">
-        <is>
-          <t>{"osm_n14084275565": 1401, "osm_n14089610125": 1467, "osm_n14084275564": 1644, "osm_n5165462147": 2063, "osm_w1041344025": 3064, "osm_n5165462148": 3194, "beryanak": 3351, "helal_ahmar": 3408, "osm_n3635251445": 3930, "osm_n5190423570": 4033, "mahdieh": 4350, "osm_n5165422504": 4621, "osm_n11417054143": 4792, "osm_n5165422503": 5311, "osm_n14058146709": 5324, "moniriyeh": 5344, "osm_n13380425834": 5355, "osm_n11417054161": 5426, "osm_n14065977511": 5475, "osm_n13380425728": 5479, "osm_n13380425818": 5494, "osm_n5183625750": 5551, "osm_w1314615868": 5555, "osm_n14058145514": 5644, "osm_n6737096941": 5760, "osm_n5186234550": 5803, "osm_w671794339": 5939, "osm_n5183513583": 5941, "osm_n5162855447": 6046, "osm_n14058145512": 6081, "osm_n5183520307": 6168, "osm_n14058145515": 6294, "osm_n4396461099": 6353, "osm_n14075053790": 6443, "osm_n5162910431": 6495, "osm_n14071125007": 6927, "osm_n5186262276": 7054, "teatr_shahr": 7167, "osm_n14058145513": 7307, "osm_w1169531671": 7333, "osm_n13380418873": 7365, "osm_n13230313218": 7438, "osm_n14059862414": 7607, "osm_n14058409025": 7657, "osm_n10746895093": 7742, "osm_n5604727197": 7744, "saadi": 7803, "osm_n13202066659": 8033, "osm_n9149513248": 8053, "osm_n6444462277": 8081, "vali_asr": 8179, "osm_n12659430599": 8297, "osm_n14058409026": 8384, "osm_n13284688255": 8384, "darvazeh_dowlat": 8493, "osm_n5190423568": 8534, "osm_n8273593826": 8654, "osm_n8907277818": 8685, "osm_n5602579936": 8830, "taleghani": 8881, "osm_n13279314257": 8899, "osm_n8243426038": 8967, "osm_n14072135584": 9068, "jahad": 9088, "osm_n5188341403": 9110, "osm_n8890549263": 9276, "osm_n14075284474": 9333, "osm_n14072135585": 9347, "osm_n6390530109": 9370, "haft_tir": 9597, "osm_n14072135586": 9726, "osm_n14059828792": 9848, "osm_n10861347776": 9897, "osm_n13426743990": 9957, "osm_n14065945232": 10069, "osm_n2169732971": 10147, "osm_n14060820580": 10201, "mirza_shirazi": 10213, "mofatteh": 10449, "osm_n6390530105": 10454, "osm_n14071125009": 10470, "osm_n14075125225": 10734, "osm_n11281445852": 10882, "osm_n12157511978": 10906, "osm_n14058409027": 10911, "shahid_beheshti": 10956, "osm_n14075125227": 11080, "osm_n14064336782": 11197, "sohrevardi": 11543, "osm_n14075284475": 11546, "osm_n5162855462": 11793, "osm_n14072135587": 11864, "osm_n13381123730": 11875, "osm_n5194776019": 11890, "osm_n5162910430": 11895, "osm_n3778821747": 12030, "osm_n11750922029": 12276, "osm_n14058409028": 12360, "osm_n5604726917": 12462, "osm_n660658572": 12617, "osm_n5162910441": 12847, "osm_n14075284476": 12942, "osm_n14064708968": 12987, "osm_n14072135588": 13214, "osm_n13381123745": 13365, "osm_n14058409029": 13723, "osm_n13381123758": 14025, "osm_n14075284477": 14036, "osm_n14064708967": 14044, "osm_n5162910442": 14066, "osm_n3778861787": 14081, "osm_n13817588094": 14099, "osm_n14058409030": 14781, "osm_n13381123759": 14797, "osm_n13230283736": 14974, "osm_n2169380700": 15445, "osm_n14058409031": 15714, "osm_n14072135590": 15739, "osm_n14058409032": 16378, "osm_n13381123770": 16583, "osm_n3778822187": 17146, "osm_n5163103599": 17178, "osm_n13381264373": 17383, "osm_n14072135591": 18054, "osm_n5163103601": 18232, "osm_n13381264374": 18482, "osm_n14061094940": 19103, "osm_n5163103600": 19390, "osm_n8738914819": 20306, "osm_n5163103597": 21359, "osm_n5163103598": 22200}</t>
-        </is>
-      </c>
-      <c r="BI35" t="inlineStr">
         <is>
           <t>آپارتمان 54 متری یک خوابه | رهن و اجاره
 ✨ یک واحد آپارتمان 54 متری، یک خوابه .با دسترسی مناسب به امکانات شهری
@@ -8711,218 +8221,218 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>pin is ~1851 m estimated walk (1402 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRT️⚜️</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>gaTvxbnm</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaTvxbnm</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>آپارتمان65متر/2خوابه/همکف/پارکینگ‌موتور/جیحون</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>جیحون</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>خ باقرزاده</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>جیحون</t>
         </is>
       </c>
-      <c r="I36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
         <v>500000000</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K34" t="n">
         <v>5000000</v>
       </c>
-      <c r="L36" t="b">
-        <v>1</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
         <v>65</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N34" t="n">
         <v>2</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O34" t="n">
         <v>1390</v>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>همکف از 4</t>
         </is>
       </c>
-      <c r="Q36" t="b">
-        <v>0</v>
-      </c>
-      <c r="R36" t="b">
-        <v>1</v>
-      </c>
-      <c r="S36" t="b">
-        <v>1</v>
-      </c>
-      <c r="T36" t="n">
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34" t="b">
+        <v>1</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
         <v>4</v>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>premium-panel</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>۲۵ مهر ۱۴۰۵، ۱۰:۲۸</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="n">
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="n">
         <v>35.68225090847448</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="Y34" t="n">
         <v>51.36458075917938</v>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>FUZZY</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>APPROXIMATE</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>api_approximate</t>
         </is>
       </c>
-      <c r="AC36" t="n">
+      <c r="AC34" t="n">
         <v>500</v>
       </c>
-      <c r="AD36" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
         </is>
       </c>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="n">
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="n">
         <v>1851</v>
       </c>
-      <c r="AJ36" t="n">
+      <c r="AJ34" t="n">
         <v>24.7</v>
       </c>
-      <c r="AK36" t="inlineStr">
+      <c r="AK34" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr">
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr">
         <is>
           <t>osm_n5190423570</t>
         </is>
       </c>
-      <c r="AN36" t="n">
+      <c r="AN34" t="n">
         <v>1402</v>
       </c>
-      <c r="AO36" t="inlineStr">
+      <c r="AO34" t="inlineStr">
         <is>
           <t>Secondary</t>
         </is>
       </c>
-      <c r="AP36" t="inlineStr">
+      <c r="AP34" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ36" t="inlineStr"/>
-      <c r="AR36" t="inlineStr">
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr">
         <is>
           <t>مترو و BRT️⚜️</t>
         </is>
       </c>
-      <c r="AS36" t="n">
+      <c r="AS34" t="n">
         <v>500000000</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="AT34" t="n">
         <v>5000000</v>
       </c>
-      <c r="AU36" t="inlineStr">
+      <c r="AU34" t="inlineStr">
         <is>
           <t>RENT_SLIDER credit.value=500000000</t>
         </is>
       </c>
-      <c r="AV36" t="inlineStr">
+      <c r="AV34" t="inlineStr">
         <is>
           <t>RENT_SLIDER rent.value=5000000</t>
         </is>
       </c>
-      <c r="AW36" t="inlineStr">
+      <c r="AW34" t="inlineStr">
         <is>
           <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>اجاره: ۵,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr">
+      <c r="AY34" t="inlineStr">
         <is>
           <t>credit 650000000 / rent None</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr"/>
-      <c r="BA36" t="inlineStr"/>
-      <c r="BB36" t="inlineStr"/>
-      <c r="BC36" t="inlineStr"/>
-      <c r="BD36" t="inlineStr">
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE36" t="inlineStr"/>
-      <c r="BF36" t="inlineStr">
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr">
         <is>
           <t>2026-11-17T10:28:24.059444</t>
         </is>
       </c>
-      <c r="BG36" t="inlineStr"/>
-      <c r="BH36" t="inlineStr">
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr">
         <is>
           <t>{"osm_n5190423570": 1402, "osm_n5165422504": 1482, "beryanak": 1786, "osm_n5165422503": 1905, "osm_n5183625750": 2020, "osm_n14065977511": 2150, "osm_n14058146709": 2348, "osm_w671794339": 2443, "helal_ahmar": 2596, "osm_w1314615868": 2691, "osm_n14058145512": 2777, "osm_n14075053790": 2907, "osm_n14058145514": 3168, "osm_n11417054143": 3174, "osm_n5162910431": 3280, "osm_w1041344025": 3294, "moniriyeh": 3348, "osm_n14084275564": 3397, "osm_n5186234550": 3475, "mahdieh": 3562, "osm_n11417054161": 3766, "osm_n3635251445": 3920, "osm_w1169531671": 4024, "osm_n14058145515": 4141, "osm_n14058145513": 4211, "teatr_shahr": 4239, "osm_n14084275565": 4243, "osm_n10746895093": 4279, "osm_n5183520307": 4281, "osm_n4396461099": 4782, "osm_n5162855447": 4808, "osm_n14089610125": 4896, "osm_n6737096941": 4906, "osm_n5190423568": 4977, "osm_n5604727197": 4978, "vali_asr": 5030, "osm_n5186262276": 5091, "osm_n13380425834": 5267, "osm_n13202066659": 5372, "osm_n14072135584": 5524, "saadi": 5545, "osm_n5165462147": 5614, "osm_n14058409025": 5656, "osm_n13230313218": 5754, "osm_n14075284474": 5773, "osm_n13279314257": 5804, "jahad": 5817, "osm_n8890549263": 5820, "osm_n13380425818": 5829, "darvazeh_dowlat": 5950, "osm_n14071125007": 5981, "osm_n14072135585": 6075, "taleghani": 6159, "osm_n14058409026": 6295, "osm_n13380425728": 6468, "osm_n5165462148": 6638, "osm_n14059862414": 6645, "haft_tir": 6677, "osm_n14072135586": 6725, "osm_n5188341403": 6824, "osm_n5602579936": 6878, "mirza_shirazi": 6964, "osm_n14065945232": 7291, "osm_n12157511978": 7347, "mofatteh": 7387, "osm_n8243426038": 7432, "osm_n5183513583": 7454, "osm_n13284688255": 7493, "osm_n10861347776": 7497, "osm_n6390530109": 7532, "osm_n12659430599": 7556, "osm_n13426743990": 7669, "osm_n14060820580": 7683, "osm_n14071125009": 7743, "shahid_beheshti": 7795, "osm_n9149513248": 7983, "osm_n14075284475": 8030, "osm_n6444462277": 8340, "osm_n2169732971": 8379, "sohrevardi": 8490, "osm_n14058409027": 8517, "osm_n13381123730": 8611, "osm_n14064336782": 8743, "osm_n14059828792": 8982, "osm_n3778821747": 9069, "osm_n660658572": 9271, "osm_n8273593826": 9361, "osm_n14075125227": 9378, "osm_n13380418873": 9437, "osm_n14075284476": 9437, "osm_n14072135587": 9459, "osm_n14075125225": 9825, "osm_n14058409028": 9869, "osm_n13381123745": 9969, "osm_n5162910430": 10237, "osm_n14072135588": 10337, "osm_n14064708968": 10587, "osm_n14075284477": 10598, "osm_n13381123758": 10667, "osm_n8907277818": 11021, "osm_n3778861787": 11130, "osm_n14058409029": 11176, "osm_n5162910441": 11218, "osm_n6390530105": 11432, "osm_n11750922029": 11466, "osm_n13381123759": 11496, "osm_n5604726917": 11564, "osm_n14064708967": 11578, "osm_n2169380700": 12050, "osm_n14058409030": 12193, "osm_n5162910442": 12346, "osm_n13230283736": 12493, "osm_n14072135590": 12631, "osm_n13381123770": 13129, "osm_n14058409031": 13176, "osm_n13817588094": 13340, "osm_n13381264373": 13902, "osm_n14058409032": 13942, "osm_n11281445852": 13959, "osm_n3778822187": 13996, "osm_n5163103599": 14856, "osm_n14072135591": 14891, "osm_n13381264374": 14974, "osm_n5162855462": 15089, "osm_n5194776019": 15271, "osm_n14061094940": 15869, "osm_n5163103601": 16041, "osm_n8738914819": 17045, "osm_n5163103600": 17304, "osm_n5163103597": 18249, "osm_n5163103598": 19157}</t>
         </is>
       </c>
-      <c r="BI36" t="inlineStr">
+      <c r="BI34" t="inlineStr">
         <is>
           <t>⚜️مشاورین کندو⚜️
      ⚜️️آپارتمان 65متر خوش نقشه تخلیه️⚜️
@@ -8957,218 +8467,218 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>pin is ~1851 m estimated walk (1402 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRT️⚜️</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>gaLHDD_8</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaLHDD_8</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>آپارتمان70متری/2خواب/پارکینگ موتور/اوکازیون/جیحون</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>جیحون</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>خ باقرزاده</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>جیحون</t>
         </is>
       </c>
-      <c r="I37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
         <v>500000000</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K35" t="n">
         <v>15000000</v>
       </c>
-      <c r="L37" t="b">
-        <v>1</v>
-      </c>
-      <c r="M37" t="n">
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
         <v>70</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N35" t="n">
         <v>2</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O35" t="n">
         <v>1390</v>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>همکف از 4</t>
         </is>
       </c>
-      <c r="Q37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R37" t="b">
-        <v>1</v>
-      </c>
-      <c r="S37" t="b">
-        <v>1</v>
-      </c>
-      <c r="T37" t="n">
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
+      <c r="R35" t="b">
+        <v>1</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
         <v>5</v>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>premium-panel</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>۱۹ مهر ۱۴۰۵، ۱۰:۵۶</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="n">
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="n">
         <v>35.68223546929239</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Y35" t="n">
         <v>51.36458189763601</v>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>FUZZY</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>APPROXIMATE</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>api_approximate</t>
         </is>
       </c>
-      <c r="AC37" t="n">
+      <c r="AC35" t="n">
         <v>500</v>
       </c>
-      <c r="AD37" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
         </is>
       </c>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="n">
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="n">
         <v>1851</v>
       </c>
-      <c r="AJ37" t="n">
+      <c r="AJ35" t="n">
         <v>24.7</v>
       </c>
-      <c r="AK37" t="inlineStr">
+      <c r="AK35" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr">
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr">
         <is>
           <t>osm_n5190423570</t>
         </is>
       </c>
-      <c r="AN37" t="n">
+      <c r="AN35" t="n">
         <v>1402</v>
       </c>
-      <c r="AO37" t="inlineStr">
+      <c r="AO35" t="inlineStr">
         <is>
           <t>Secondary</t>
         </is>
       </c>
-      <c r="AP37" t="inlineStr">
+      <c r="AP35" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ37" t="inlineStr"/>
-      <c r="AR37" t="inlineStr">
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr">
         <is>
           <t>مترو و BRT️⚜️</t>
         </is>
       </c>
-      <c r="AS37" t="n">
+      <c r="AS35" t="n">
         <v>500000000</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="AT35" t="n">
         <v>15000000</v>
       </c>
-      <c r="AU37" t="inlineStr">
+      <c r="AU35" t="inlineStr">
         <is>
           <t>RENT_SLIDER credit.value=500000000</t>
         </is>
       </c>
-      <c r="AV37" t="inlineStr">
+      <c r="AV35" t="inlineStr">
         <is>
           <t>RENT_SLIDER rent.value=15000000</t>
         </is>
       </c>
-      <c r="AW37" t="inlineStr">
+      <c r="AW35" t="inlineStr">
         <is>
           <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>اجاره: ۱۵,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
+      <c r="AY35" t="inlineStr">
         <is>
           <t>credit 1000000000 / rent None</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr"/>
-      <c r="BA37" t="inlineStr"/>
-      <c r="BB37" t="inlineStr"/>
-      <c r="BC37" t="inlineStr"/>
-      <c r="BD37" t="inlineStr">
+      <c r="AZ35" t="inlineStr"/>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE37" t="inlineStr"/>
-      <c r="BF37" t="inlineStr">
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr">
         <is>
           <t>2026-11-11T10:56:47.07346</t>
         </is>
       </c>
-      <c r="BG37" t="inlineStr"/>
-      <c r="BH37" t="inlineStr">
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr">
         <is>
           <t>{"osm_n5190423570": 1402, "osm_n5165422504": 1482, "beryanak": 1785, "osm_n5165422503": 1907, "osm_n5183625750": 2022, "osm_n14065977511": 2152, "osm_n14058146709": 2349, "osm_w671794339": 2445, "helal_ahmar": 2594, "osm_w1314615868": 2692, "osm_n14058145512": 2778, "osm_n14075053790": 2909, "osm_n14058145514": 3168, "osm_n11417054143": 3175, "osm_n5162910431": 3281, "osm_w1041344025": 3293, "moniriyeh": 3348, "osm_n14084275564": 3396, "osm_n5186234550": 3476, "mahdieh": 3561, "osm_n11417054161": 3767, "osm_n3635251445": 3918, "osm_w1169531671": 4025, "osm_n14058145515": 4141, "osm_n14058145513": 4213, "teatr_shahr": 4240, "osm_n14084275565": 4241, "osm_n10746895093": 4280, "osm_n5183520307": 4282, "osm_n4396461099": 4782, "osm_n5162855447": 4808, "osm_n14089610125": 4895, "osm_n6737096941": 4905, "osm_n5190423568": 4978, "osm_n5604727197": 4979, "vali_asr": 5031, "osm_n5186262276": 5091, "osm_n13380425834": 5266, "osm_n13202066659": 5372, "osm_n14072135584": 5526, "saadi": 5545, "osm_n5165462147": 5612, "osm_n14058409025": 5656, "osm_n13230313218": 5755, "osm_n14075284474": 5775, "osm_n13279314257": 5805, "jahad": 5818, "osm_n8890549263": 5821, "osm_n13380425818": 5828, "darvazeh_dowlat": 5951, "osm_n14071125007": 5980, "osm_n14072135585": 6077, "taleghani": 6160, "osm_n14058409026": 6295, "osm_n13380425728": 6467, "osm_n5165462148": 6636, "osm_n14059862414": 6644, "haft_tir": 6677, "osm_n14072135586": 6726, "osm_n5188341403": 6825, "osm_n5602579936": 6879, "mirza_shirazi": 6965, "osm_n14065945232": 7293, "osm_n12157511978": 7349, "mofatteh": 7388, "osm_n8243426038": 7432, "osm_n5183513583": 7453, "osm_n13284688255": 7492, "osm_n10861347776": 7498, "osm_n6390530109": 7532, "osm_n12659430599": 7555, "osm_n13426743990": 7670, "osm_n14060820580": 7684, "osm_n14071125009": 7744, "shahid_beheshti": 7796, "osm_n9149513248": 7982, "osm_n14075284475": 8031, "osm_n6444462277": 8339, "osm_n2169732971": 8379, "sohrevardi": 8491, "osm_n14058409027": 8518, "osm_n13381123730": 8612, "osm_n14064336782": 8744, "osm_n14059828792": 8982, "osm_n3778821747": 9070, "osm_n660658572": 9272, "osm_n8273593826": 9360, "osm_n14075125227": 9379, "osm_n13380418873": 9435, "osm_n14075284476": 9439, "osm_n14072135587": 9460, "osm_n14075125225": 9825, "osm_n14058409028": 9869, "osm_n13381123745": 9970, "osm_n5162910430": 10237, "osm_n14072135588": 10338, "osm_n14064708968": 10588, "osm_n14075284477": 10600, "osm_n13381123758": 10668, "osm_n8907277818": 11019, "osm_n3778861787": 11131, "osm_n14058409029": 11177, "osm_n5162910441": 11218, "osm_n6390530105": 11431, "osm_n11750922029": 11466, "osm_n13381123759": 11497, "osm_n5604726917": 11564, "osm_n14064708967": 11579, "osm_n2169380700": 12051, "osm_n14058409030": 12193, "osm_n5162910442": 12346, "osm_n13230283736": 12495, "osm_n14072135590": 12632, "osm_n13381123770": 13131, "osm_n14058409031": 13177, "osm_n13817588094": 13339, "osm_n13381264373": 13904, "osm_n14058409032": 13943, "osm_n11281445852": 13957, "osm_n3778822187": 13997, "osm_n5163103599": 14856, "osm_n14072135591": 14892, "osm_n13381264374": 14976, "osm_n5162855462": 15088, "osm_n5194776019": 15269, "osm_n14061094940": 15870, "osm_n5163103601": 16041, "osm_n8738914819": 17046, "osm_n5163103600": 17304, "osm_n5163103597": 18250, "osm_n5163103598": 19158}</t>
         </is>
       </c>
-      <c r="BI37" t="inlineStr">
+      <c r="BI35" t="inlineStr">
         <is>
           <t>⚜️مشاورین املاک کندو⚜️
          ⚜️️آپارتمان70متری خوش نقشه تخلیه️⚜️
@@ -9203,214 +8713,214 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>pin is ~1884 m estimated walk (1427 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRT️</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>gah786Yu</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gah786Yu</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>آپارتمان70متر/آسانسور/پارکینگ موتور/فول شیک</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>جیحون</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>خ مرتضوی</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>جیحون</t>
         </is>
       </c>
-      <c r="I38" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
         <v>500000000</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K36" t="n">
         <v>15000000</v>
       </c>
-      <c r="L38" t="b">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>70</v>
       </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="n">
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
         <v>1399</v>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>3 از 4</t>
         </is>
       </c>
-      <c r="Q38" t="b">
-        <v>1</v>
-      </c>
-      <c r="R38" t="b">
-        <v>1</v>
-      </c>
-      <c r="S38" t="b">
-        <v>1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" t="inlineStr">
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="b">
+        <v>1</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="inlineStr">
         <is>
           <t>premium-panel</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>۶ آبان ۱۴۰۵، ۱۵:۵۵</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="n">
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="n">
         <v>35.6834902140664</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Y36" t="n">
         <v>51.3644888994061</v>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>FUZZY</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>APPROXIMATE</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>api_approximate</t>
         </is>
       </c>
-      <c r="AC38" t="n">
+      <c r="AC36" t="n">
         <v>500</v>
       </c>
-      <c r="AD38" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
         </is>
       </c>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="n">
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="n">
         <v>1884</v>
       </c>
-      <c r="AJ38" t="n">
+      <c r="AJ36" t="n">
         <v>25.1</v>
       </c>
-      <c r="AK38" t="inlineStr">
+      <c r="AK36" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr">
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr">
         <is>
           <t>osm_n5190423570</t>
         </is>
       </c>
-      <c r="AN38" t="n">
+      <c r="AN36" t="n">
         <v>1427</v>
       </c>
-      <c r="AO38" t="inlineStr">
+      <c r="AO36" t="inlineStr">
         <is>
           <t>Secondary</t>
         </is>
       </c>
-      <c r="AP38" t="inlineStr">
+      <c r="AP36" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr">
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr">
         <is>
           <t>مترو و BRT️</t>
         </is>
       </c>
-      <c r="AS38" t="n">
+      <c r="AS36" t="n">
         <v>500000000</v>
       </c>
-      <c r="AT38" t="n">
+      <c r="AT36" t="n">
         <v>15000000</v>
       </c>
-      <c r="AU38" t="inlineStr">
+      <c r="AU36" t="inlineStr">
         <is>
           <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV38" t="inlineStr">
+      <c r="AV36" t="inlineStr">
         <is>
           <t>‏۱۵,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AW38" t="inlineStr">
+      <c r="AW36" t="inlineStr">
         <is>
           <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
+      <c r="AX36" t="inlineStr">
         <is>
           <t>اجاره: ۱۵,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr"/>
-      <c r="BA38" t="inlineStr"/>
-      <c r="BB38" t="inlineStr"/>
-      <c r="BC38" t="inlineStr"/>
-      <c r="BD38" t="inlineStr">
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE38" t="inlineStr"/>
-      <c r="BF38" t="inlineStr">
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr">
         <is>
           <t>2026-11-28T15:55:22.384303</t>
         </is>
       </c>
-      <c r="BG38" t="inlineStr"/>
-      <c r="BH38" t="inlineStr">
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr">
         <is>
           <t>{"osm_n5190423570": 1427, "osm_n5165422504": 1438, "osm_n5165422503": 1812, "beryanak": 1875, "osm_n5183625750": 1882, "osm_n14065977511": 2019, "osm_n14058146709": 2303, "osm_w671794339": 2331, "osm_w1314615868": 2584, "osm_n14058145512": 2645, "helal_ahmar": 2690, "osm_n14075053790": 2785, "osm_n11417054143": 3136, "osm_n14058145514": 3154, "osm_n5162910431": 3200, "moniriyeh": 3365, "osm_n5186234550": 3392, "osm_w1041344025": 3407, "osm_n14084275564": 3533, "mahdieh": 3636, "osm_n11417054161": 3716, "osm_w1169531671": 3930, "osm_n3635251445": 4016, "osm_n14058145513": 4085, "osm_n14058145515": 4137, "osm_n10746895093": 4167, "teatr_shahr": 4179, "osm_n5183520307": 4213, "osm_n14084275565": 4381, "osm_n4396461099": 4805, "osm_n5162855447": 4847, "osm_n5190423568": 4848, "osm_n5604727197": 4863, "vali_asr": 4948, "osm_n6737096941": 4961, "osm_n14089610125": 5033, "osm_n5186262276": 5090, "osm_n13202066659": 5326, "osm_n13380425834": 5348, "osm_n14072135584": 5388, "saadi": 5524, "osm_n14075284474": 5644, "osm_n14058409025": 5649, "osm_n8890549263": 5682, "osm_n13230313218": 5686, "jahad": 5723, "osm_n13279314257": 5725, "osm_n5165462147": 5744, "darvazeh_dowlat": 5910, "osm_n13380425818": 5919, "osm_n14072135585": 5940, "osm_n14071125007": 6023, "taleghani": 6106, "osm_n14058409026": 6280, "osm_n13380425728": 6573, "osm_n14072135586": 6598, "haft_tir": 6608, "osm_n14059862414": 6683, "osm_n5165462148": 6761, "osm_n5602579936": 6793, "osm_n5188341403": 6796, "mirza_shirazi": 6870, "osm_n14065945232": 7172, "osm_n12157511978": 7213, "mofatteh": 7307, "osm_n10861347776": 7392, "osm_n8243426038": 7441, "osm_n6390530109": 7526, "osm_n13284688255": 7530, "osm_n5183513583": 7568, "osm_n12659430599": 7599, "osm_n13426743990": 7638, "osm_n14060820580": 7639, "osm_n14071125009": 7685, "shahid_beheshti": 7707, "osm_n14075284475": 7892, "osm_n9149513248": 8050, "osm_n2169732971": 8373, "sohrevardi": 8409, "osm_n6444462277": 8416, "osm_n14058409027": 8478, "osm_n13381123730": 8514, "osm_n14064336782": 8634, "osm_n3778821747": 8993, "osm_n14059828792": 9016, "osm_n660658572": 9166, "osm_n14075284476": 9300, "osm_n14072135587": 9351, "osm_n14075125227": 9373, "osm_n8273593826": 9449, "osm_n13380418873": 9559, "osm_n14058409028": 9821, "osm_n14075125225": 9855, "osm_n13381123745": 9859, "osm_n5162910430": 10232, "osm_n14072135588": 10266, "osm_n14075284477": 10460, "osm_n14064708968": 10478, "osm_n13381123758": 10560, "osm_n3778861787": 11053, "osm_n14058409029": 11124, "osm_n8907277818": 11146, "osm_n5162910441": 11213, "osm_n13381123759": 11394, "osm_n14064708967": 11466, "osm_n11750922029": 11496, "osm_n5604726917": 11510, "osm_n6390530105": 11524, "osm_n2169380700": 11940, "osm_n14058409030": 12136, "osm_n5162910442": 12334, "osm_n13230283736": 12380, "osm_n14072135590": 12542, "osm_n13381123770": 13013, "osm_n14058409031": 13122, "osm_n13817588094": 13369, "osm_n13381264373": 13783, "osm_n14058409032": 13893, "osm_n3778822187": 13903, "osm_n11281445852": 14095, "osm_n14072135591": 14797, "osm_n5163103599": 14812, "osm_n13381264374": 14852, "osm_n5162855462": 15227, "osm_n5194776019": 15409, "osm_n14061094940": 15770, "osm_n5163103601": 16003, "osm_n8738914819": 16944, "osm_n5163103600": 17270, "osm_n5163103597": 18158, "osm_n5163103598": 19070}</t>
         </is>
       </c>
-      <c r="BI38" t="inlineStr">
+      <c r="BI36" t="inlineStr">
         <is>
           <t>ـمشاورین کندو___________
 ️آپارتمان70متر خوش نقشه تخلیه️
@@ -9448,449 +8958,208 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>pin is ~1883 m estimated walk (1427 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و brt</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>ga7O2Vf2</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://divar.ir/v/ga7O2Vf2</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>۴۵متر/تک واحدی/جیحون/با پارکینگ</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>جیحون</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>خ مرتضوی</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>جیحون</t>
-        </is>
-      </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>400000000</v>
-      </c>
-      <c r="K39" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="L39" t="b">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>45</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1387</v>
-      </c>
-      <c r="P39" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>pin is ~2026 m estimated walk (1535 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>gaDjfQcR</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://divar.ir/v/gaDjfQcR</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>58 متری امام خمینی جیحون</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>هاشمی</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>هاشمی</t>
+        </is>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>58</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1396</v>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>2 از 4</t>
         </is>
       </c>
-      <c r="Q39" t="b">
-        <v>0</v>
-      </c>
-      <c r="R39" t="b">
-        <v>1</v>
-      </c>
-      <c r="S39" t="b">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3</v>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>premium-panel</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>۷ مهر ۱۴۰۵، ۱۰:۴۷</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>۱۴ مهر ۱۴۰۵، ۱۰:۳۶</t>
-        </is>
-      </c>
-      <c r="X39" t="n">
-        <v>35.68358463489643</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>51.36451503350634</v>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>FUZZY</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>APPROXIMATE</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>api_approximate</t>
-        </is>
-      </c>
-      <c r="AC39" t="n">
-        <v>500</v>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="n">
-        <v>1883</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="AK39" t="inlineStr">
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>6</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>personal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>۱۳ مهر ۱۴۰۵، ۲۲:۵۳</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="n">
+        <v>35.686547897133</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>51.357473328431</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>EXACT_DATA_UNTYPED</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>api_exact_pin</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>sections[6].widgets[0].data.location.exact_data.point</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK37" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>osm_n5190423570</t>
-        </is>
-      </c>
-      <c r="AN39" t="n">
-        <v>1427</v>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Secondary</t>
-        </is>
-      </c>
-      <c r="AP39" t="inlineStr">
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>osm_n14065977511</t>
+        </is>
+      </c>
+      <c r="AN37" t="n">
+        <v>1535</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Excluded (&gt;1500 m)</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ39" t="inlineStr"/>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>مترو و brt</t>
-        </is>
-      </c>
-      <c r="AS39" t="n">
-        <v>400000000</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>‏۴۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AV39" t="inlineStr">
-        <is>
-          <t>‏۱۳,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>ودیعه: ۴۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>اجاره: ۱۳,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr"/>
-      <c r="BA39" t="inlineStr"/>
-      <c r="BB39" t="inlineStr"/>
-      <c r="BC39" t="inlineStr"/>
-      <c r="BD39" t="inlineStr">
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>مترو و BRT</t>
+        </is>
+      </c>
+      <c r="AS37" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>‏۱۴,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>اجاره: ۱۴,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE39" t="inlineStr"/>
-      <c r="BF39" t="inlineStr">
-        <is>
-          <t>2026-10-30T10:47:08.660619</t>
-        </is>
-      </c>
-      <c r="BG39" t="inlineStr"/>
-      <c r="BH39" t="inlineStr">
-        <is>
-          <t>{"osm_n5190423570": 1427, "osm_n5165422504": 1432, "osm_n5165422503": 1803, "osm_n5183625750": 1872, "beryanak": 1880, "osm_n14065977511": 2010, "osm_n14058146709": 2297, "osm_w671794339": 2321, "osm_w1314615868": 2578, "osm_n14058145512": 2636, "helal_ahmar": 2695, "osm_n14075053790": 2775, "osm_n11417054143": 3136, "osm_n14058145514": 3150, "osm_n5162910431": 3191, "moniriyeh": 3363, "osm_n5186234550": 3388, "osm_w1041344025": 3413, "osm_n14084275564": 3543, "mahdieh": 3640, "osm_n11417054161": 3715, "osm_w1169531671": 3921, "osm_n3635251445": 4021, "osm_n14058145513": 4077, "osm_n14058145515": 4134, "osm_n10746895093": 4157, "teatr_shahr": 4172, "osm_n5183520307": 4211, "osm_n14084275565": 4391, "osm_n4396461099": 4804, "osm_n5190423568": 4837, "osm_n5162855447": 4847, "osm_n5604727197": 4857, "vali_asr": 4940, "osm_n6737096941": 4962, "osm_n14089610125": 5044, "osm_n5186262276": 5087, "osm_n13202066659": 5320, "osm_n13380425834": 5352, "osm_n14072135584": 5377, "saadi": 5519, "osm_n14075284474": 5633, "osm_n14058409025": 5646, "osm_n8890549263": 5671, "osm_n13230313218": 5683, "jahad": 5713, "osm_n13279314257": 5716, "osm_n5165462147": 5755, "darvazeh_dowlat": 5904, "osm_n13380425818": 5923, "osm_n14072135585": 5931, "osm_n14071125007": 6024, "taleghani": 6099, "osm_n14058409026": 6276, "osm_n13380425728": 6579, "osm_n14072135586": 6590, "haft_tir": 6600, "osm_n14059862414": 6683, "osm_n5165462148": 6772, "osm_n5602579936": 6789, "osm_n5188341403": 6791, "mirza_shirazi": 6861, "osm_n14065945232": 7165, "osm_n12157511978": 7202, "mofatteh": 7298, "osm_n10861347776": 7386, "osm_n8243426038": 7439, "osm_n6390530109": 7522, "osm_n13284688255": 7530, "osm_n5183513583": 7575, "osm_n12659430599": 7600, "osm_n14060820580": 7633, "osm_n13426743990": 7633, "osm_n14071125009": 7678, "shahid_beheshti": 7698, "osm_n14075284475": 7882, "osm_n9149513248": 8052, "osm_n2169732971": 8370, "sohrevardi": 8400, "osm_n6444462277": 8420, "osm_n14058409027": 8472, "osm_n13381123730": 8504, "osm_n14064336782": 8628, "osm_n3778821747": 8985, "osm_n14059828792": 9015, "osm_n660658572": 9156, "osm_n14075284476": 9289, "osm_n14072135587": 9345, "osm_n14075125227": 9370, "osm_n8273593826": 9453, "osm_n13380418873": 9566, "osm_n14058409028": 9815, "osm_n13381123745": 9849, "osm_n14075125225": 9854, "osm_n5162910430": 10229, "osm_n14072135588": 10258, "osm_n14075284477": 10450, "osm_n14064708968": 10471, "osm_n13381123758": 10550, "osm_n3778861787": 11044, "osm_n14058409029": 11117, "osm_n8907277818": 11155, "osm_n5162910441": 11209, "osm_n13381123759": 11384, "osm_n14064708967": 11459, "osm_n11750922029": 11495, "osm_n5604726917": 11509, "osm_n6390530105": 11528, "osm_n2169380700": 11929, "osm_n14058409030": 12130, "osm_n5162910442": 12331, "osm_n13230283736": 12373, "osm_n14072135590": 12533, "osm_n13381123770": 13003, "osm_n14058409031": 13115, "osm_n13817588094": 13368, "osm_n13381264373": 13773, "osm_n14058409032": 13887, "osm_n3778822187": 13894, "osm_n11281445852": 14105, "osm_n14072135591": 14788, "osm_n5163103599": 14805, "osm_n13381264374": 14842, "osm_n5162855462": 15237, "osm_n5194776019": 15419, "osm_n14061094940": 15761, "osm_n5163103601": 15997, "osm_n8738914819": 16934, "osm_n5163103600": 17265, "osm_n5163103597": 18149, "osm_n5163103598": 19061}</t>
-        </is>
-      </c>
-      <c r="BI39" t="inlineStr">
-        <is>
-          <t>✅️ املاک عمارت ،امانت دار منافع شما✅️
-✅️با اطمینان بخرید با رضایت استفاده کنید✅️
----------------------------------------------------------
-✅️ ۴۵متر
-✅️ تک خواب
-✅️ طبقه ۲
-✅️ ۴ طبقه ۱ واحدی
----------------------------------------------------------
-خوش قیمت ترین واحد های منطقه ۹ و ۱۰
-✅️امکانات
-✔️پارکینگ سندی غیر مزاحم
-✔️بالکن
----------------------------------------------------------
-نور مستقیم از پذیرایی/سالن مربع/خوش چیدمان/آشپزخانه بزرگ/کابینت دیزاین/کمد دیواری
-----‐----------------------------------------------------
-دسترسی عالی به: ⬇️
-خیابان آزادی
-یادگار امام
-مترو و brt
----------------------------------------------------------
-لوکیشن:جیحون/مرتضوی
-قیمت: ۴۰۰ ماهی ۱۳
----------------------------------------------------------
-جهت کسب اطلاعات بیشتر و فایل های مشابه تماس بگیرید
-کارشناس شما:جعفرزاده</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>NEEDS_LOCATION_VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>pin is ~2026 m estimated walk (1535 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRT</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>gaDjfQcR</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://divar.ir/v/gaDjfQcR</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>58 متری امام خمینی جیحون</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>هاشمی</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>هاشمی</t>
-        </is>
-      </c>
-      <c r="I40" t="b">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="K40" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="L40" t="b">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>58</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1396</v>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>2 از 4</t>
-        </is>
-      </c>
-      <c r="Q40" t="b">
-        <v>1</v>
-      </c>
-      <c r="R40" t="b">
-        <v>0</v>
-      </c>
-      <c r="S40" t="b">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>6</v>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>personal</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>۱۳ مهر ۱۴۰۵، ۲۲:۵۳</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="n">
-        <v>35.686547897133</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>51.357473328431</v>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>EXACT_DATA_UNTYPED</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>api_exact_pin</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr"/>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>sections[6].widgets[0].data.location.exact_data.point</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Excluded (&gt;1500 m)</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>osm_n14065977511</t>
-        </is>
-      </c>
-      <c r="AN40" t="n">
-        <v>1535</v>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Excluded (&gt;1500 m)</t>
-        </is>
-      </c>
-      <c r="AP40" t="inlineStr">
-        <is>
-          <t>not routed (estimate only)</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr"/>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>مترو و BRT</t>
-        </is>
-      </c>
-      <c r="AS40" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AV40" t="inlineStr">
-        <is>
-          <t>‏۱۴,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>اجاره: ۱۴,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr"/>
-      <c r="BA40" t="inlineStr"/>
-      <c r="BB40" t="inlineStr"/>
-      <c r="BC40" t="inlineStr"/>
-      <c r="BD40" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="BE40" t="inlineStr"/>
-      <c r="BF40" t="inlineStr">
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr">
         <is>
           <t>2026-11-05T22:53:11.985088</t>
         </is>
       </c>
-      <c r="BG40" t="inlineStr"/>
-      <c r="BH40" t="inlineStr">
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr">
         <is>
           <t>{"osm_n14065977511": 1535, "osm_n5183625750": 1677, "osm_w1314615868": 1913, "osm_n5165422504": 1996, "osm_n5190423570": 2121, "osm_n5165422503": 2138, "osm_n14058145512": 2155, "osm_n11417054143": 2457, "osm_w671794339": 2493, "beryanak": 2586, "osm_n5186234550": 2675, "osm_n14058146709": 2828, "osm_n14075053790": 2841, "osm_n11417054161": 3014, "helal_ahmar": 3396, "osm_n5183520307": 3496, "osm_n14058145513": 3514, "osm_n5162910431": 3552, "osm_n14058145514": 3759, "moniriyeh": 4033, "osm_n14084275564": 4047, "osm_w1041344025": 4076, "osm_w1169531671": 4190, "osm_n5604727197": 4214, "osm_n10746895093": 4286, "mahdieh": 4355, "teatr_shahr": 4616, "osm_n3635251445": 4719, "osm_n14058145515": 4760, "osm_n5190423568": 4776, "osm_n14084275565": 4810, "osm_n13230313218": 4968, "osm_n14072135584": 5157, "vali_asr": 5267, "osm_n8890549263": 5327, "osm_n14089610125": 5361, "osm_n14072135585": 5461, "osm_n4396461099": 5481, "osm_n5162855447": 5546, "osm_n14075284474": 5552, "osm_n6737096941": 5674, "osm_n5186262276": 5717, "osm_n13202066659": 5811, "osm_n5165462147": 5941, "jahad": 5957, "osm_n14072135586": 6020, "osm_n13279314257": 6050, "osm_n13380425834": 6065, "osm_n5602579936": 6078, "saadi": 6095, "osm_n14058409025": 6260, "darvazeh_dowlat": 6412, "osm_n14065945232": 6544, "taleghani": 6557, "osm_n13380425818": 6629, "osm_n10861347776": 6709, "osm_n14071125007": 6726, "osm_n5165462148": 6864, "osm_n14058409026": 6866, "haft_tir": 6986, "osm_n12157511978": 7023, "mirza_shirazi": 7098, "osm_n13380425728": 7260, "osm_n5188341403": 7339, "osm_n14059862414": 7380, "osm_n14075284475": 7605, "mofatteh": 7619, "osm_n14064336782": 7963, "shahid_beheshti": 7969, "osm_n8243426038": 8086, "osm_n14071125009": 8110, "osm_n14060820580": 8119, "osm_n6390530109": 8133, "osm_n13426743990": 8169, "osm_n13284688255": 8226, "osm_n5183513583": 8230, "osm_n12659430599": 8302, "osm_n14072135587": 8677, "sohrevardi": 8711, "osm_n13381123730": 8714, "osm_n9149513248": 8768, "osm_n14058409027": 8976, "osm_n2169732971": 8981, "osm_n14075284476": 8995, "osm_n6444462277": 9135, "osm_n660658572": 9309, "osm_n3778821747": 9325, "osm_n14059828792": 9705, "osm_n14064708968": 9806, "osm_n13381123745": 9961, "osm_n14075125227": 9982, "osm_n14075284477": 10092, "osm_n8273593826": 10161, "osm_n13380418873": 10185, "osm_n14058409028": 10284, "osm_n14075125225": 10537, "osm_n14072135588": 10616, "osm_n13381123758": 10685, "osm_n5604726917": 10801, "osm_n14064708967": 10805, "osm_n5162910430": 10840, "osm_n3778861787": 11371, "osm_n13381123759": 11551, "osm_n14058409029": 11563, "osm_n13230283736": 11723, "osm_n8907277818": 11751, "osm_n5162910441": 11819, "osm_n2169380700": 12031, "osm_n11750922029": 12179, "osm_n6390530105": 12232, "osm_n14058409030": 12559, "osm_n14072135590": 12790, "osm_n5162910442": 12922, "osm_n13381123770": 13052, "osm_n14058409031": 13552, "osm_n13381264373": 13793, "osm_n13817588094": 14050, "osm_n3778822187": 14126, "osm_n14058409032": 14344, "osm_n11281445852": 14579, "osm_n13381264374": 14827, "osm_n14072135591": 15010, "osm_n5163103599": 15283, "osm_n5162855462": 15645, "osm_n5194776019": 15792, "osm_n14061094940": 15946, "osm_n5163103601": 16497, "osm_n8738914819": 17102, "osm_n5163103600": 17780, "osm_n5163103597": 18385, "osm_n5163103598": 19321}</t>
         </is>
       </c>
-      <c r="BI40" t="inlineStr">
+      <c r="BI37" t="inlineStr">
         <is>
           <t>تخلیه جهت تحویل
 خ امام خمینی- بین یادگار امام و خ جیحون
@@ -9911,216 +9180,216 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>pin is ~2068 m estimated walk (1566 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و بی ارتی</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>gaIrfAUI</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaIrfAUI</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>آپارتمان۶۲متر۲خواب طبقه۳تمیزبازسازی سلیمانی حسینی</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>سلیمانی</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>خ حسینی</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>سلیمانی</t>
         </is>
       </c>
-      <c r="I41" t="b">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
         <v>400000000</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K38" t="n">
         <v>9700000</v>
       </c>
-      <c r="L41" t="b">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>62</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N38" t="n">
         <v>2</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O38" t="n">
         <v>1387</v>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>3 از 4</t>
         </is>
       </c>
-      <c r="Q41" t="b">
-        <v>0</v>
-      </c>
-      <c r="R41" t="b">
-        <v>0</v>
-      </c>
-      <c r="S41" t="b">
-        <v>1</v>
-      </c>
-      <c r="T41" t="n">
+      <c r="Q38" t="b">
+        <v>0</v>
+      </c>
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
         <v>4</v>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>personal</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>۱۸ مهر ۱۴۰۵، ۱۱:۰۲</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>۲۱ مهر ۱۴۰۵، ۱۱:۴۷</t>
         </is>
       </c>
-      <c r="X41" t="n">
+      <c r="X38" t="n">
         <v>35.669854119404</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="Y38" t="n">
         <v>51.363940077382</v>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>api_exact_pin</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr">
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
-      <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="n">
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="n">
         <v>2068</v>
       </c>
-      <c r="AJ41" t="n">
+      <c r="AJ38" t="n">
         <v>27.6</v>
       </c>
-      <c r="AK41" t="inlineStr">
+      <c r="AK38" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr">
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr">
         <is>
           <t>beryanak</t>
         </is>
       </c>
-      <c r="AN41" t="n">
+      <c r="AN38" t="n">
         <v>1566</v>
       </c>
-      <c r="AO41" t="inlineStr">
+      <c r="AO38" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP41" t="inlineStr">
+      <c r="AP38" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ41" t="inlineStr"/>
-      <c r="AR41" t="inlineStr">
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr">
         <is>
           <t>مترو و بی ارتی</t>
         </is>
       </c>
-      <c r="AS41" t="n">
+      <c r="AS38" t="n">
         <v>400000000</v>
       </c>
-      <c r="AT41" t="n">
+      <c r="AT38" t="n">
         <v>9700000</v>
       </c>
-      <c r="AU41" t="inlineStr">
+      <c r="AU38" t="inlineStr">
         <is>
           <t>‏۴۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV41" t="inlineStr">
+      <c r="AV38" t="inlineStr">
         <is>
           <t>‏۹,۷۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AW41" t="inlineStr">
+      <c r="AW38" t="inlineStr">
         <is>
           <t>ودیعه: ۴۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>اجاره: ۹,۷۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr"/>
-      <c r="BA41" t="inlineStr"/>
-      <c r="BB41" t="inlineStr"/>
-      <c r="BC41" t="inlineStr"/>
-      <c r="BD41" t="inlineStr">
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE41" t="inlineStr"/>
-      <c r="BF41" t="inlineStr">
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr">
         <is>
           <t>2026-11-10T11:02:57.843605</t>
         </is>
       </c>
-      <c r="BG41" t="inlineStr"/>
-      <c r="BH41" t="inlineStr">
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr">
         <is>
           <t>{"beryanak": 1566, "osm_n5190423570": 1937, "helal_ahmar": 2106, "osm_n14084275564": 2109, "osm_n5165422504": 2438, "osm_w1041344025": 2449, "osm_n14084275565": 2879, "osm_n5165422503": 3093, "osm_n14058146709": 3208, "mahdieh": 3215, "osm_n3635251445": 3262, "osm_n5183625750": 3399, "osm_n14065977511": 3460, "osm_n14089610125": 3518, "moniriyeh": 3628, "osm_n11417054143": 3703, "osm_w671794339": 3715, "osm_n14058145514": 3727, "osm_w1314615868": 3802, "osm_n14058145512": 4087, "osm_n14075053790": 4221, "osm_n5165462147": 4287, "osm_n5162910431": 4331, "osm_n11417054161": 4361, "osm_n5186234550": 4365, "osm_n14058145515": 4552, "osm_n6737096941": 4696, "osm_n13380425834": 4750, "osm_n5162855447": 4774, "osm_n4396461099": 4911, "osm_n5183520307": 5008, "teatr_shahr": 5111, "osm_w1169531671": 5148, "osm_n13380425818": 5178, "osm_n5165462148": 5374, "osm_n5186262276": 5433, "osm_n14058145513": 5457, "osm_n10746895093": 5523, "osm_n13380425728": 5617, "osm_n14071125007": 5862, "osm_n14058409025": 6035, "vali_asr": 6053, "saadi": 6056, "osm_n5604727197": 6103, "osm_n13202066659": 6103, "osm_n5190423568": 6318, "osm_n13230313218": 6446, "osm_n5183513583": 6471, "osm_n14059862414": 6555, "darvazeh_dowlat": 6624, "osm_n14058409026": 6734, "osm_n13279314257": 6798, "osm_n14072135584": 6902, "jahad": 6924, "taleghani": 6936, "osm_n14075284474": 7118, "osm_n8890549263": 7191, "osm_n5188341403": 7374, "osm_n13284688255": 7395, "osm_n12659430599": 7395, "osm_n14072135585": 7397, "osm_n9149513248": 7559, "haft_tir": 7572, "osm_n8243426038": 7623, "osm_n5602579936": 7706, "osm_n6444462277": 7799, "osm_n6390530109": 7869, "osm_n14072135586": 7958, "mirza_shirazi": 8062, "osm_n13426743990": 8232, "osm_n13380418873": 8331, "osm_n14060820580": 8366, "mofatteh": 8371, "osm_n14065945232": 8447, "osm_n10861347776": 8511, "osm_n14071125009": 8538, "osm_n8273593826": 8679, "osm_n2169732971": 8695, "osm_n12157511978": 8717, "shahid_beheshti": 8840, "osm_n14059828792": 8903, "osm_n14058409027": 9144, "osm_n14075284475": 9409, "sohrevardi": 9473, "osm_n14075125227": 9677, "osm_n13381123730": 9722, "osm_n14075125225": 9777, "osm_n14064336782": 9790, "osm_n8907277818": 9859, "osm_n3778821747": 10002, "osm_n660658572": 10437, "osm_n14072135587": 10493, "osm_n5162910430": 10525, "osm_n14058409028": 10556, "osm_n6390530105": 10686, "osm_n14075284476": 10817, "osm_n13381123745": 11169, "osm_n14072135588": 11229, "osm_n11750922029": 11396, "osm_n5162910441": 11501, "osm_n14064708968": 11626, "osm_n13381123758": 11842, "osm_n14058409029": 11899, "osm_n14075284477": 11969, "osm_n5604726917": 12042, "osm_n3778861787": 12065, "osm_n11281445852": 12635, "osm_n13381123759": 12636, "osm_n14064708967": 12647, "osm_n5162910442": 12680, "osm_n14058409030": 12941, "osm_n2169380700": 13252, "osm_n13817588094": 13266, "osm_n13230283736": 13571, "osm_n14072135590": 13658, "osm_n5162855462": 13727, "osm_n5194776019": 13898, "osm_n14058409031": 13903, "osm_n13381123770": 14372, "osm_n14058409032": 14621, "osm_n3778822187": 15049, "osm_n13381264373": 15165, "osm_n5163103599": 15483, "osm_n14072135591": 15952, "osm_n13381264374": 16260, "osm_n5163103601": 16610, "osm_n14061094940": 16973, "osm_n5163103600": 17829, "osm_n8738914819": 18165, "osm_n5163103597": 19284, "osm_n5163103598": 20157}</t>
         </is>
       </c>
-      <c r="BI41" t="inlineStr">
+      <c r="BI38" t="inlineStr">
         <is>
           <t>املاک
 همکار زنگ نزن
@@ -10170,218 +9439,218 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>pin is ~2089 m estimated walk (1583 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRTکمتر از 10دقیقه</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>gaCvBQsh</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaCvBQsh</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>۴۵متر/۱خواب/خوش نقشه/بالکن</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>سلیمانی</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>خ کاظمی</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>سلیمانی</t>
         </is>
       </c>
-      <c r="I42" t="b">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
         <v>500000000</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K39" t="n">
         <v>4000000</v>
       </c>
-      <c r="L42" t="b">
-        <v>1</v>
-      </c>
-      <c r="M42" t="n">
+      <c r="L39" t="b">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
         <v>45</v>
       </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
         <v>1388</v>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q42" t="b">
-        <v>0</v>
-      </c>
-      <c r="R42" t="b">
-        <v>0</v>
-      </c>
-      <c r="S42" t="b">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" t="inlineStr">
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
+      <c r="R39" t="b">
+        <v>0</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="inlineStr">
         <is>
           <t>premium-panel</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>۱۲ مهر ۱۴۰۵، ۱۸:۴۶</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="n">
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="n">
         <v>35.67519959430987</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="Y39" t="n">
         <v>51.36349141614174</v>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>FUZZY</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>APPROXIMATE</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>api_approximate</t>
         </is>
       </c>
-      <c r="AC42" t="n">
+      <c r="AC39" t="n">
         <v>500</v>
       </c>
-      <c r="AD42" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
         </is>
       </c>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="n">
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="n">
         <v>2089</v>
       </c>
-      <c r="AJ42" t="n">
+      <c r="AJ39" t="n">
         <v>27.9</v>
       </c>
-      <c r="AK42" t="inlineStr">
+      <c r="AK39" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr">
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr">
         <is>
           <t>beryanak</t>
         </is>
       </c>
-      <c r="AN42" t="n">
+      <c r="AN39" t="n">
         <v>1583</v>
       </c>
-      <c r="AO42" t="inlineStr">
+      <c r="AO39" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP42" t="inlineStr">
+      <c r="AP39" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="inlineStr">
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr">
         <is>
           <t>مترو و BRTکمتر از 10دقیقه</t>
         </is>
       </c>
-      <c r="AS42" t="n">
+      <c r="AS39" t="n">
         <v>500000000</v>
       </c>
-      <c r="AT42" t="n">
+      <c r="AT39" t="n">
         <v>4000000</v>
       </c>
-      <c r="AU42" t="inlineStr">
+      <c r="AU39" t="inlineStr">
         <is>
           <t>RENT_SLIDER credit.value=500000000</t>
         </is>
       </c>
-      <c r="AV42" t="inlineStr">
+      <c r="AV39" t="inlineStr">
         <is>
           <t>RENT_SLIDER rent.value=4000000</t>
         </is>
       </c>
-      <c r="AW42" t="inlineStr">
+      <c r="AW39" t="inlineStr">
         <is>
           <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
+      <c r="AX39" t="inlineStr">
         <is>
           <t>اجاره: ۴,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr">
+      <c r="AY39" t="inlineStr">
         <is>
           <t>credit 600000000 / rent None</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr"/>
-      <c r="BA42" t="inlineStr"/>
-      <c r="BB42" t="inlineStr"/>
-      <c r="BC42" t="inlineStr"/>
-      <c r="BD42" t="inlineStr">
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE42" t="inlineStr"/>
-      <c r="BF42" t="inlineStr">
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr">
         <is>
           <t>2026-11-04T18:46:52.775659</t>
         </is>
       </c>
-      <c r="BG42" t="inlineStr"/>
-      <c r="BH42" t="inlineStr">
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr">
         <is>
           <t>{"beryanak": 1583, "osm_n5190423570": 1645, "osm_n5165422504": 2011, "helal_ahmar": 2288, "osm_n5165422503": 2592, "osm_n14084275564": 2675, "osm_n5183625750": 2806, "osm_w1041344025": 2812, "osm_n14058146709": 2838, "osm_n14065977511": 2871, "osm_w671794339": 3183, "osm_w1314615868": 3263, "osm_n11417054143": 3359, "mahdieh": 3362, "osm_n14084275565": 3473, "osm_n14058145514": 3490, "osm_n14058145512": 3499, "moniriyeh": 3507, "osm_n3635251445": 3551, "osm_n14075053790": 3671, "osm_n5162910431": 3896, "osm_n5186234550": 3900, "osm_n11417054161": 4001, "osm_n14089610125": 4107, "osm_n14058145515": 4388, "osm_n5183520307": 4605, "osm_w1169531671": 4686, "teatr_shahr": 4757, "osm_n6737096941": 4803, "osm_n5162855447": 4805, "osm_n5165462147": 4835, "osm_n4396461099": 4873, "osm_n14058145513": 4887, "osm_n13380425834": 4993, "osm_n10746895093": 5008, "osm_n5186262276": 5308, "osm_n13380425818": 5482, "osm_n5604727197": 5569, "vali_asr": 5638, "osm_n5190423568": 5755, "osm_n13202066659": 5815, "saadi": 5862, "osm_n5165462148": 5884, "osm_n14058409025": 5898, "osm_n14071125007": 5939, "osm_n13380425728": 6011, "osm_n13230313218": 6065, "osm_n14072135584": 6314, "darvazeh_dowlat": 6364, "osm_n13279314257": 6399, "jahad": 6475, "osm_n14075284474": 6554, "osm_n14058409026": 6575, "osm_n8890549263": 6596, "osm_n14059862414": 6624, "taleghani": 6632, "osm_n14072135585": 6809, "osm_n5183513583": 6923, "osm_n5188341403": 7170, "haft_tir": 7218, "osm_n5602579936": 7279, "osm_n14072135586": 7394, "osm_n13284688255": 7471, "osm_n12659430599": 7498, "osm_n8243426038": 7575, "mirza_shirazi": 7619, "osm_n6390530109": 7759, "osm_n9149513248": 7776, "osm_n14065945232": 7907, "mofatteh": 7980, "osm_n10861347776": 8019, "osm_n13426743990": 8025, "osm_n6444462277": 8067, "osm_n14060820580": 8108, "osm_n12157511978": 8137, "osm_n14071125009": 8231, "shahid_beheshti": 8422, "osm_n2169732971": 8597, "osm_n14075284475": 8817, "osm_n13380418873": 8836, "osm_n14058409027": 8912, "osm_n14059828792": 8976, "osm_n8273593826": 9009, "sohrevardi": 9084, "osm_n13381123730": 9275, "osm_n14064336782": 9288, "osm_n14075125227": 9589, "osm_n3778821747": 9636, "osm_n14075125225": 9839, "osm_n660658572": 9964, "osm_n14072135587": 9996, "osm_n14075284476": 10224, "osm_n14058409028": 10300, "osm_n8907277818": 10387, "osm_n5162910430": 10444, "osm_n13381123745": 10681, "osm_n14072135588": 10884, "osm_n6390530105": 11046, "osm_n14064708968": 11128, "osm_n13381123758": 11366, "osm_n14075284477": 11374, "osm_n5162910441": 11424, "osm_n11750922029": 11471, "osm_n14058409029": 11630, "osm_n3778861787": 11701, "osm_n5604726917": 11758, "osm_n14064708967": 12139, "osm_n13381123759": 12177, "osm_n5162910442": 12582, "osm_n14058409030": 12661, "osm_n2169380700": 12763, "osm_n13230283736": 13061, "osm_n11281445852": 13220, "osm_n14072135590": 13253, "osm_n13817588094": 13346, "osm_n14058409031": 13634, "osm_n13381123770": 13864, "osm_n5162855462": 14322, "osm_n14058409032": 14374, "osm_n5194776019": 14493, "osm_n3778822187": 14632, "osm_n13381264373": 14647, "osm_n5163103599": 15260, "osm_n14072135591": 15532, "osm_n13381264374": 15730, "osm_n5163103601": 16414, "osm_n14061094940": 16533, "osm_n5163103600": 17653, "osm_n8738914819": 17718, "osm_n5163103597": 18878, "osm_n5163103598": 19767}</t>
         </is>
       </c>
-      <c r="BI42" t="inlineStr">
+      <c r="BI39" t="inlineStr">
         <is>
           <t>...هوالرزاق...
 رهن و اجاره آپارتمان:
@@ -10397,222 +9666,222 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>pin is ~2153 m estimated walk (1631 m straight-line) from nearest target station; text mentions target metro jahad: مترو جهاد</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>ga2m-38Q</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>https://divar.ir/v/ga2m-38Q</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>تا 80 متر/یوسف‌آباد/امیرآباد/فاطمی</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>یوسف‌آباد</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>خ جهان‌آرا</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>یوسف‌آباد</t>
         </is>
       </c>
-      <c r="I43" t="b">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
         <v>300000000</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K40" t="n">
         <v>1000</v>
       </c>
-      <c r="L43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
+      <c r="L40" t="b">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>70</v>
       </c>
-      <c r="N43" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" t="n">
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
         <v>1380</v>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>1 از 5</t>
         </is>
       </c>
-      <c r="Q43" t="b">
-        <v>1</v>
-      </c>
-      <c r="R43" t="b">
-        <v>1</v>
-      </c>
-      <c r="S43" t="b">
-        <v>1</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="inlineStr">
+      <c r="Q40" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" t="b">
+        <v>1</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="inlineStr">
         <is>
           <t>premium-panel</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>۴ مهر ۱۴۰۵، ۱۶:۱۷</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>۴ آبان ۱۴۰۵، ۰۹:۵۸</t>
         </is>
       </c>
-      <c r="X43" t="n">
+      <c r="X40" t="n">
         <v>35.737869963268</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="Y40" t="n">
         <v>51.403844842472</v>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>FUZZY</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>APPROXIMATE</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>api_approximate</t>
         </is>
       </c>
-      <c r="AC43" t="n">
+      <c r="AC40" t="n">
         <v>500</v>
       </c>
-      <c r="AD43" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
         </is>
       </c>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="n">
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="n">
         <v>2153</v>
       </c>
-      <c r="AJ43" t="n">
+      <c r="AJ40" t="n">
         <v>28.7</v>
       </c>
-      <c r="AK43" t="inlineStr">
+      <c r="AK40" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr">
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr">
         <is>
           <t>mirza_shirazi</t>
         </is>
       </c>
-      <c r="AN43" t="n">
+      <c r="AN40" t="n">
         <v>1631</v>
       </c>
-      <c r="AO43" t="inlineStr">
+      <c r="AO40" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP43" t="inlineStr">
+      <c r="AP40" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ43" t="inlineStr">
+      <c r="AQ40" t="inlineStr">
         <is>
           <t>jahad</t>
         </is>
       </c>
-      <c r="AR43" t="inlineStr">
+      <c r="AR40" t="inlineStr">
         <is>
           <t>مترو جهاد</t>
         </is>
       </c>
-      <c r="AS43" t="n">
+      <c r="AS40" t="n">
         <v>300000000</v>
       </c>
-      <c r="AT43" t="n">
+      <c r="AT40" t="n">
         <v>1000</v>
       </c>
-      <c r="AU43" t="inlineStr">
+      <c r="AU40" t="inlineStr">
         <is>
           <t>‏۳۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV43" t="inlineStr">
+      <c r="AV40" t="inlineStr">
         <is>
           <t>‏۱,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AW43" t="inlineStr">
+      <c r="AW40" t="inlineStr">
         <is>
           <t>ودیعه: ۳۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>اجاره: ۱,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr"/>
-      <c r="BA43" t="inlineStr"/>
-      <c r="BB43" t="inlineStr"/>
-      <c r="BC43" t="inlineStr"/>
-      <c r="BD43" t="inlineStr">
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr"/>
+      <c r="BA40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE43" t="inlineStr"/>
-      <c r="BF43" t="inlineStr">
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr">
         <is>
           <t>2026-11-26T16:17:44.514498</t>
         </is>
       </c>
-      <c r="BG43" t="inlineStr"/>
-      <c r="BH43" t="inlineStr">
+      <c r="BG40" t="inlineStr"/>
+      <c r="BH40" t="inlineStr">
         <is>
           <t>{"mirza_shirazi": 1631, "jahad": 1969, "osm_n14075284474": 1990, "osm_n13381123730": 2167, "shahid_beheshti": 2247, "osm_n660658572": 2368, "osm_n5190423568": 2493, "osm_n12157511978": 2512, "mofatteh": 2626, "osm_n13279314257": 2697, "osm_n10746895093": 2856, "osm_n13381123745": 2901, "vali_asr": 2939, "sohrevardi": 3063, "osm_n14072135584": 3083, "haft_tir": 3191, "osm_w1169531671": 3344, "osm_n13381123758": 3656, "osm_n14075284475": 3723, "osm_n3778821747": 3766, "taleghani": 3938, "osm_n8890549263": 4023, "teatr_shahr": 4073, "osm_n14071125009": 4078, "osm_n5162910431": 4208, "osm_n14075053790": 4247, "osm_n13202066659": 4270, "darvazeh_dowlat": 4505, "osm_n13381123759": 4583, "osm_n14075284476": 4683, "osm_w671794339": 4686, "osm_n14060820580": 4770, "osm_n14072135588": 4929, "osm_n2169380700": 4955, "osm_n14072135585": 5228, "osm_n5188341403": 5272, "osm_n5165422503": 5284, "saadi": 5290, "osm_n3778861787": 5296, "osm_n14058146709": 5416, "osm_n5183625750": 5458, "osm_n14058409027": 5468, "osm_n13426743990": 5468, "osm_n14058145514": 5625, "osm_n14058409026": 5714, "osm_n14058145512": 5735, "osm_n14058145515": 5781, "osm_n14058409025": 5881, "osm_n14058409028": 5882, "osm_n14058145513": 5958, "osm_n5186262276": 5980, "osm_n5165422504": 5990, "osm_n13381123770": 6001, "osm_n14065977511": 6006, "osm_n14072135590": 6142, "osm_n14075284477": 6165, "moniriyeh": 6311, "osm_n14072135586": 6571, "osm_n14058409029": 6603, "osm_n6390530109": 6611, "osm_n5190423570": 6642, "osm_n4396461099": 6735, "osm_w1314615868": 6786, "osm_n13381264373": 6789, "osm_n5604727197": 6928, "osm_n2169732971": 7116, "osm_n14058409030": 7264, "osm_n8243426038": 7274, "osm_n5162855447": 7287, "osm_n3778822187": 7323, "beryanak": 7498, "osm_n14065945232": 7572, "osm_n5186234550": 7676, "osm_n14075125227": 7782, "mahdieh": 7872, "osm_n6737096941": 7877, "osm_n13381264374": 7902, "helal_ahmar": 7940, "osm_n14071125007": 7958, "osm_n14059862414": 8134, "osm_n14072135591": 8155, "osm_n14058409031": 8213, "osm_n5162910430": 8395, "osm_n5183520307": 8516, "osm_n11417054143": 8565, "osm_n13284688255": 8595, "osm_n11417054161": 8675, "osm_n3635251445": 8731, "osm_n10861347776": 8759, "osm_w1041344025": 8843, "osm_n12659430599": 8898, "osm_n14061094940": 8973, "osm_n13380425834": 8994, "osm_n5162910441": 9112, "osm_n14058409032": 9136, "osm_n14064336782": 9300, "osm_n13230313218": 9397, "osm_n14059828792": 9398, "osm_n5602579936": 9463, "osm_n5162910442": 9700, "osm_n13380425818": 9736, "osm_n14075125225": 9814, "osm_n14084275564": 9869, "osm_n14072135587": 9880, "osm_n8738914819": 10087, "osm_n5163103599": 10214, "osm_n9149513248": 10254, "osm_n14064708968": 10656, "osm_n13380425728": 10842, "osm_n14084275565": 10890, "osm_n6444462277": 10980, "osm_n11750922029": 11115, "osm_n14064708967": 11182, "osm_n5163103597": 11533, "osm_n5163103601": 11579, "osm_n14089610125": 11752, "osm_n13230283736": 11837, "osm_n5183513583": 12082, "osm_n8273593826": 12339, "osm_n5163103598": 12545, "osm_n13817588094": 12626, "osm_n5165462147": 12654, "osm_n5163103600": 12957, "osm_n5165462148": 13746, "osm_n13380418873": 14283, "osm_n6390530105": 14315, "osm_n5604726917": 14627, "osm_n8907277818": 15980, "osm_n11281445852": 19789, "osm_n5162855462": 21270, "osm_n5194776019": 21616}</t>
         </is>
       </c>
-      <c r="BI43" t="inlineStr">
+      <c r="BI40" t="inlineStr">
         <is>
           <t>⏫️فرصتی محدود برای تجربه حس آرامش⏫️    
     ✳️  املاک ارگ ، معمار رویاهای شما ✳️
@@ -10633,212 +9902,212 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>pin is ~2160 m estimated walk (1637 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و مراکز خرید عالی نورگیر فوقال</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>gafziAqx</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gafziAqx</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>رهن اجاره ۴۰ متر آپارتمان حاجیان انتهای جیحون</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>سلیمانی</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>خ خواجه زاده</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>سلیمانی</t>
         </is>
       </c>
-      <c r="I44" t="b">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
         <v>400000000</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K41" t="n">
         <v>10000000</v>
       </c>
-      <c r="L44" t="b">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>40</v>
       </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" t="n">
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
         <v>1385</v>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>همکف از 3</t>
         </is>
       </c>
-      <c r="Q44" t="b">
-        <v>0</v>
-      </c>
-      <c r="R44" t="b">
-        <v>0</v>
-      </c>
-      <c r="S44" t="b">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
         <v>7</v>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>premium-panel</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>۴ آبان ۱۴۰۵، ۱۶:۳۲</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="n">
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="n">
         <v>35.678418180103</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="Y41" t="n">
         <v>51.362307036737</v>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>api_exact_pin</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr">
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
-      <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="n">
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="n">
         <v>2160</v>
       </c>
-      <c r="AJ44" t="n">
+      <c r="AJ41" t="n">
         <v>28.8</v>
       </c>
-      <c r="AK44" t="inlineStr">
+      <c r="AK41" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr">
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr">
         <is>
           <t>osm_n5190423570</t>
         </is>
       </c>
-      <c r="AN44" t="n">
+      <c r="AN41" t="n">
         <v>1637</v>
       </c>
-      <c r="AO44" t="inlineStr">
+      <c r="AO41" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP44" t="inlineStr">
+      <c r="AP41" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ44" t="inlineStr"/>
-      <c r="AR44" t="inlineStr">
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr">
         <is>
           <t>مترو و مراکز خرید عالی نورگیر فوقال</t>
         </is>
       </c>
-      <c r="AS44" t="n">
+      <c r="AS41" t="n">
         <v>400000000</v>
       </c>
-      <c r="AT44" t="n">
+      <c r="AT41" t="n">
         <v>10000000</v>
       </c>
-      <c r="AU44" t="inlineStr">
+      <c r="AU41" t="inlineStr">
         <is>
           <t>‏۴۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV44" t="inlineStr">
+      <c r="AV41" t="inlineStr">
         <is>
           <t>‏۱۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AW44" t="inlineStr">
+      <c r="AW41" t="inlineStr">
         <is>
           <t>ودیعه: ۴۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
+      <c r="AX41" t="inlineStr">
         <is>
           <t>اجاره: ۱۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
-      <c r="AZ44" t="inlineStr"/>
-      <c r="BA44" t="inlineStr"/>
-      <c r="BB44" t="inlineStr"/>
-      <c r="BC44" t="inlineStr"/>
-      <c r="BD44" t="inlineStr">
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE44" t="inlineStr"/>
-      <c r="BF44" t="inlineStr">
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr">
         <is>
           <t>2026-11-26T16:32:03.398844</t>
         </is>
       </c>
-      <c r="BG44" t="inlineStr"/>
-      <c r="BH44" t="inlineStr">
+      <c r="BG41" t="inlineStr"/>
+      <c r="BH41" t="inlineStr">
         <is>
           <t>{"osm_n5190423570": 1637, "beryanak": 1774, "osm_n5165422504": 1869, "osm_n5165422503": 2363, "osm_n5183625750": 2456, "osm_n14065977511": 2498, "helal_ahmar": 2535, "osm_n14058146709": 2726, "osm_w1314615868": 2904, "osm_w671794339": 2915, "osm_n14084275564": 3048, "osm_n11417054143": 3111, "osm_w1041344025": 3126, "osm_n14058145512": 3126, "osm_n14075053790": 3380, "osm_n14058145514": 3469, "moniriyeh": 3564, "mahdieh": 3574, "osm_n5186234550": 3577, "osm_n5162910431": 3716, "osm_n11417054161": 3739, "osm_n3635251445": 3829, "osm_n14084275565": 3843, "osm_n5183520307": 4315, "osm_n14058145515": 4408, "osm_n14089610125": 4457, "osm_w1169531671": 4477, "osm_n14058145513": 4515, "teatr_shahr": 4637, "osm_n10746895093": 4750, "osm_n5162855447": 4941, "osm_n4396461099": 4968, "osm_n6737096941": 4981, "osm_n5165462147": 5148, "osm_n5604727197": 5209, "osm_n13380425834": 5240, "osm_n5186262276": 5345, "osm_n5190423568": 5445, "vali_asr": 5466, "osm_n13202066659": 5739, "osm_n13380425818": 5757, "osm_n13230313218": 5782, "saadi": 5851, "osm_n14058409025": 5924, "osm_n14072135584": 5971, "osm_n14071125007": 6094, "osm_n5165462148": 6165, "osm_n8890549263": 6233, "osm_n13279314257": 6236, "osm_n14075284474": 6241, "jahad": 6271, "darvazeh_dowlat": 6304, "osm_n13380425728": 6324, "osm_n14072135585": 6436, "taleghani": 6540, "osm_n14058409026": 6584, "osm_n14059862414": 6772, "osm_n5602579936": 6968, "osm_n14072135586": 7023, "haft_tir": 7088, "osm_n5188341403": 7147, "osm_n5183513583": 7259, "mirza_shirazi": 7417, "osm_n14065945232": 7544, "osm_n13284688255": 7621, "osm_n8243426038": 7652, "osm_n12659430599": 7663, "osm_n10861347776": 7676, "osm_n6390530109": 7796, "osm_n12157511978": 7803, "mofatteh": 7819, "osm_n13426743990": 7998, "osm_n9149513248": 8002, "osm_n14060820580": 8044, "osm_n14071125009": 8133, "shahid_beheshti": 8240, "osm_n6444462277": 8319, "osm_n14075284475": 8465, "osm_n2169732971": 8639, "osm_n14058409027": 8865, "sohrevardi": 8923, "osm_n14064336782": 8940, "osm_n13381123730": 9068, "osm_n14059828792": 9121, "osm_n13380418873": 9191, "osm_n8273593826": 9290, "osm_n3778821747": 9492, "osm_n14075125227": 9636, "osm_n14072135587": 9650, "osm_n660658572": 9735, "osm_n14075284476": 9869, "osm_n14075125225": 9976, "osm_n14058409028": 10234, "osm_n13381123745": 10437, "osm_n5162910430": 10493, "osm_n8907277818": 10750, "osm_n14072135588": 10753, "osm_n14064708968": 10782, "osm_n14075284477": 11010, "osm_n13381123758": 11133, "osm_n6390530105": 11340, "osm_n5162910441": 11474, "osm_n5604726917": 11522, "osm_n14058409029": 11552, "osm_n3778861787": 11555, "osm_n11750922029": 11613, "osm_n14064708967": 11788, "osm_n13381123759": 11958, "osm_n2169380700": 12519, "osm_n14058409030": 12576, "osm_n5162910442": 12618, "osm_n13230283736": 12709, "osm_n14072135590": 13075, "osm_n13817588094": 13488, "osm_n14058409031": 13555, "osm_n11281445852": 13593, "osm_n13381123770": 13601, "osm_n14058409032": 14310, "osm_n13381264373": 14375, "osm_n3778822187": 14445, "osm_n5162855462": 14690, "osm_n5194776019": 14857, "osm_n5163103599": 15211, "osm_n14072135591": 15341, "osm_n13381264374": 15447, "osm_n14061094940": 16327, "osm_n5163103601": 16382, "osm_n8738914819": 17505, "osm_n5163103600": 17634, "osm_n5163103597": 18696, "osm_n5163103598": 19597}</t>
         </is>
       </c>
-      <c r="BI44" t="inlineStr">
+      <c r="BI41" t="inlineStr">
         <is>
           <t>۳ طبقه ۲ واحدی
 ۱ خواب مستر
@@ -10852,216 +10121,216 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>pin is ~2164 m estimated walk (1639 m straight-line) from nearest target station; text mentions target metro osm_n8907277818: مترو و میدان شهرری</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>gaTjTH1c</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaTjTH1c</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>45متر/ بیات(شهرری)/داماک</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>شهرری</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>خ بیات</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>شهرری; ظهیرآباد قدیمی</t>
         </is>
       </c>
-      <c r="I45" t="b">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
         <v>400000000</v>
       </c>
-      <c r="K45" t="n">
+      <c r="K42" t="n">
         <v>11000000</v>
       </c>
-      <c r="L45" t="b">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
+      <c r="L42" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>45</v>
       </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
         <v>1396</v>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q45" t="b">
-        <v>0</v>
-      </c>
-      <c r="R45" t="b">
-        <v>0</v>
-      </c>
-      <c r="S45" t="b">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" t="inlineStr">
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="inlineStr">
         <is>
           <t>premium-panel</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>۲۵ مهر ۱۴۰۵، ۱۲:۳۱</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="n">
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="n">
         <v>35.591002247027</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="Y42" t="n">
         <v>51.43977131839</v>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>api_exact_pin</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr">
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
-      <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="n">
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="n">
         <v>2164</v>
       </c>
-      <c r="AJ45" t="n">
+      <c r="AJ42" t="n">
         <v>28.9</v>
       </c>
-      <c r="AK45" t="inlineStr">
+      <c r="AK42" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr">
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr">
         <is>
           <t>osm_n8907277818</t>
         </is>
       </c>
-      <c r="AN45" t="n">
+      <c r="AN42" t="n">
         <v>1639</v>
       </c>
-      <c r="AO45" t="inlineStr">
+      <c r="AO42" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP45" t="inlineStr">
+      <c r="AP42" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ45" t="inlineStr">
+      <c r="AQ42" t="inlineStr">
         <is>
           <t>osm_n8907277818</t>
         </is>
       </c>
-      <c r="AR45" t="inlineStr">
+      <c r="AR42" t="inlineStr">
         <is>
           <t>مترو و میدان شهرری</t>
         </is>
       </c>
-      <c r="AS45" t="n">
+      <c r="AS42" t="n">
         <v>400000000</v>
       </c>
-      <c r="AT45" t="n">
+      <c r="AT42" t="n">
         <v>11000000</v>
       </c>
-      <c r="AU45" t="inlineStr">
+      <c r="AU42" t="inlineStr">
         <is>
           <t>‏۴۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV45" t="inlineStr">
+      <c r="AV42" t="inlineStr">
         <is>
           <t>‏۱۱,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AW45" t="inlineStr">
+      <c r="AW42" t="inlineStr">
         <is>
           <t>ودیعه: ۴۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
+      <c r="AX42" t="inlineStr">
         <is>
           <t>اجاره: ۱۱,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr"/>
-      <c r="BA45" t="inlineStr"/>
-      <c r="BB45" t="inlineStr"/>
-      <c r="BC45" t="inlineStr"/>
-      <c r="BD45" t="inlineStr">
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE45" t="inlineStr"/>
-      <c r="BF45" t="inlineStr">
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr">
         <is>
           <t>2026-11-17T12:31:06.449723</t>
         </is>
       </c>
-      <c r="BG45" t="inlineStr"/>
-      <c r="BH45" t="inlineStr">
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="inlineStr">
         <is>
           <t>{"osm_n8907277818": 1639, "osm_n13380418873": 2803, "osm_n6390530105": 3797, "osm_n8273593826": 4743, "osm_n5183513583": 4815, "osm_n11281445852": 5028, "osm_n13380425728": 5977, "osm_n6444462277": 6002, "osm_n9149513248": 6774, "osm_n13380425818": 6990, "osm_n5162855462": 7080, "osm_n13380425834": 7738, "osm_n5194776019": 7906, "osm_n12659430599": 8289, "osm_n3635251445": 8512, "osm_n13284688255": 8632, "osm_n14084275565": 8748, "osm_n14059862414": 8755, "osm_n14071125007": 8756, "osm_n6737096941": 8799, "osm_n14059828792": 8808, "osm_n14089610125": 8935, "osm_w1041344025": 8940, "osm_n14084275564": 9093, "osm_n14075125225": 9179, "mahdieh": 9223, "osm_n5162855447": 9373, "osm_n11750922029": 9545, "osm_n5165462147": 9621, "helal_ahmar": 9773, "osm_n4396461099": 9917, "osm_n8243426038": 10201, "osm_n5165462148": 10285, "osm_n13817588094": 10391, "beryanak": 10568, "moniriyeh": 10599, "osm_n5186262276": 10688, "osm_n14058409025": 10889, "osm_n14058145515": 10911, "osm_n6390530109": 11040, "osm_n2169732971": 11167, "osm_n14058409026": 11283, "osm_n14058145514": 11335, "osm_n5190423570": 11402, "osm_n14075125227": 11406, "saadi": 11462, "osm_n5162910430": 11692, "osm_n5188341403": 12011, "osm_n14058146709": 12032, "osm_n5165422504": 12058, "osm_n5162910441": 12131, "darvazeh_dowlat": 12358, "osm_n13426743990": 12399, "osm_n13202066659": 12431, "teatr_shahr": 12650, "osm_n5165422503": 12802, "osm_n5162910431": 12976, "taleghani": 12977, "osm_n14060820580": 13131, "osm_n5162910442": 13138, "osm_n14058409027": 13182, "osm_w671794339": 13438, "osm_w1169531671": 13692, "vali_asr": 13729, "osm_n14071125009": 13863, "haft_tir": 13906, "osm_n5183625750": 13927, "osm_n14075053790": 13978, "osm_n13279314257": 13998, "osm_n14065977511": 14316, "osm_n14058409028": 14336, "osm_n10746895093": 14510, "jahad": 14682, "osm_n11417054143": 14714, "mofatteh": 14877, "osm_w1314615868": 14880, "osm_n14058145512": 14921, "mirza_shirazi": 15371, "osm_n11417054161": 15376, "osm_n14058409029": 15422, "osm_n5186234550": 15492, "shahid_beheshti": 15566, "sohrevardi": 15589, "osm_n3778821747": 15611, "osm_n5190423568": 15797, "osm_n5183520307": 16076, "osm_n14072135588": 16162, "osm_n14058409030": 16317, "osm_n14058145513": 16399, "osm_n14075284474": 16491, "osm_n13381123730": 16641, "osm_n14058409031": 16844, "osm_n14072135584": 16848, "osm_n14058409032": 17004, "osm_n3778861787": 17073, "osm_n5604727197": 17183, "osm_n5163103599": 17244, "osm_n13230313218": 17454, "osm_n8890549263": 17520, "osm_n660658572": 17598, "osm_n5163103601": 17638, "osm_n14072135585": 18090, "osm_n5163103600": 18227, "osm_n12157511978": 18242, "osm_n13381123745": 18467, "osm_n5602579936": 18785, "osm_n13381123758": 18798, "osm_n14072135586": 18903, "osm_n14072135590": 19007, "osm_n13381123759": 19131, "osm_n14075284475": 19293, "osm_n14065945232": 19503, "osm_n10861347776": 19639, "osm_n2169380700": 20205, "osm_n3778822187": 20360, "osm_n14075284476": 20671, "osm_n14064336782": 20913, "osm_n14072135591": 21191, "osm_n13381123770": 21587, "osm_n14072135587": 21620, "osm_n14075284477": 22059, "osm_n14061094940": 22449, "osm_n13381264373": 22512, "osm_n5604726917": 22571, "osm_n14064708968": 22753, "osm_n8738914819": 23655, "osm_n14064708967": 23766, "osm_n13381264374": 23768, "osm_n5163103597": 23810, "osm_n5163103598": 24245, "osm_n13230283736": 24687}</t>
         </is>
       </c>
-      <c r="BI45" t="inlineStr">
+      <c r="BI42" t="inlineStr">
         <is>
           <t>کار خوبه خدا درست کنه........
 آپارتمان نقلی و تمیز برای شما عزیزان 
@@ -11074,216 +10343,216 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>pin is ~2309 m estimated walk (1749 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و اتوبوس و سواری</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>gaDzeQZr</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaDzeQZr</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>مرتضوی ۵۵ متر</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>هاشمی</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>خ مرتضوی</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>هاشمی</t>
         </is>
       </c>
-      <c r="I46" t="b">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>360000000</v>
       </c>
-      <c r="K46" t="n">
+      <c r="K43" t="n">
         <v>15500000</v>
       </c>
-      <c r="L46" t="b">
-        <v>1</v>
-      </c>
-      <c r="M46" t="n">
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
         <v>55</v>
       </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="n">
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
         <v>1385</v>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>3 از 4</t>
         </is>
       </c>
-      <c r="Q46" t="b">
-        <v>0</v>
-      </c>
-      <c r="R46" t="b">
-        <v>0</v>
-      </c>
-      <c r="S46" t="b">
-        <v>1</v>
-      </c>
-      <c r="T46" t="n">
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
+      <c r="R43" t="b">
+        <v>0</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
         <v>3</v>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>personal</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>۱۳ مهر ۱۴۰۵، ۲۱:۵۸</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="n">
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="n">
         <v>35.683196891759</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="Y43" t="n">
         <v>51.360837831994</v>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>api_exact_pin</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr">
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
-      <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="n">
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="n">
         <v>2309</v>
       </c>
-      <c r="AJ46" t="n">
+      <c r="AJ43" t="n">
         <v>30.8</v>
       </c>
-      <c r="AK46" t="inlineStr">
+      <c r="AK43" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr">
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr">
         <is>
           <t>osm_n5190423570</t>
         </is>
       </c>
-      <c r="AN46" t="n">
+      <c r="AN43" t="n">
         <v>1749</v>
       </c>
-      <c r="AO46" t="inlineStr">
+      <c r="AO43" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP46" t="inlineStr">
+      <c r="AP43" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ46" t="inlineStr"/>
-      <c r="AR46" t="inlineStr">
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr">
         <is>
           <t>مترو و اتوبوس و سواری</t>
         </is>
       </c>
-      <c r="AS46" t="n">
+      <c r="AS43" t="n">
         <v>360000000</v>
       </c>
-      <c r="AT46" t="n">
+      <c r="AT43" t="n">
         <v>15500000</v>
       </c>
-      <c r="AU46" t="inlineStr">
+      <c r="AU43" t="inlineStr">
         <is>
           <t>RENT_SLIDER credit.value=360000000</t>
         </is>
       </c>
-      <c r="AV46" t="inlineStr">
+      <c r="AV43" t="inlineStr">
         <is>
           <t>RENT_SLIDER rent.value=15500000</t>
         </is>
       </c>
-      <c r="AW46" t="inlineStr">
+      <c r="AW43" t="inlineStr">
         <is>
           <t>ودیعه: ۳۶۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
+      <c r="AX43" t="inlineStr">
         <is>
           <t>اجاره: ۱۵,۵۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr">
+      <c r="AY43" t="inlineStr">
         <is>
           <t>credit 760000000 / rent 1000000</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr"/>
-      <c r="BA46" t="inlineStr"/>
-      <c r="BB46" t="inlineStr"/>
-      <c r="BC46" t="inlineStr"/>
-      <c r="BD46" t="inlineStr">
+      <c r="AZ43" t="inlineStr"/>
+      <c r="BA43" t="inlineStr"/>
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="inlineStr"/>
+      <c r="BD43" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE46" t="inlineStr"/>
-      <c r="BF46" t="inlineStr">
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="inlineStr">
         <is>
           <t>2026-11-05T21:58:52.818879</t>
         </is>
       </c>
-      <c r="BG46" t="inlineStr"/>
-      <c r="BH46" t="inlineStr">
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr">
         <is>
           <t>{"osm_n5190423570": 1749, "osm_n5165422504": 1762, "osm_n5183625750": 1947, "osm_n14065977511": 1951, "osm_n5165422503": 2080, "beryanak": 2127, "osm_w1314615868": 2393, "osm_w671794339": 2550, "osm_n14058145512": 2579, "osm_n14058146709": 2625, "osm_n11417054143": 2821, "helal_ahmar": 2929, "osm_n14075053790": 2969, "osm_n5186234550": 3138, "osm_n11417054161": 3412, "osm_n5162910431": 3484, "osm_n14058145514": 3485, "osm_n14084275564": 3593, "osm_w1041344025": 3596, "moniriyeh": 3691, "mahdieh": 3911, "osm_n5183520307": 3932, "osm_n14058145513": 3973, "osm_w1169531671": 4190, "osm_n3635251445": 4248, "osm_n10746895093": 4381, "osm_n14084275565": 4388, "osm_n14058145515": 4468, "teatr_shahr": 4487, "osm_n5604727197": 4693, "osm_n14089610125": 4984, "osm_n5190423568": 4992, "osm_n4396461099": 5129, "osm_n5162855447": 5161, "vali_asr": 5228, "osm_n6737096941": 5260, "osm_n13230313218": 5405, "osm_n5186262276": 5421, "osm_n14072135584": 5464, "osm_n13380425834": 5611, "osm_n5165462147": 5632, "osm_n13202066659": 5645, "osm_n8890549263": 5698, "osm_n14075284474": 5781, "saadi": 5854, "osm_n14072135585": 5888, "jahad": 5979, "osm_n14058409025": 5980, "osm_n13279314257": 6007, "osm_n13380425818": 6164, "darvazeh_dowlat": 6231, "osm_n14071125007": 6334, "taleghani": 6419, "osm_n14072135586": 6484, "osm_n5602579936": 6541, "osm_n5165462148": 6609, "osm_n14058409026": 6611, "osm_n13380425728": 6783, "haft_tir": 6905, "osm_n14059862414": 6998, "osm_n14065945232": 7020, "osm_n5188341403": 7123, "mirza_shirazi": 7125, "osm_n10861347776": 7189, "osm_n12157511978": 7310, "mofatteh": 7587, "osm_n5183513583": 7749, "osm_n8243426038": 7771, "osm_n13284688255": 7845, "osm_n6390530109": 7857, "osm_n12659430599": 7909, "osm_n14075284475": 7945, "osm_n14060820580": 7957, "osm_n13426743990": 7964, "shahid_beheshti": 7973, "osm_n14071125009": 7993, "osm_n9149513248": 8334, "osm_n14064336782": 8443, "osm_n6444462277": 8686, "sohrevardi": 8687, "osm_n2169732971": 8704, "osm_n13381123730": 8762, "osm_n14058409027": 8800, "osm_n14072135587": 9157, "osm_n3778821747": 9280, "osm_n14059828792": 9334, "osm_n14075284476": 9345, "osm_n660658572": 9396, "osm_n8273593826": 9697, "osm_n14075125227": 9705, "osm_n13380418873": 9707, "osm_n13381123745": 10075, "osm_n14058409028": 10137, "osm_n14075125225": 10175, "osm_n14064708968": 10287, "osm_n14075284477": 10473, "osm_n14072135588": 10558, "osm_n5162910430": 10563, "osm_n13381123758": 10785, "osm_n5604726917": 11210, "osm_n8907277818": 11276, "osm_n14064708967": 11285, "osm_n3778861787": 11336, "osm_n14058409029": 11436, "osm_n5162910441": 11544, "osm_n13381123759": 11629, "osm_n6390530105": 11763, "osm_n11750922029": 11816, "osm_n2169380700": 12153, "osm_n13230283736": 12203, "osm_n14058409030": 12445, "osm_n5162910442": 12666, "osm_n14072135590": 12807, "osm_n13381123770": 13208, "osm_n14058409031": 13432, "osm_n13817588094": 13690, "osm_n13381264373": 13967, "osm_n11281445852": 14141, "osm_n3778822187": 14161, "osm_n14058409032": 14208, "osm_n13381264374": 15023, "osm_n14072135591": 15052, "osm_n5163103599": 15130, "osm_n5162855462": 15234, "osm_n5194776019": 15396, "osm_n14061094940": 16013, "osm_n5163103601": 16325, "osm_n8738914819": 17181, "osm_n5163103600": 17595, "osm_n5163103597": 18418, "osm_n5163103598": 19336}</t>
         </is>
       </c>
-      <c r="BI46" t="inlineStr">
+      <c r="BI43" t="inlineStr">
         <is>
           <t>بهترین موقعیت مکانی به مترو و اتوبوس و سواری 
 بر خیابان اصلی
@@ -11302,218 +10571,218 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>pin is ~2451 m estimated walk (1857 m straight-line) from nearest target station; text mentions target metro osm_n13381123759,osm_n14084275565: مترو شهرک شریعتی</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>ga-SE8m9</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>https://divar.ir/v/ga-SE8m9</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>اجاره واحد نقلی و شیک با قیمت باورنکردنی</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>شهرک شریعتی</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>خ صمدی</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>شهرک شریعتی</t>
         </is>
       </c>
-      <c r="I47" t="b">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
         <v>200000000</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K44" t="n">
         <v>14000000</v>
       </c>
-      <c r="L47" t="b">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
+      <c r="L44" t="b">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>55</v>
       </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="n">
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
         <v>1390</v>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q47" t="b">
-        <v>0</v>
-      </c>
-      <c r="R47" t="b">
-        <v>0</v>
-      </c>
-      <c r="S47" t="b">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
+      <c r="R44" t="b">
+        <v>0</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
         <v>10</v>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>personal</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>۹ مهر ۱۴۰۵، ۱۵:۰۳</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="n">
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="n">
         <v>35.63064752797965</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="Y44" t="n">
         <v>51.38046095550556</v>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>FUZZY</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>APPROXIMATE</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>api_approximate</t>
         </is>
       </c>
-      <c r="AC47" t="n">
+      <c r="AC44" t="n">
         <v>500</v>
       </c>
-      <c r="AD47" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
         </is>
       </c>
-      <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="n">
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="n">
         <v>2451</v>
       </c>
-      <c r="AJ47" t="n">
+      <c r="AJ44" t="n">
         <v>32.7</v>
       </c>
-      <c r="AK47" t="inlineStr">
+      <c r="AK44" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr">
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr">
         <is>
           <t>osm_n14084275565</t>
         </is>
       </c>
-      <c r="AN47" t="n">
+      <c r="AN44" t="n">
         <v>1857</v>
       </c>
-      <c r="AO47" t="inlineStr">
+      <c r="AO44" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP47" t="inlineStr">
+      <c r="AP44" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ47" t="inlineStr">
+      <c r="AQ44" t="inlineStr">
         <is>
           <t>osm_n13381123759,osm_n14084275565</t>
         </is>
       </c>
-      <c r="AR47" t="inlineStr">
+      <c r="AR44" t="inlineStr">
         <is>
           <t>مترو شهرک شریعتی</t>
         </is>
       </c>
-      <c r="AS47" t="n">
+      <c r="AS44" t="n">
         <v>200000000</v>
       </c>
-      <c r="AT47" t="n">
+      <c r="AT44" t="n">
         <v>14000000</v>
       </c>
-      <c r="AU47" t="inlineStr">
+      <c r="AU44" t="inlineStr">
         <is>
           <t>‏۲۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV47" t="inlineStr">
+      <c r="AV44" t="inlineStr">
         <is>
           <t>‏۱۴,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AW47" t="inlineStr">
+      <c r="AW44" t="inlineStr">
         <is>
           <t>ودیعه: ۲۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
+      <c r="AX44" t="inlineStr">
         <is>
           <t>اجاره: ۱۴,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr"/>
-      <c r="BA47" t="inlineStr"/>
-      <c r="BB47" t="inlineStr"/>
-      <c r="BC47" t="inlineStr"/>
-      <c r="BD47" t="inlineStr">
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
+      <c r="BA44" t="inlineStr"/>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="inlineStr"/>
+      <c r="BD44" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE47" t="inlineStr"/>
-      <c r="BF47" t="inlineStr">
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="inlineStr">
         <is>
           <t>2026-11-01T15:03:21.557936</t>
         </is>
       </c>
-      <c r="BG47" t="inlineStr"/>
-      <c r="BH47" t="inlineStr">
+      <c r="BG44" t="inlineStr"/>
+      <c r="BH44" t="inlineStr">
         <is>
           <t>{"osm_n14084275565": 1857, "osm_n14089610125": 2044, "osm_n14084275564": 2517, "osm_n5165462147": 3022, "osm_n5183513583": 3187, "osm_w1041344025": 3267, "osm_n13380425728": 3299, "osm_n3635251445": 3568, "osm_n13380425818": 3943, "osm_n5165462148": 4101, "helal_ahmar": 4171, "osm_n13380418873": 4204, "osm_n13380425834": 4264, "mahdieh": 4406, "beryanak": 4719, "osm_n6737096941": 5217, "osm_n8907277818": 5484, "osm_n5190423570": 5637, "osm_n5162855447": 5747, "moniriyeh": 5932, "osm_n6444462277": 6006, "osm_n14071125007": 6125, "osm_n8273593826": 6168, "osm_n9149513248": 6255, "osm_n4396461099": 6257, "osm_n5165422504": 6351, "osm_n14058145514": 6534, "osm_n14059862414": 6670, "osm_n14058146709": 6728, "osm_n14058145515": 6728, "osm_n12659430599": 7042, "osm_n5186262276": 7140, "osm_n5165422503": 7149, "osm_n13284688255": 7248, "osm_n14058409025": 7659, "osm_n6390530105": 7677, "osm_w671794339": 7837, "osm_n5183625750": 7886, "osm_n11417054143": 7913, "osm_n5162910431": 7917, "saadi": 8023, "osm_n11281445852": 8046, "osm_n14065977511": 8053, "teatr_shahr": 8165, "osm_n8243426038": 8326, "osm_n14058409026": 8350, "osm_w1314615868": 8388, "osm_n14075053790": 8398, "osm_n14059828792": 8497, "osm_n11417054161": 8563, "osm_n13202066659": 8621, "osm_n14058145512": 8682, "osm_w1169531671": 8774, "osm_n5186234550": 8821, "darvazeh_dowlat": 8896, "osm_n6390530109": 8960, "osm_n5188341403": 9171, "osm_n5162855462": 9264, "osm_n5183520307": 9291, "vali_asr": 9312, "osm_n14075125225": 9331, "osm_n10746895093": 9410, "taleghani": 9428, "osm_n5194776019": 9537, "osm_n2169732971": 9582, "osm_n13279314257": 9889, "osm_n13426743990": 9925, "osm_n14058145513": 10065, "haft_tir": 10303, "jahad": 10313, "osm_n14075125227": 10363, "osm_n14060820580": 10389, "osm_n5190423568": 10480, "osm_n13230313218": 10609, "osm_n5604727197": 10670, "osm_n11750922029": 10673, "osm_n14071125009": 10869, "osm_n14058409027": 10904, "osm_n5162910430": 11071, "osm_n14075284474": 11268, "mofatteh": 11271, "osm_n14072135584": 11272, "mirza_shirazi": 11325, "osm_n8890549263": 11694, "shahid_beheshti": 11886, "osm_n5162910441": 11930, "osm_n5602579936": 11982, "osm_n14072135585": 11988, "sohrevardi": 12281, "osm_n13817588094": 12354, "osm_n14058409028": 12355, "osm_n14072135586": 12562, "osm_n3778821747": 12614, "osm_n13381123730": 12920, "osm_n10861347776": 12970, "osm_n12157511978": 12977, "osm_n14065945232": 13018, "osm_n5162910442": 13166, "osm_n14072135588": 13624, "osm_n14058409029": 13702, "osm_n660658572": 13784, "osm_n14075284475": 13808, "osm_n14064336782": 14266, "osm_n3778861787": 14552, "osm_n13381123745": 14610, "osm_n14058409030": 14759, "osm_n14072135587": 14951, "osm_n13381123758": 15167, "osm_n14075284476": 15226, "osm_n14058409031": 15595, "osm_n5604726917": 15632, "osm_n13381123759": 15800, "osm_n14064708968": 16081, "osm_n14058409032": 16115, "osm_n14072135590": 16381, "osm_n14075284477": 16458, "osm_n2169380700": 16631, "osm_n5163103599": 16762, "osm_n14064708967": 17125, "osm_n5163103601": 17640, "osm_n3778822187": 17816, "osm_n13381123770": 17893, "osm_n13230283736": 18054, "osm_n5163103600": 18655, "osm_n14072135591": 18724, "osm_n13381264373": 18759, "osm_n14061094940": 19875, "osm_n13381264374": 19940, "osm_n8738914819": 21108, "osm_n5163103597": 21873, "osm_n5163103598": 22593}</t>
         </is>
       </c>
-      <c r="BI47" t="inlineStr">
+      <c r="BI44" t="inlineStr">
         <is>
           <t>یک واحد آپارتمان نقلی و تمیز واقع در شهرک شریعتی 
 خوش نقشه
@@ -11527,427 +10796,427 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>pin is ~2502 m estimated walk (1896 m straight-line) from nearest target station; text mentions target metro osm_n8907277818: مترو و میدان شهرری و مرکز خرید و</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>gaP78RSH</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaP78RSH</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>آپارتمان نقلی  ۴۵ متری</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>شهرری</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>خ یوسفی نژاد</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>شهرری; ظهیرآباد قدیمی</t>
         </is>
       </c>
-      <c r="I48" t="b">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
         <v>500000000</v>
       </c>
-      <c r="K48" t="n">
+      <c r="K45" t="n">
         <v>8000000</v>
       </c>
-      <c r="L48" t="b">
-        <v>1</v>
-      </c>
-      <c r="M48" t="n">
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
         <v>45</v>
       </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" t="n">
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
         <v>1396</v>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>3 از 3</t>
         </is>
       </c>
-      <c r="Q48" t="b">
-        <v>0</v>
-      </c>
-      <c r="R48" t="b">
-        <v>0</v>
-      </c>
-      <c r="S48" t="b">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
         <v>2</v>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>personal</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>۲۲ مهر ۱۴۰۵، ۲۲:۱۷</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="n">
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="n">
         <v>35.589479654655</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="Y45" t="n">
         <v>51.442158251762</v>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>api_exact_pin</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr"/>
-      <c r="AD48" t="inlineStr">
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
-      <c r="AE48" t="inlineStr"/>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="n">
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="n">
         <v>2502</v>
       </c>
-      <c r="AJ48" t="n">
+      <c r="AJ45" t="n">
         <v>33.4</v>
       </c>
-      <c r="AK48" t="inlineStr">
+      <c r="AK45" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="inlineStr">
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr">
         <is>
           <t>osm_n8907277818</t>
         </is>
       </c>
-      <c r="AN48" t="n">
+      <c r="AN45" t="n">
         <v>1896</v>
       </c>
-      <c r="AO48" t="inlineStr">
+      <c r="AO45" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP48" t="inlineStr">
+      <c r="AP45" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ48" t="inlineStr">
+      <c r="AQ45" t="inlineStr">
         <is>
           <t>osm_n8907277818</t>
         </is>
       </c>
-      <c r="AR48" t="inlineStr">
+      <c r="AR45" t="inlineStr">
         <is>
           <t>مترو و میدان شهرری و مرکز خرید و</t>
         </is>
       </c>
-      <c r="AS48" t="n">
+      <c r="AS45" t="n">
         <v>500000000</v>
       </c>
-      <c r="AT48" t="n">
+      <c r="AT45" t="n">
         <v>8000000</v>
       </c>
-      <c r="AU48" t="inlineStr">
+      <c r="AU45" t="inlineStr">
         <is>
           <t>RENT_SLIDER credit.value=500000000</t>
         </is>
       </c>
-      <c r="AV48" t="inlineStr">
+      <c r="AV45" t="inlineStr">
         <is>
           <t>RENT_SLIDER rent.value=8000000</t>
         </is>
       </c>
-      <c r="AW48" t="inlineStr">
+      <c r="AW45" t="inlineStr">
         <is>
           <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
+      <c r="AX45" t="inlineStr">
         <is>
           <t>اجاره: ۸,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr">
+      <c r="AY45" t="inlineStr">
         <is>
           <t>credit 400000000 / rent 11000000</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr"/>
-      <c r="BA48" t="inlineStr"/>
-      <c r="BB48" t="inlineStr"/>
-      <c r="BC48" t="inlineStr"/>
-      <c r="BD48" t="inlineStr">
+      <c r="AZ45" t="inlineStr"/>
+      <c r="BA45" t="inlineStr"/>
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="inlineStr"/>
+      <c r="BD45" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE48" t="inlineStr"/>
-      <c r="BF48" t="inlineStr">
+      <c r="BE45" t="inlineStr"/>
+      <c r="BF45" t="inlineStr">
         <is>
           <t>2026-11-14T22:17:40.758013</t>
         </is>
       </c>
-      <c r="BG48" t="inlineStr"/>
-      <c r="BH48" t="inlineStr">
+      <c r="BG45" t="inlineStr"/>
+      <c r="BH45" t="inlineStr">
         <is>
           <t>{"osm_n8907277818": 1896, "osm_n13380418873": 3073, "osm_n6390530105": 3820, "osm_n8273593826": 4879, "osm_n5183513583": 5065, "osm_n11281445852": 5076, "osm_n6444462277": 6160, "osm_n13380425728": 6217, "osm_n9149513248": 6933, "osm_n5162855462": 7127, "osm_n13380425818": 7218, "osm_n13380425834": 7965, "osm_n5194776019": 7966, "osm_n12659430599": 8447, "osm_n3635251445": 8761, "osm_n13284688255": 8790, "osm_n14059828792": 8926, "osm_n14059862414": 8934, "osm_n14071125007": 8950, "osm_n6737096941": 9018, "osm_n14084275565": 9021, "osm_w1041344025": 9198, "osm_n14089610125": 9209, "osm_n14075125225": 9274, "osm_n14084275564": 9363, "mahdieh": 9464, "osm_n5162855447": 9587, "osm_n11750922029": 9595, "osm_n5165462147": 9893, "helal_ahmar": 10026, "osm_n4396461099": 10128, "osm_n8243426038": 10359, "osm_n13817588094": 10395, "osm_n5165462148": 10550, "beryanak": 10824, "moniriyeh": 10831, "osm_n5186262276": 10892, "osm_n14058409025": 11082, "osm_n14058145515": 11129, "osm_n6390530109": 11198, "osm_n2169732971": 11307, "osm_n14058409026": 11465, "osm_n14075125227": 11525, "osm_n14058145514": 11566, "osm_n5190423570": 11654, "saadi": 11658, "osm_n5162910430": 11794, "osm_n5188341403": 12186, "osm_n5162910441": 12214, "osm_n14058146709": 12272, "osm_n5165422504": 12307, "darvazeh_dowlat": 12550, "osm_n13426743990": 12561, "osm_n13202066659": 12632, "teatr_shahr": 12868, "osm_n5165422503": 13049, "taleghani": 13168, "osm_n5162910442": 13205, "osm_n5162910431": 13208, "osm_n14060820580": 13297, "osm_n14058409027": 13333, "osm_w671794339": 13682, "osm_w1169531671": 13919, "vali_asr": 13942, "osm_n14071125009": 14034, "haft_tir": 14095, "osm_n5183625750": 14180, "osm_n13279314257": 14201, "osm_n14075053790": 14221, "osm_n14058409028": 14472, "osm_n14065977511": 14575, "osm_n10746895093": 14739, "jahad": 14890, "osm_n11417054143": 14984, "mofatteh": 15063, "osm_w1314615868": 15143, "osm_n14058145512": 15178, "osm_n14058409029": 15544, "mirza_shirazi": 15568, "osm_n11417054161": 15646, "shahid_beheshti": 15752, "osm_n5186234550": 15759, "sohrevardi": 15764, "osm_n3778821747": 15776, "osm_n5190423568": 16029, "osm_n14072135588": 16309, "osm_n5183520307": 16345, "osm_n14058409030": 16430, "osm_n14058145513": 16658, "osm_n14075284474": 16720, "osm_n13381123730": 16825, "osm_n14058409031": 16944, "osm_n14072135584": 17086, "osm_n14058409032": 17090, "osm_n3778861787": 17217, "osm_n5163103599": 17314, "osm_n5604727197": 17445, "osm_n5163103601": 17688, "osm_n13230313218": 17725, "osm_n8890549263": 17764, "osm_n660658572": 17783, "osm_n5163103600": 18258, "osm_n14072135585": 18341, "osm_n12157511978": 18469, "osm_n13381123745": 18651, "osm_n13381123758": 18974, "osm_n5602579936": 19055, "osm_n14072135590": 19150, "osm_n14072135586": 19160, "osm_n13381123759": 19297, "osm_n14075284475": 19525, "osm_n14065945232": 19764, "osm_n10861347776": 19905, "osm_n2169380700": 20377, "osm_n3778822187": 20497, "osm_n14075284476": 20901, "osm_n14064336782": 21178, "osm_n14072135591": 21324, "osm_n13381123770": 21760, "osm_n14072135587": 21885, "osm_n14075284477": 22293, "osm_n14061094940": 22583, "osm_n13381264373": 22686, "osm_n5604726917": 22846, "osm_n14064708968": 23018, "osm_n8738914819": 23787, "osm_n5163103597": 23919, "osm_n13381264374": 23943, "osm_n14064708967": 24030, "osm_n5163103598": 24343, "osm_n13230283736": 24951}</t>
         </is>
       </c>
-      <c r="BI48" t="inlineStr">
+      <c r="BI45" t="inlineStr">
         <is>
           <t>آپارتمان نقلی در بهترین لوکیشن شهرری با دسترسی آسان به مترو و میدان شهرری و مرکز خرید و...</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>pin is ~2554 m estimated walk (1935 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRT️✅</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>gaAv6nsI</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaAv6nsI</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>اجاره ۵۵متر/انباری /بالکن /pموتور/ تک واحدی</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>سلیمانی</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
         <is>
           <t>سلیمانی; شبیری قدیمی</t>
         </is>
       </c>
-      <c r="I49" t="b">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
         <v>500000000</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="b">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>60</v>
       </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" t="n">
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
         <v>1389</v>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q49" t="b">
-        <v>0</v>
-      </c>
-      <c r="R49" t="b">
-        <v>1</v>
-      </c>
-      <c r="S49" t="b">
-        <v>1</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1</v>
-      </c>
-      <c r="U49" t="inlineStr">
+      <c r="Q46" t="b">
+        <v>0</v>
+      </c>
+      <c r="R46" t="b">
+        <v>1</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="inlineStr">
         <is>
           <t>premium-panel</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>۱۱ مهر ۱۴۰۵، ۱۰:۵۳</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="n">
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="n">
         <v>35.671277607959</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Y46" t="n">
         <v>51.359515433265</v>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>api_exact_pin</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr">
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
-      <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="n">
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="n">
         <v>2554</v>
       </c>
-      <c r="AJ49" t="n">
+      <c r="AJ46" t="n">
         <v>34.1</v>
       </c>
-      <c r="AK49" t="inlineStr">
+      <c r="AK46" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr">
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr">
         <is>
           <t>beryanak</t>
         </is>
       </c>
-      <c r="AN49" t="n">
+      <c r="AN46" t="n">
         <v>1935</v>
       </c>
-      <c r="AO49" t="inlineStr">
+      <c r="AO46" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP49" t="inlineStr">
+      <c r="AP46" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ49" t="inlineStr"/>
-      <c r="AR49" t="inlineStr">
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr">
         <is>
           <t>مترو و BRT️✅</t>
         </is>
       </c>
-      <c r="AS49" t="n">
+      <c r="AS46" t="n">
         <v>500000000</v>
       </c>
-      <c r="AT49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
         <is>
           <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV49" t="inlineStr">
+      <c r="AV46" t="inlineStr">
         <is>
           <t>رایگان</t>
         </is>
       </c>
-      <c r="AW49" t="inlineStr">
+      <c r="AW46" t="inlineStr">
         <is>
           <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
+      <c r="AX46" t="inlineStr">
         <is>
           <t>رهن کامل</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr"/>
-      <c r="BA49" t="inlineStr"/>
-      <c r="BB49" t="inlineStr"/>
-      <c r="BC49" t="inlineStr"/>
-      <c r="BD49" t="inlineStr">
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE49" t="inlineStr"/>
-      <c r="BF49" t="inlineStr">
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr">
         <is>
           <t>2026-11-03T10:53:41.236539</t>
         </is>
       </c>
-      <c r="BG49" t="inlineStr"/>
-      <c r="BH49" t="inlineStr">
+      <c r="BG46" t="inlineStr"/>
+      <c r="BH46" t="inlineStr">
         <is>
           <t>{"beryanak": 1935, "osm_n5190423570": 2167, "osm_n14084275564": 2436, "helal_ahmar": 2523, "osm_n5165422504": 2573, "osm_w1041344025": 2876, "osm_n14084275565": 3115, "osm_n5165422503": 3153, "osm_n14065977511": 3243, "osm_n5183625750": 3274, "osm_n11417054143": 3287, "osm_n14058146709": 3391, "osm_w1314615868": 3489, "mahdieh": 3629, "osm_n14089610125": 3658, "osm_n3635251445": 3692, "osm_w671794339": 3733, "osm_n14058145512": 3863, "osm_n11417054161": 3947, "moniriyeh": 3959, "osm_n5186234550": 3992, "osm_n14058145514": 3999, "osm_n14075053790": 4209, "osm_n5165462147": 4316, "osm_n5162910431": 4460, "osm_n5183520307": 4605, "osm_n14058145515": 4865, "osm_n6737096941": 5105, "osm_n5162855447": 5163, "osm_n13380425834": 5178, "osm_n14058145513": 5184, "osm_w1169531671": 5251, "osm_n4396461099": 5278, "teatr_shahr": 5309, "osm_n5165462148": 5337, "osm_n10746895093": 5563, "osm_n13380425818": 5607, "osm_n5186262276": 5766, "osm_n5604727197": 5777, "osm_n13230313218": 6035, "osm_n13380425728": 6036, "vali_asr": 6201, "osm_n14071125007": 6265, "osm_n5190423568": 6278, "osm_n13202066659": 6348, "saadi": 6356, "osm_n14058409025": 6363, "osm_n14072135584": 6792, "osm_n5183513583": 6871, "darvazeh_dowlat": 6887, "osm_n14059862414": 6957, "osm_n13279314257": 6960, "osm_n8890549263": 7022, "jahad": 7040, "osm_n14058409026": 7052, "osm_n14075284474": 7074, "osm_n14072135585": 7164, "taleghani": 7171, "osm_n5602579936": 7309, "osm_n14072135586": 7669, "osm_n5188341403": 7670, "haft_tir": 7772, "osm_n13284688255": 7799, "osm_n12659430599": 7805, "osm_n9149513248": 7987, "osm_n8243426038": 7989, "osm_n14065945232": 8124, "osm_n10861347776": 8147, "mirza_shirazi": 8184, "osm_n6390530109": 8211, "osm_n6444462277": 8229, "osm_n13426743990": 8527, "mofatteh": 8540, "osm_n14060820580": 8631, "osm_n12157511978": 8631, "osm_n13380418873": 8701, "osm_n14071125009": 8772, "shahid_beheshti": 8986, "osm_n2169732971": 9042, "osm_n8273593826": 9107, "osm_n14075284475": 9275, "osm_n14059828792": 9307, "osm_n14058409027": 9425, "osm_n14064336782": 9431, "sohrevardi": 9645, "osm_n13381123730": 9840, "osm_n14075125227": 10029, "osm_n14072135587": 10131, "osm_n14075125225": 10179, "osm_n3778821747": 10193, "osm_n8907277818": 10210, "osm_n660658572": 10528, "osm_n14075284476": 10675, "osm_n14058409028": 10823, "osm_n5162910430": 10880, "osm_n6390530105": 11109, "osm_n13381123745": 11241, "osm_n14064708968": 11264, "osm_n14072135588": 11436, "osm_n5604726917": 11614, "osm_n14075284477": 11793, "osm_n11750922029": 11802, "osm_n5162910441": 11858, "osm_n13381123758": 11929, "osm_n14058409029": 12159, "osm_n3778861787": 12257, "osm_n14064708967": 12291, "osm_n13381123759": 12741, "osm_n11281445852": 12894, "osm_n5162910442": 13029, "osm_n14058409030": 13194, "osm_n13230283736": 13217, "osm_n2169380700": 13323, "osm_n13817588094": 13673, "osm_n14072135590": 13816, "osm_n5162855462": 13939, "osm_n5194776019": 14085, "osm_n14058409031": 14163, "osm_n13381123770": 14418, "osm_n14058409032": 14895, "osm_n3778822187": 15196, "osm_n13381264373": 15197, "osm_n5163103599": 15771, "osm_n14072135591": 16097, "osm_n13381264374": 16274, "osm_n5163103601": 16913, "osm_n14061094940": 17098, "osm_n5163103600": 18142, "osm_n8738914819": 18283, "osm_n5163103597": 19441, "osm_n5163103598": 20328}</t>
         </is>
       </c>
-      <c r="BI49" t="inlineStr">
+      <c r="BI46" t="inlineStr">
         <is>
           <t>✅مشاورین آلفا ✅
         ✅آپارتمان۵۵متر  خوش نقشه تخلیه️✅
@@ -11981,429 +11250,429 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>pin is ~2982 m estimated walk (2259 m straight-line) from nearest target station; text mentions an unnamed metro: مترو اتوبوس نانوایی هایپر و غیره</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>gaibuU9i</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaibuU9i</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>اجاره آپارتمان ۲۵ متری</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>اوقاف</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>کنارگذر مظفری نیا</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>اوقاف</t>
         </is>
       </c>
-      <c r="I50" t="b">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
         <v>100000000</v>
       </c>
-      <c r="K50" t="n">
+      <c r="K47" t="n">
         <v>15000000</v>
       </c>
-      <c r="L50" t="b">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>25</v>
       </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="n">
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
         <v>1385</v>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q50" t="b">
-        <v>0</v>
-      </c>
-      <c r="R50" t="b">
-        <v>0</v>
-      </c>
-      <c r="S50" t="b">
-        <v>1</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1</v>
-      </c>
-      <c r="U50" t="inlineStr">
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
+      <c r="R47" t="b">
+        <v>0</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="inlineStr">
         <is>
           <t>personal</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>۷ آبان ۱۴۰۵، ۰۹:۵۳</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="n">
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="n">
         <v>35.753025904894</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="Y47" t="n">
         <v>51.520065764008</v>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>api_exact_pin</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr"/>
-      <c r="AD50" t="inlineStr">
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
-      <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="n">
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="n">
         <v>2982</v>
       </c>
-      <c r="AJ50" t="n">
+      <c r="AJ47" t="n">
         <v>39.8</v>
       </c>
-      <c r="AK50" t="inlineStr">
+      <c r="AK47" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="inlineStr">
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr">
         <is>
           <t>osm_n5163103599</t>
         </is>
       </c>
-      <c r="AN50" t="n">
+      <c r="AN47" t="n">
         <v>2259</v>
       </c>
-      <c r="AO50" t="inlineStr">
+      <c r="AO47" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP50" t="inlineStr">
+      <c r="AP47" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ50" t="inlineStr"/>
-      <c r="AR50" t="inlineStr">
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr">
         <is>
           <t>مترو اتوبوس نانوایی هایپر و غیره</t>
         </is>
       </c>
-      <c r="AS50" t="n">
+      <c r="AS47" t="n">
         <v>100000000</v>
       </c>
-      <c r="AT50" t="n">
+      <c r="AT47" t="n">
         <v>15000000</v>
       </c>
-      <c r="AU50" t="inlineStr">
+      <c r="AU47" t="inlineStr">
         <is>
           <t>‏۱۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV50" t="inlineStr">
+      <c r="AV47" t="inlineStr">
         <is>
           <t>‏۱۵,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AW50" t="inlineStr">
+      <c r="AW47" t="inlineStr">
         <is>
           <t>ودیعه: ۱۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
+      <c r="AX47" t="inlineStr">
         <is>
           <t>اجاره: ۱۵,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr"/>
-      <c r="BA50" t="inlineStr"/>
-      <c r="BB50" t="inlineStr"/>
-      <c r="BC50" t="inlineStr"/>
-      <c r="BD50" t="inlineStr">
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
+      <c r="BA47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE50" t="inlineStr"/>
-      <c r="BF50" t="inlineStr">
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="inlineStr">
         <is>
           <t>2026-11-29T09:53:31.972577</t>
         </is>
       </c>
-      <c r="BG50" t="inlineStr"/>
-      <c r="BH50" t="inlineStr">
+      <c r="BG47" t="inlineStr"/>
+      <c r="BH47" t="inlineStr">
         <is>
           <t>{"osm_n5163103599": 2259, "osm_n14058409032": 2474, "osm_n5163103601": 2682, "osm_n14058409031": 2982, "osm_n5163103600": 3548, "osm_n14058409030": 3919, "osm_n14072135591": 4713, "osm_n3778822187": 4731, "osm_n14072135590": 4963, "osm_n14058409029": 4970, "osm_n5163103597": 5093, "osm_n5163103598": 5098, "osm_n3778861787": 5337, "osm_n14061094940": 5534, "osm_n14072135588": 5896, "osm_n8738914819": 6182, "osm_n5162910442": 6321, "osm_n14058409028": 6331, "osm_n13381123759": 6946, "osm_n3778821747": 7209, "osm_n5162910441": 7294, "osm_n2169380700": 7713, "osm_n14058409027": 7786, "osm_n13381123758": 7821, "osm_n5162910430": 7842, "sohrevardi": 7901, "osm_n14071125009": 8350, "osm_n14075125227": 8353, "osm_n13381123770": 8381, "osm_n13381123730": 8458, "osm_n660658572": 8474, "osm_n13381123745": 8490, "osm_n14060820580": 8502, "osm_n13426743990": 8754, "shahid_beheshti": 8754, "osm_n13381264373": 8887, "mofatteh": 8916, "osm_n2169732971": 9000, "haft_tir": 9450, "osm_n5188341403": 9589, "osm_n6390530109": 9591, "osm_n13381264374": 9684, "mirza_shirazi": 9689, "osm_n13817588094": 9871, "taleghani": 9944, "osm_n11750922029": 9996, "darvazeh_dowlat": 10237, "osm_n8243426038": 10250, "osm_n14075125225": 10272, "osm_n14058409026": 10348, "osm_n13279314257": 10421, "jahad": 10702, "osm_n13202066659": 10762, "osm_n14059828792": 10787, "saadi": 10889, "osm_n14058409025": 11076, "vali_asr": 11199, "osm_n13284688255": 11549, "osm_n5186262276": 11667, "osm_n12659430599": 11838, "teatr_shahr": 11854, "osm_n14059862414": 11949, "osm_w1169531671": 12316, "osm_n14058145515": 12399, "osm_n14071125007": 12436, "osm_n4396461099": 12455, "osm_n10746895093": 12517, "osm_n14075284474": 12587, "osm_n12157511978": 12784, "osm_n5162910431": 12883, "osm_n5162855447": 12887, "osm_n5190423568": 12908, "osm_n14058145514": 13134, "osm_n9149513248": 13158, "moniriyeh": 13350, "osm_n6737096941": 13361, "osm_n14072135584": 13701, "osm_n14075284475": 13725, "osm_n14058146709": 13757, "osm_n6444462277": 13827, "osm_n14075053790": 13871, "osm_n14075284476": 13945, "osm_w671794339": 14025, "osm_n13380425834": 14294, "osm_n5165422503": 14297, "mahdieh": 14488, "osm_n5165422504": 14617, "osm_n8890549263": 14640, "osm_n13380425818": 14724, "osm_n8273593826": 14819, "osm_n5190423570": 14943, "osm_n14075284477": 15064, "osm_n3635251445": 15171, "osm_n5183625750": 15191, "helal_ahmar": 15296, "beryanak": 15397, "osm_n13380425728": 15691, "osm_n6390530105": 15755, "osm_n14072135585": 15835, "osm_w1041344025": 15842, "osm_n14058145512": 15873, "osm_n14065977511": 15925, "osm_n14058145513": 16454, "osm_n5183513583": 16645, "osm_w1314615868": 16886, "osm_n14072135586": 17158, "osm_n14084275564": 17312, "osm_n5604727197": 17493, "osm_n5186234550": 17904, "osm_n14065945232": 18148, "osm_n14084275565": 18266, "osm_n13380418873": 18312, "osm_n11417054143": 18537, "osm_n11417054161": 18817, "osm_n5183520307": 18826, "osm_n14089610125": 19277, "osm_n10861347776": 19370, "osm_n8907277818": 19672, "osm_n14064336782": 19821, "osm_n13230313218": 19886, "osm_n5602579936": 20070, "osm_n14072135587": 20346, "osm_n5165462147": 20480, "osm_n14064708968": 20991, "osm_n14064708967": 21338, "osm_n5165462148": 21757, "osm_n13230283736": 21838, "osm_n11281445852": 24081, "osm_n5604726917": 25250, "osm_n5162855462": 26017, "osm_n5194776019": 26667}</t>
         </is>
       </c>
-      <c r="BI50" t="inlineStr">
+      <c r="BI47" t="inlineStr">
         <is>
           <t>آپارتمان نقلی سوئیت ۲۵ متری نبش خیابان سراج بعد از پل طرف استقلال پنجره بزرگ موقعیت عالی به مترو اتوبوس نانوایی هایپر و غیره</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>pin is ~3032 m estimated walk (2297 m straight-line) from nearest target station; text mentions an unnamed metro: ایستگاه بی آرتی و مترو ➡️</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>gafv0lmB</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gafv0lmB</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>بازرگان  بدون پارکینگ</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>شهرک ولیعصر شمالی</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>خ هداوندی میر</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>شهرک ولیعصر شمالی</t>
         </is>
       </c>
-      <c r="I51" t="b">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
         <v>300000000</v>
       </c>
-      <c r="K51" t="n">
+      <c r="K48" t="n">
         <v>15000000</v>
       </c>
-      <c r="L51" t="b">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
         <v>65</v>
       </c>
-      <c r="N51" t="n">
-        <v>1</v>
-      </c>
-      <c r="O51" t="n">
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
         <v>1393</v>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q51" t="b">
-        <v>1</v>
-      </c>
-      <c r="R51" t="b">
-        <v>0</v>
-      </c>
-      <c r="S51" t="b">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
+      <c r="Q48" t="b">
+        <v>1</v>
+      </c>
+      <c r="R48" t="b">
+        <v>0</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
         <v>7</v>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>personal</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>۴ آبان ۱۴۰۵، ۱۶:۲۶</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>۷ آبان ۱۴۰۵، ۱۵:۵۳</t>
         </is>
       </c>
-      <c r="X51" t="n">
+      <c r="X48" t="n">
         <v>35.65320163424493</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="Y48" t="n">
         <v>51.33861650961857</v>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>FUZZY</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>APPROXIMATE</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>api_approximate</t>
         </is>
       </c>
-      <c r="AC51" t="n">
+      <c r="AC48" t="n">
         <v>500</v>
       </c>
-      <c r="AD51" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
         </is>
       </c>
-      <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="n">
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="n">
         <v>3032</v>
       </c>
-      <c r="AJ51" t="n">
+      <c r="AJ48" t="n">
         <v>40.4</v>
       </c>
-      <c r="AK51" t="inlineStr">
+      <c r="AK48" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr">
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr">
         <is>
           <t>osm_n5165462147</t>
         </is>
       </c>
-      <c r="AN51" t="n">
+      <c r="AN48" t="n">
         <v>2297</v>
       </c>
-      <c r="AO51" t="inlineStr">
+      <c r="AO48" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP51" t="inlineStr">
+      <c r="AP48" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="inlineStr">
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr">
         <is>
           <t>ایستگاه بی آرتی و مترو ➡️</t>
         </is>
       </c>
-      <c r="AS51" t="n">
+      <c r="AS48" t="n">
         <v>300000000</v>
       </c>
-      <c r="AT51" t="n">
+      <c r="AT48" t="n">
         <v>15000000</v>
       </c>
-      <c r="AU51" t="inlineStr">
+      <c r="AU48" t="inlineStr">
         <is>
           <t>‏۳۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV51" t="inlineStr">
+      <c r="AV48" t="inlineStr">
         <is>
           <t>‏۱۵,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AW51" t="inlineStr">
+      <c r="AW48" t="inlineStr">
         <is>
           <t>ودیعه: ۳۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
+      <c r="AX48" t="inlineStr">
         <is>
           <t>اجاره: ۱۵,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr"/>
-      <c r="BA51" t="inlineStr"/>
-      <c r="BB51" t="inlineStr"/>
-      <c r="BC51" t="inlineStr"/>
-      <c r="BD51" t="inlineStr">
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr"/>
+      <c r="BA48" t="inlineStr"/>
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="inlineStr"/>
+      <c r="BD48" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE51" t="inlineStr"/>
-      <c r="BF51" t="inlineStr">
+      <c r="BE48" t="inlineStr"/>
+      <c r="BF48" t="inlineStr">
         <is>
           <t>2026-11-26T16:26:19.614649</t>
         </is>
       </c>
-      <c r="BG51" t="inlineStr"/>
-      <c r="BH51" t="inlineStr">
+      <c r="BG48" t="inlineStr"/>
+      <c r="BH48" t="inlineStr">
         <is>
           <t>{"osm_n5165462147": 2297, "osm_n14089610125": 2535, "osm_n5165462148": 2872, "osm_n14084275565": 2880, "osm_n14084275564": 3160, "osm_n11417054143": 4055, "beryanak": 4407, "osm_w1041344025": 4498, "osm_n11417054161": 4608, "helal_ahmar": 4671, "osm_n5190423570": 4880, "osm_n5186234550": 5219, "osm_w1314615868": 5260, "osm_n5165422504": 5331, "osm_n5183520307": 5358, "osm_n3635251445": 5386, "osm_n14065977511": 5469, "mahdieh": 5704, "osm_n5183625750": 5757, "osm_n5165422503": 5890, "osm_n14058145512": 6008, "osm_n14058146709": 6138, "osm_w671794339": 6429, "osm_n13230313218": 6455, "moniriyeh": 6485, "osm_n14058145514": 6657, "osm_n13380425834": 6849, "osm_n14075053790": 6862, "osm_n14058145513": 7004, "osm_n13380425728": 7019, "osm_n13380425818": 7022, "osm_n6737096941": 7162, "osm_n5162910431": 7217, "osm_n5604727197": 7220, "osm_n5162855447": 7389, "osm_n14058145515": 7429, "osm_n5183513583": 7443, "osm_n4396461099": 7636, "osm_n5602579936": 7882, "osm_w1169531671": 8000, "teatr_shahr": 8050, "osm_n5186262276": 8263, "osm_n10746895093": 8265, "osm_n14071125007": 8342, "osm_n13380418873": 8742, "osm_n5190423568": 8855, "osm_n14058409025": 8869, "saadi": 8945, "vali_asr": 8959, "osm_n14059862414": 9032, "osm_n13202066659": 9042, "osm_n14072135585": 9095, "osm_n10861347776": 9101, "osm_n14072135584": 9192, "osm_n8890549263": 9226, "osm_n14072135586": 9261, "osm_n14065945232": 9458, "darvazeh_dowlat": 9553, "osm_n9149513248": 9578, "osm_n14058409026": 9585, "osm_n6444462277": 9620, "osm_n14075284474": 9632, "osm_n13279314257": 9717, "osm_n12659430599": 9761, "jahad": 9792, "osm_n13284688255": 9829, "taleghani": 9878, "osm_n8907277818": 9959, "osm_n8273593826": 10192, "osm_n5188341403": 10264, "osm_n8243426038": 10310, "osm_n14064336782": 10390, "haft_tir": 10512, "osm_n6390530109": 10650, "mirza_shirazi": 10937, "osm_n14072135587": 11020, "osm_n12157511978": 11072, "osm_n5604726917": 11113, "osm_n13426743990": 11120, "osm_n14060820580": 11290, "mofatteh": 11295, "osm_n14059828792": 11310, "osm_n2169732971": 11452, "osm_n14071125009": 11480, "osm_n14075284475": 11562, "osm_n11281445852": 11735, "shahid_beheshti": 11744, "osm_n6390530105": 11971, "osm_n14058409027": 12050, "osm_n14064708968": 12120, "osm_n14075125225": 12197, "sohrevardi": 12399, "osm_n14075125227": 12409, "osm_n5194776019": 12418, "osm_n5162855462": 12428, "osm_n13381123730": 12591, "osm_n14075284476": 12914, "osm_n3778821747": 12939, "osm_n14064708967": 13191, "osm_n5162910430": 13239, "osm_n660658572": 13262, "osm_n14058409028": 13475, "osm_n11750922029": 13759, "osm_n14075284477": 13885, "osm_n13381123745": 13959, "osm_n13230283736": 14115, "osm_n14072135588": 14172, "osm_n5162910441": 14203, "osm_n13381123758": 14659, "osm_n14058409029": 14825, "osm_n3778861787": 15003, "osm_n5162910442": 15409, "osm_n13381123759": 15485, "osm_n13817588094": 15594, "osm_n14058409030": 15871, "osm_n2169380700": 16039, "osm_n14072135590": 16573, "osm_n14058409031": 16827, "osm_n13381123770": 17101, "osm_n14058409032": 17531, "osm_n13381264373": 17858, "osm_n3778822187": 17954, "osm_n5163103599": 18372, "osm_n14072135591": 18854, "osm_n13381264374": 18904, "osm_n5163103601": 19470, "osm_n14061094940": 19850, "osm_n5163103600": 20662, "osm_n8738914819": 21031, "osm_n5163103597": 22199, "osm_n5163103598": 23084}</t>
         </is>
       </c>
-      <c r="BI51" t="inlineStr">
+      <c r="BI48" t="inlineStr">
         <is>
           <t>⬅️توضیحات کامل میباشد فقط برای بازدید تماس بگیرید ➡️
 ⛔️دوستان عزیز املاکی لطفا تماس نگیرند همکار هستیم ⛔️
@@ -12421,216 +11690,216 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>pin is ~3261 m estimated walk (2470 m straight-line) from nearest target station; text mentions an unnamed metro: ایستگاه اتوبوس و مراکز خرید</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>ga56yB2u</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>https://divar.ir/v/ga56yB2u</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>آپارتمان 70متری/ط اول/۲خوابه/شهرک صاحب الزمان</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>صاحب الزمان</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>خ مرادی</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>صاحب الزمان</t>
         </is>
       </c>
-      <c r="I52" t="b">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
         <v>300000000</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K49" t="n">
         <v>15000000</v>
       </c>
-      <c r="L52" t="b">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
+      <c r="L49" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>70</v>
       </c>
-      <c r="N52" t="n">
+      <c r="N49" t="n">
         <v>2</v>
       </c>
-      <c r="O52" t="n">
+      <c r="O49" t="n">
         <v>1388</v>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>1 از 3</t>
         </is>
       </c>
-      <c r="Q52" t="b">
-        <v>0</v>
-      </c>
-      <c r="R52" t="b">
-        <v>0</v>
-      </c>
-      <c r="S52" t="b">
-        <v>1</v>
-      </c>
-      <c r="T52" t="n">
+      <c r="Q49" t="b">
+        <v>0</v>
+      </c>
+      <c r="R49" t="b">
+        <v>0</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
         <v>3</v>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>premium-panel</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>۵ مهر ۱۴۰۵، ۱۸:۲۴</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>۵ آبان ۱۴۰۵، ۱۶:۰۸</t>
         </is>
       </c>
-      <c r="X52" t="n">
+      <c r="X49" t="n">
         <v>35.648512871943</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="Y49" t="n">
         <v>51.326303472035</v>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>api_exact_pin</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr">
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
-      <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="inlineStr"/>
-      <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="n">
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="n">
         <v>3261</v>
       </c>
-      <c r="AJ52" t="n">
+      <c r="AJ49" t="n">
         <v>43.5</v>
       </c>
-      <c r="AK52" t="inlineStr">
+      <c r="AK49" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr">
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr">
         <is>
           <t>osm_n5165462148</t>
         </is>
       </c>
-      <c r="AN52" t="n">
+      <c r="AN49" t="n">
         <v>2470</v>
       </c>
-      <c r="AO52" t="inlineStr">
+      <c r="AO49" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP52" t="inlineStr">
+      <c r="AP49" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ52" t="inlineStr"/>
-      <c r="AR52" t="inlineStr">
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr">
         <is>
           <t>ایستگاه اتوبوس و مراکز خرید</t>
         </is>
       </c>
-      <c r="AS52" t="n">
+      <c r="AS49" t="n">
         <v>300000000</v>
       </c>
-      <c r="AT52" t="n">
+      <c r="AT49" t="n">
         <v>15000000</v>
       </c>
-      <c r="AU52" t="inlineStr">
+      <c r="AU49" t="inlineStr">
         <is>
           <t>‏۳۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV52" t="inlineStr">
+      <c r="AV49" t="inlineStr">
         <is>
           <t>‏۱۵,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AW52" t="inlineStr">
+      <c r="AW49" t="inlineStr">
         <is>
           <t>ودیعه: ۳۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
+      <c r="AX49" t="inlineStr">
         <is>
           <t>اجاره: ۱۵,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr"/>
-      <c r="BA52" t="inlineStr"/>
-      <c r="BB52" t="inlineStr"/>
-      <c r="BC52" t="inlineStr"/>
-      <c r="BD52" t="inlineStr">
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
+      <c r="BA49" t="inlineStr"/>
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="inlineStr"/>
+      <c r="BD49" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE52" t="inlineStr"/>
-      <c r="BF52" t="inlineStr">
+      <c r="BE49" t="inlineStr"/>
+      <c r="BF49" t="inlineStr">
         <is>
           <t>2026-11-27T18:24:11.498399</t>
         </is>
       </c>
-      <c r="BG52" t="inlineStr"/>
-      <c r="BH52" t="inlineStr">
+      <c r="BG49" t="inlineStr"/>
+      <c r="BH49" t="inlineStr">
         <is>
           <t>{"osm_n5165462148": 2470, "osm_n5165462147": 2504, "osm_n14089610125": 3241, "osm_n14084275565": 3844, "osm_n14084275564": 4296, "osm_n11417054143": 4525, "osm_n11417054161": 4966, "beryanak": 5632, "osm_n5183520307": 5682, "osm_w1041344025": 5688, "osm_n5186234550": 5745, "helal_ahmar": 5896, "osm_w1314615868": 5987, "osm_n5190423570": 6076, "osm_n14065977511": 6354, "osm_n5165422504": 6492, "osm_n13230313218": 6559, "osm_n3635251445": 6568, "osm_n5183625750": 6736, "osm_n14058145512": 6842, "mahdieh": 6920, "osm_n5165422503": 7008, "osm_n14058146709": 7317, "osm_w671794339": 7510, "osm_n14058145513": 7671, "moniriyeh": 7712, "osm_n5604727197": 7722, "osm_n14058145514": 7870, "osm_n14075053790": 7911, "osm_n5602579936": 7984, "osm_n13380425834": 8007, "osm_n13380425728": 8041, "osm_n13380425818": 8135, "osm_n5183513583": 8347, "osm_n5162910431": 8365, "osm_n6737096941": 8368, "osm_n5162855447": 8608, "osm_n14058145515": 8655, "osm_n4396461099": 8863, "osm_w1169531671": 9126, "teatr_shahr": 9234, "osm_n10861347776": 9329, "osm_n10746895093": 9339, "osm_n13380418873": 9444, "osm_n5186262276": 9491, "osm_n14071125007": 9545, "osm_n14072135585": 9756, "osm_n14072135586": 9767, "osm_n5190423568": 9840, "osm_n14065945232": 9845, "osm_n8890549263": 10012, "osm_n14072135584": 10076, "osm_n14058409025": 10098, "vali_asr": 10113, "saadi": 10170, "osm_n14059862414": 10231, "osm_n13202066659": 10249, "osm_n8907277818": 10525, "osm_n14064336782": 10589, "osm_n14075284474": 10599, "osm_n5604726917": 10647, "osm_n9149513248": 10695, "osm_n6444462277": 10696, "darvazeh_dowlat": 10768, "osm_n14058409026": 10813, "osm_n13279314257": 10879, "jahad": 10919, "osm_n12659430599": 10942, "osm_n13284688255": 11020, "taleghani": 11081, "osm_n14072135587": 11175, "osm_n8273593826": 11188, "osm_n5188341403": 11489, "osm_n8243426038": 11531, "haft_tir": 11697, "osm_n11281445852": 11859, "osm_n6390530109": 11878, "osm_n12157511978": 11960, "mirza_shirazi": 12066, "osm_n14064708968": 12240, "osm_n5194776019": 12252, "osm_n13426743990": 12346, "osm_n5162855462": 12353, "osm_n14075284475": 12362, "mofatteh": 12461, "osm_n14059828792": 12492, "osm_n14060820580": 12507, "osm_n2169732971": 12678, "osm_n14071125009": 12683, "osm_n6390530105": 12887, "shahid_beheshti": 12891, "osm_n14058409027": 13272, "osm_n14064708967": 13315, "osm_n14075125225": 13378, "sohrevardi": 13565, "osm_n14075125227": 13632, "osm_n14075284476": 13678, "osm_n13381123730": 13712, "osm_n3778821747": 14118, "osm_n13230283736": 14226, "osm_n660658572": 14356, "osm_n5162910430": 14461, "osm_n14075284477": 14566, "osm_n14058409028": 14694, "osm_n11750922029": 14927, "osm_n13381123745": 15031, "osm_n14072135588": 15361, "osm_n5162910441": 15423, "osm_n13381123758": 15744, "osm_n14058409029": 16042, "osm_n3778861787": 16183, "osm_n13381123759": 16589, "osm_n5162910442": 16632, "osm_n13817588094": 16751, "osm_n14058409030": 17086, "osm_n2169380700": 17105, "osm_n14072135590": 17726, "osm_n14058409031": 18045, "osm_n13381123770": 18133, "osm_n14058409032": 18753, "osm_n13381264373": 18868, "osm_n3778822187": 19096, "osm_n5163103599": 19598, "osm_n13381264374": 19887, "osm_n14072135591": 19992, "osm_n5163103601": 20699, "osm_n14061094940": 20969, "osm_n5163103600": 21890, "osm_n8738914819": 22141, "osm_n5163103597": 23348, "osm_n5163103598": 24245}</t>
         </is>
       </c>
-      <c r="BI52" t="inlineStr">
+      <c r="BI49" t="inlineStr">
         <is>
           <t>↩️آپارتمان 70 متری↪️ 
 ⬅️نقاشی شده
@@ -12654,216 +11923,216 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>pin is ~3650 m estimated walk (2765 m straight-line) from nearest target station; text mentions an unnamed metro: ایستگاه اتوبوس و مراکز خرید</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>gaUDVo63</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaUDVo63</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>واحد۶۵متری/طبقه همکف/شهرک صاحب الزمان</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>صاحب الزمان</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>خ مرادی</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>صاحب الزمان</t>
         </is>
       </c>
-      <c r="I53" t="b">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
         <v>200000000</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K50" t="n">
         <v>12000000</v>
       </c>
-      <c r="L53" t="b">
-        <v>1</v>
-      </c>
-      <c r="M53" t="n">
+      <c r="L50" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
         <v>65</v>
       </c>
-      <c r="N53" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" t="n">
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="n">
         <v>1388</v>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>همکف از 2</t>
         </is>
       </c>
-      <c r="Q53" t="b">
-        <v>0</v>
-      </c>
-      <c r="R53" t="b">
-        <v>0</v>
-      </c>
-      <c r="S53" t="b">
-        <v>1</v>
-      </c>
-      <c r="T53" t="n">
+      <c r="Q50" t="b">
+        <v>0</v>
+      </c>
+      <c r="R50" t="b">
+        <v>0</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
         <v>3</v>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>premium-panel</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>۲۶ مهر ۱۴۰۵، ۰۸:۲۳</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="n">
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="n">
         <v>35.649981000067</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="Y50" t="n">
         <v>51.322108902304</v>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>api_exact_pin</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr">
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
-      <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="n">
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="n">
         <v>3650</v>
       </c>
-      <c r="AJ53" t="n">
+      <c r="AJ50" t="n">
         <v>48.7</v>
       </c>
-      <c r="AK53" t="inlineStr">
+      <c r="AK50" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr">
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr">
         <is>
           <t>osm_n5165462148</t>
         </is>
       </c>
-      <c r="AN53" t="n">
+      <c r="AN50" t="n">
         <v>2765</v>
       </c>
-      <c r="AO53" t="inlineStr">
+      <c r="AO50" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP53" t="inlineStr">
+      <c r="AP50" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ53" t="inlineStr"/>
-      <c r="AR53" t="inlineStr">
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr">
         <is>
           <t>ایستگاه اتوبوس و مراکز خرید</t>
         </is>
       </c>
-      <c r="AS53" t="n">
+      <c r="AS50" t="n">
         <v>200000000</v>
       </c>
-      <c r="AT53" t="n">
+      <c r="AT50" t="n">
         <v>12000000</v>
       </c>
-      <c r="AU53" t="inlineStr">
+      <c r="AU50" t="inlineStr">
         <is>
           <t>RENT_SLIDER credit.value=200000000</t>
         </is>
       </c>
-      <c r="AV53" t="inlineStr">
+      <c r="AV50" t="inlineStr">
         <is>
           <t>RENT_SLIDER rent.value=12000000</t>
         </is>
       </c>
-      <c r="AW53" t="inlineStr">
+      <c r="AW50" t="inlineStr">
         <is>
           <t>ودیعه: ۲۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
+      <c r="AX50" t="inlineStr">
         <is>
           <t>اجاره: ۱۲,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr">
+      <c r="AY50" t="inlineStr">
         <is>
           <t>credit 350000000 / rent 8500000</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr"/>
-      <c r="BA53" t="inlineStr"/>
-      <c r="BB53" t="inlineStr"/>
-      <c r="BC53" t="inlineStr"/>
-      <c r="BD53" t="inlineStr">
+      <c r="AZ50" t="inlineStr"/>
+      <c r="BA50" t="inlineStr"/>
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="inlineStr"/>
+      <c r="BD50" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE53" t="inlineStr"/>
-      <c r="BF53" t="inlineStr">
+      <c r="BE50" t="inlineStr"/>
+      <c r="BF50" t="inlineStr">
         <is>
           <t>2026-11-18T08:23:02.529807</t>
         </is>
       </c>
-      <c r="BG53" t="inlineStr"/>
-      <c r="BH53" t="inlineStr">
+      <c r="BG50" t="inlineStr"/>
+      <c r="BH50" t="inlineStr">
         <is>
           <t>{"osm_n5165462148": 2765, "osm_n5165462147": 2900, "osm_n14089610125": 3654, "osm_n14084275565": 4242, "osm_n11417054143": 4411, "osm_n14084275564": 4660, "osm_n11417054161": 4809, "osm_n5183520307": 5507, "osm_n5186234550": 5635, "beryanak": 5893, "osm_w1314615868": 5949, "osm_w1041344025": 6028, "helal_ahmar": 6197, "osm_n5190423570": 6291, "osm_n13230313218": 6313, "osm_n14065977511": 6380, "osm_n5165422504": 6674, "osm_n5183625750": 6804, "osm_n14058145512": 6842, "osm_n3635251445": 6914, "osm_n5165422503": 7154, "mahdieh": 7237, "osm_n14058146709": 7511, "osm_n5604727197": 7591, "osm_n14058145513": 7599, "osm_w671794339": 7631, "osm_n5602579936": 7730, "moniriyeh": 7976, "osm_n14075053790": 8011, "osm_n14058145514": 8104, "osm_n13380425834": 8365, "osm_n13380425728": 8436, "osm_n13380425818": 8510, "osm_n5162910431": 8530, "osm_n6737096941": 8696, "osm_n5183513583": 8756, "osm_n14058145515": 8914, "osm_n5162855447": 8920, "osm_n10861347776": 9105, "osm_n4396461099": 9158, "osm_w1169531671": 9272, "teatr_shahr": 9430, "osm_n10746895093": 9450, "osm_n14072135586": 9628, "osm_n14065945232": 9667, "osm_n14072135585": 9673, "osm_n5186262276": 9765, "osm_n13380418873": 9856, "osm_n14071125007": 9876, "osm_n5190423568": 9898, "osm_n8890549263": 9978, "osm_n14072135584": 10084, "osm_n5604726917": 10267, "vali_asr": 10280, "osm_n14064336782": 10353, "osm_n14058409025": 10371, "saadi": 10425, "osm_n13202066659": 10471, "osm_n14059862414": 10565, "osm_n14075284474": 10647, "osm_n14072135587": 10926, "osm_n8907277818": 10930, "darvazeh_dowlat": 11001, "osm_n13279314257": 11051, "jahad": 11063, "osm_n9149513248": 11070, "osm_n6444462277": 11082, "osm_n14058409026": 11082, "osm_n12659430599": 11289, "taleghani": 11297, "osm_n13284688255": 11361, "osm_n8273593826": 11588, "osm_n5188341403": 11744, "osm_n8243426038": 11838, "haft_tir": 11891, "osm_n12157511978": 11967, "osm_n14064708968": 11979, "osm_n6390530109": 12167, "osm_n11281445852": 12208, "mirza_shirazi": 12211, "osm_n14075284475": 12329, "osm_n5194776019": 12539, "osm_n13426743990": 12602, "mofatteh": 12634, "osm_n5162855462": 12661, "osm_n14060820580": 12743, "osm_n14059828792": 12839, "osm_n14071125009": 12898, "osm_n2169732971": 12973, "shahid_beheshti": 13048, "osm_n14064708967": 13054, "osm_n6390530105": 13296, "osm_n14058409027": 13520, "osm_n14075284476": 13627, "osm_n14075125225": 13725, "sohrevardi": 13738, "osm_n13381123730": 13849, "osm_n14075125227": 13934, "osm_n13230283736": 13960, "osm_n3778821747": 14304, "osm_n660658572": 14473, "osm_n14075284477": 14480, "osm_n5162910430": 14767, "osm_n14058409028": 14933, "osm_n13381123745": 15132, "osm_n11750922029": 15282, "osm_n14072135588": 15556, "osm_n5162910441": 15732, "osm_n13381123758": 15854, "osm_n14058409029": 16275, "osm_n3778861787": 16368, "osm_n13381123759": 16711, "osm_n5162910442": 16936, "osm_n13817588094": 17111, "osm_n2169380700": 17201, "osm_n14058409030": 17315, "osm_n14072135590": 17884, "osm_n13381123770": 18207, "osm_n14058409031": 18280, "osm_n13381264373": 18930, "osm_n14058409032": 18999, "osm_n3778822187": 19245, "osm_n5163103599": 19855, "osm_n13381264374": 19933, "osm_n14072135591": 20138, "osm_n5163103601": 20968, "osm_n14061094940": 21100, "osm_n5163103600": 22170, "osm_n8738914819": 22264, "osm_n5163103597": 23501, "osm_n5163103598": 24410}</t>
         </is>
       </c>
-      <c r="BI53" t="inlineStr">
+      <c r="BI50" t="inlineStr">
         <is>
           <t>↩️واحد ۶۰ متری↪️ 
 ⬅️نقاشی شده
@@ -12888,6 +12157,517 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NEEDS_LOCATION_VERIFICATION</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>no usable coordinates (MISSING)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>gaWLISx4</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://divar.ir/v/gaWLISx4</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>رهن و اجاره</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>سبلان (لشگر)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>سبلان قدیمی; سبلان (لشگر)</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="K51" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>30</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1399</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>1 از 4</t>
+        </is>
+      </c>
+      <c r="Q51" t="b">
+        <v>0</v>
+      </c>
+      <c r="R51" t="b">
+        <v>0</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>personal</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>۲۸ مهر ۱۴۰۵، ۰۰:۱۹</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>‏۱۲,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>اجاره: ۱۲,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr"/>
+      <c r="BA51" t="inlineStr"/>
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="inlineStr"/>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="BE51" t="inlineStr"/>
+      <c r="BF51" t="inlineStr">
+        <is>
+          <t>2026-11-20T00:19:19.272296</t>
+        </is>
+      </c>
+      <c r="BG51" t="inlineStr"/>
+      <c r="BH51" t="inlineStr"/>
+      <c r="BI51" t="inlineStr">
+        <is>
+          <t>به ۱ یا ۲ اقای مجرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NEEDS_LOCATION_VERIFICATION</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>no usable coordinates (MISSING)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>gahzd8iK</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://divar.ir/v/gahzd8iK</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>۴۰ متر سوئیت تکواحدی</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>تهرانپارس شرقی</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>تهرانپارس شرقی</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="K52" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>40</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1397</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q52" t="b">
+        <v>0</v>
+      </c>
+      <c r="R52" t="b">
+        <v>0</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>personal</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>۶ آبان ۱۴۰۵، ۱۵:۰۲</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>‏۷,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>اجاره: ۷,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
+      <c r="BA52" t="inlineStr"/>
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="inlineStr"/>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="BE52" t="inlineStr"/>
+      <c r="BF52" t="inlineStr">
+        <is>
+          <t>2026-11-28T15:02:12.339491</t>
+        </is>
+      </c>
+      <c r="BG52" t="inlineStr"/>
+      <c r="BH52" t="inlineStr"/>
+      <c r="BI52" t="inlineStr">
+        <is>
+          <t>املاک تماس نگیرید تشکر
+فقط به موزیسین یا افراد مرتبط با موسیقی و هنر اجاره داده میشود
+در غیر اینصورت لطفا تماس نگیرید الویت 
+استدیو موسیقی استدیو موزیک
+الویت با تنظیم کننده ها ی موسیقی ،  نوازندگان یا میکس من میکس و مستر کاران برای اجاره این ملک</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NEEDS_LOCATION_VERIFICATION</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>no usable coordinates (MISSING)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>gagfiDTq</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://divar.ir/v/gagfiDTq</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>اجاره خانه ۴۰ متری</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>تهرانپارس شرقی</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>تهرانپارس شرقی</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="K53" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>40</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1395</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q53" t="b">
+        <v>0</v>
+      </c>
+      <c r="R53" t="b">
+        <v>0</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>personal</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>۵ آبان ۱۴۰۵، ۰۷:۵۴</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>‏۱۶۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>‏۱۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>ودیعه: ۱۶۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>اجاره: ۱۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr"/>
+      <c r="BA53" t="inlineStr"/>
+      <c r="BB53" t="inlineStr"/>
+      <c r="BC53" t="inlineStr"/>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="BE53" t="inlineStr"/>
+      <c r="BF53" t="inlineStr">
+        <is>
+          <t>2026-11-27T07:54:42.431949</t>
+        </is>
+      </c>
+      <c r="BG53" t="inlineStr"/>
+      <c r="BH53" t="inlineStr"/>
+      <c r="BI53" t="inlineStr">
+        <is>
+          <t>با سلام 
+خونه ۴۰ متری واقع در میدان رهبر 
+کامل بازسازی شده 
+نورگیر فوق العاده 
+طبقه اول 
+مالک در طبقه ۲ سکونت دارد 
+سرویس بهداشتی در راه پله حمام در اتاق 
+مناسب یک زوج نهایت با یک فرزند 
+به مجرد خانوم اجاره داده میشود 
+مجرد اقا تماس نگیره 
+بازدید ۱۱ تا ۸
+توضیحات کامله در صورت بازدید تماس بگیرید
+به اتباع به هیچ وجه اجاره داده نمیشود</t>
+        </is>
+      </c>
+    </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -12896,81 +12676,81 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>no usable coordinates (MISSING)</t>
+          <t>no usable coordinates; text mentions an unnamed metro: مترو و BRT️✅</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>gaWLISx4</t>
+          <t>ga8a8R1G</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://divar.ir/v/gaWLISx4</t>
+          <t>https://divar.ir/v/ga8a8R1G</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>رهن و اجاره</t>
+          <t>اجاره ۶۰متر /pموتور /بالکن /بازسازی شده</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>سبلان (لشگر)</t>
+          <t>جیحون</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>سبلان قدیمی; سبلان (لشگر)</t>
+          <t>جیحون</t>
         </is>
       </c>
       <c r="I54" t="b">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>500000000</v>
+        <v>300000000</v>
       </c>
       <c r="K54" t="n">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>1399</v>
+        <v>1387</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>1 از 4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q54" t="b">
         <v>0</v>
       </c>
       <c r="R54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" t="b">
         <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>personal</t>
+          <t>premium-panel</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>۲۸ مهر ۱۴۰۵، ۰۰:۱۹</t>
+          <t>۸ مهر ۱۴۰۵، ۱۱:۵۲</t>
         </is>
       </c>
       <c r="W54" t="inlineStr"/>
@@ -13002,31 +12782,35 @@
       <c r="AO54" t="inlineStr"/>
       <c r="AP54" t="inlineStr"/>
       <c r="AQ54" t="inlineStr"/>
-      <c r="AR54" t="inlineStr"/>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>مترو و BRT️✅</t>
+        </is>
+      </c>
       <c r="AS54" t="n">
-        <v>500000000</v>
+        <v>300000000</v>
       </c>
       <c r="AT54" t="n">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
+          <t>‏۳۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>‏۱۲,۰۰۰,۰۰۰ تومان</t>
+          <t>‏۱۶,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
+          <t>ودیعه: ۳۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>اجاره: ۱۲,۰۰۰,۰۰۰ تومان</t>
+          <t>اجاره: ۱۶,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -13042,704 +12826,12 @@
       <c r="BE54" t="inlineStr"/>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>2026-11-20T00:19:19.272296</t>
+          <t>2026-10-31T11:52:47.452916</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr"/>
       <c r="BH54" t="inlineStr"/>
       <c r="BI54" t="inlineStr">
-        <is>
-          <t>به ۱ یا ۲ اقای مجرد</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>NEEDS_LOCATION_VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>no usable coordinates (MISSING)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ga7-F94A</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>https://divar.ir/v/ga7-F94A</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>سولقان ۸۰ متر تک واحد رهن و اجاره</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>شهران شمالی</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>شهران شمالی</t>
-        </is>
-      </c>
-      <c r="I55" t="b">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="K55" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="L55" t="b">
-        <v>1</v>
-      </c>
-      <c r="M55" t="n">
-        <v>80</v>
-      </c>
-      <c r="N55" t="n">
-        <v>2</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1395</v>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>3 از 5</t>
-        </is>
-      </c>
-      <c r="Q55" t="b">
-        <v>1</v>
-      </c>
-      <c r="R55" t="b">
-        <v>1</v>
-      </c>
-      <c r="S55" t="b">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>6</v>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>premium-panel</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>۷ مهر ۱۴۰۵، ۱۰:۲۷</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="inlineStr"/>
-      <c r="AO55" t="inlineStr"/>
-      <c r="AP55" t="inlineStr"/>
-      <c r="AQ55" t="inlineStr"/>
-      <c r="AR55" t="inlineStr"/>
-      <c r="AS55" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>RENT_SLIDER credit.value=300000000</t>
-        </is>
-      </c>
-      <c r="AV55" t="inlineStr">
-        <is>
-          <t>RENT_SLIDER rent.value=17000000</t>
-        </is>
-      </c>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>ودیعه: ۳۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>اجاره: ۱۷,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>credit 880000000 / rent None</t>
-        </is>
-      </c>
-      <c r="AZ55" t="inlineStr"/>
-      <c r="BA55" t="inlineStr"/>
-      <c r="BB55" t="inlineStr"/>
-      <c r="BC55" t="inlineStr"/>
-      <c r="BD55" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="BE55" t="inlineStr"/>
-      <c r="BF55" t="inlineStr">
-        <is>
-          <t>2026-10-30T10:27:05.786667</t>
-        </is>
-      </c>
-      <c r="BG55" t="inlineStr"/>
-      <c r="BH55" t="inlineStr"/>
-      <c r="BI55" t="inlineStr">
-        <is>
-          <t>با احترام ملک در سولقان است
-.
-۸۰ متر ۲ خواب
-تک واحدی طبقه سوم
-پارکینگ و آسانسور دارد
-نورگیر و نقشه عالی
-.
-موارد مشابه متناسب با بودجه شما موجود است.
-املاک آینده</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NEEDS_LOCATION_VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>no usable coordinates (MISSING)</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>gahzd8iK</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://divar.ir/v/gahzd8iK</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>۴۰ متر سوئیت تکواحدی</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>تهرانپارس شرقی</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>تهرانپارس شرقی</t>
-        </is>
-      </c>
-      <c r="I56" t="b">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="K56" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="L56" t="b">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>40</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1397</v>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q56" t="b">
-        <v>0</v>
-      </c>
-      <c r="R56" t="b">
-        <v>0</v>
-      </c>
-      <c r="S56" t="b">
-        <v>1</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>personal</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>۶ آبان ۱۴۰۵، ۱۵:۰۲</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
-      <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr"/>
-      <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
-      <c r="AO56" t="inlineStr"/>
-      <c r="AP56" t="inlineStr"/>
-      <c r="AQ56" t="inlineStr"/>
-      <c r="AR56" t="inlineStr"/>
-      <c r="AS56" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AV56" t="inlineStr">
-        <is>
-          <t>‏۷,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>اجاره: ۷,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr"/>
-      <c r="BA56" t="inlineStr"/>
-      <c r="BB56" t="inlineStr"/>
-      <c r="BC56" t="inlineStr"/>
-      <c r="BD56" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="BE56" t="inlineStr"/>
-      <c r="BF56" t="inlineStr">
-        <is>
-          <t>2026-11-28T15:02:12.339491</t>
-        </is>
-      </c>
-      <c r="BG56" t="inlineStr"/>
-      <c r="BH56" t="inlineStr"/>
-      <c r="BI56" t="inlineStr">
-        <is>
-          <t>املاک تماس نگیرید تشکر
-فقط به موزیسین یا افراد مرتبط با موسیقی و هنر اجاره داده میشود
-در غیر اینصورت لطفا تماس نگیرید الویت 
-استدیو موسیقی استدیو موزیک
-الویت با تنظیم کننده ها ی موسیقی ،  نوازندگان یا میکس من میکس و مستر کاران برای اجاره این ملک</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>NEEDS_LOCATION_VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>no usable coordinates (MISSING)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>gagfiDTq</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://divar.ir/v/gagfiDTq</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>اجاره خانه ۴۰ متری</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>تهرانپارس شرقی</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>تهرانپارس شرقی</t>
-        </is>
-      </c>
-      <c r="I57" t="b">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>160000000</v>
-      </c>
-      <c r="K57" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="L57" t="b">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>40</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1395</v>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q57" t="b">
-        <v>0</v>
-      </c>
-      <c r="R57" t="b">
-        <v>0</v>
-      </c>
-      <c r="S57" t="b">
-        <v>1</v>
-      </c>
-      <c r="T57" t="n">
-        <v>4</v>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>personal</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>۵ آبان ۱۴۰۵، ۰۷:۵۴</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="inlineStr"/>
-      <c r="AE57" t="inlineStr"/>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="inlineStr"/>
-      <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr"/>
-      <c r="AJ57" t="inlineStr"/>
-      <c r="AK57" t="inlineStr"/>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="inlineStr"/>
-      <c r="AN57" t="inlineStr"/>
-      <c r="AO57" t="inlineStr"/>
-      <c r="AP57" t="inlineStr"/>
-      <c r="AQ57" t="inlineStr"/>
-      <c r="AR57" t="inlineStr"/>
-      <c r="AS57" t="n">
-        <v>160000000</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>‏۱۶۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AV57" t="inlineStr">
-        <is>
-          <t>‏۱۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>ودیعه: ۱۶۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>اجاره: ۱۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-      <c r="AZ57" t="inlineStr"/>
-      <c r="BA57" t="inlineStr"/>
-      <c r="BB57" t="inlineStr"/>
-      <c r="BC57" t="inlineStr"/>
-      <c r="BD57" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="BE57" t="inlineStr"/>
-      <c r="BF57" t="inlineStr">
-        <is>
-          <t>2026-11-27T07:54:42.431949</t>
-        </is>
-      </c>
-      <c r="BG57" t="inlineStr"/>
-      <c r="BH57" t="inlineStr"/>
-      <c r="BI57" t="inlineStr">
-        <is>
-          <t>با سلام 
-خونه ۴۰ متری واقع در میدان رهبر 
-کامل بازسازی شده 
-نورگیر فوق العاده 
-طبقه اول 
-مالک در طبقه ۲ سکونت دارد 
-سرویس بهداشتی در راه پله حمام در اتاق 
-مناسب یک زوج نهایت با یک فرزند 
-به مجرد خانوم اجاره داده میشود 
-مجرد اقا تماس نگیره 
-بازدید ۱۱ تا ۸
-توضیحات کامله در صورت بازدید تماس بگیرید
-به اتباع به هیچ وجه اجاره داده نمیشود</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>NEEDS_LOCATION_VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>no usable coordinates; text mentions an unnamed metro: مترو و BRT️✅</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>ga8a8R1G</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://divar.ir/v/ga8a8R1G</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>اجاره ۶۰متر /pموتور /بالکن /بازسازی شده</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>جیحون</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>جیحون</t>
-        </is>
-      </c>
-      <c r="I58" t="b">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="K58" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="L58" t="b">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>60</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1387</v>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q58" t="b">
-        <v>0</v>
-      </c>
-      <c r="R58" t="b">
-        <v>1</v>
-      </c>
-      <c r="S58" t="b">
-        <v>1</v>
-      </c>
-      <c r="T58" t="n">
-        <v>1</v>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>premium-panel</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>۸ مهر ۱۴۰۵، ۱۱:۵۲</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr"/>
-      <c r="AD58" t="inlineStr"/>
-      <c r="AE58" t="inlineStr"/>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="inlineStr"/>
-      <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="inlineStr"/>
-      <c r="AJ58" t="inlineStr"/>
-      <c r="AK58" t="inlineStr"/>
-      <c r="AL58" t="inlineStr"/>
-      <c r="AM58" t="inlineStr"/>
-      <c r="AN58" t="inlineStr"/>
-      <c r="AO58" t="inlineStr"/>
-      <c r="AP58" t="inlineStr"/>
-      <c r="AQ58" t="inlineStr"/>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>مترو و BRT️✅</t>
-        </is>
-      </c>
-      <c r="AS58" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>‏۳۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AV58" t="inlineStr">
-        <is>
-          <t>‏۱۶,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>ودیعه: ۳۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>اجاره: ۱۶,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-      <c r="AZ58" t="inlineStr"/>
-      <c r="BA58" t="inlineStr"/>
-      <c r="BB58" t="inlineStr"/>
-      <c r="BC58" t="inlineStr"/>
-      <c r="BD58" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="BE58" t="inlineStr"/>
-      <c r="BF58" t="inlineStr">
-        <is>
-          <t>2026-10-31T11:52:47.452916</t>
-        </is>
-      </c>
-      <c r="BG58" t="inlineStr"/>
-      <c r="BH58" t="inlineStr"/>
-      <c r="BI58" t="inlineStr">
         <is>
           <t>✅مشاورین آلفا ✅
         ✅آپارتمان۶۰متر  خوش نقشه تخلیه️✅
@@ -13773,170 +12865,170 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>no usable coordinates (MISSING)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>gaCTG_5X</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaCTG_5X</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>اجاره آپارتمان ۶۰ متری</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>شهرک ولیعصر شمالی</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
         <is>
           <t>شهرک ولیعصر شمالی</t>
         </is>
       </c>
-      <c r="I59" t="b">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
         <v>500000000</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="b">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
         <v>60</v>
       </c>
-      <c r="N59" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" t="n">
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" t="n">
         <v>1395</v>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>4 از 4</t>
         </is>
       </c>
-      <c r="Q59" t="b">
-        <v>0</v>
-      </c>
-      <c r="R59" t="b">
-        <v>0</v>
-      </c>
-      <c r="S59" t="b">
-        <v>1</v>
-      </c>
-      <c r="T59" t="n">
+      <c r="Q55" t="b">
+        <v>0</v>
+      </c>
+      <c r="R55" t="b">
+        <v>0</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
         <v>2</v>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>personal</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>۱۲ مهر ۱۴۰۵، ۱۸:۰۸</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>۱۷ مهر ۱۴۰۵، ۱۲:۲۸</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr">
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr"/>
-      <c r="AD59" t="inlineStr"/>
-      <c r="AE59" t="inlineStr"/>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="inlineStr"/>
-      <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="inlineStr"/>
-      <c r="AJ59" t="inlineStr"/>
-      <c r="AK59" t="inlineStr"/>
-      <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="inlineStr"/>
-      <c r="AN59" t="inlineStr"/>
-      <c r="AO59" t="inlineStr"/>
-      <c r="AP59" t="inlineStr"/>
-      <c r="AQ59" t="inlineStr"/>
-      <c r="AR59" t="inlineStr"/>
-      <c r="AS59" t="n">
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="inlineStr"/>
+      <c r="AS55" t="n">
         <v>500000000</v>
       </c>
-      <c r="AT59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
         <is>
           <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV59" t="inlineStr">
+      <c r="AV55" t="inlineStr">
         <is>
           <t>رایگان</t>
         </is>
       </c>
-      <c r="AW59" t="inlineStr">
+      <c r="AW55" t="inlineStr">
         <is>
           <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
+      <c r="AX55" t="inlineStr">
         <is>
           <t>رهن کامل</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr"/>
-      <c r="BA59" t="inlineStr"/>
-      <c r="BB59" t="inlineStr"/>
-      <c r="BC59" t="inlineStr"/>
-      <c r="BD59" t="inlineStr">
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr"/>
+      <c r="BA55" t="inlineStr"/>
+      <c r="BB55" t="inlineStr"/>
+      <c r="BC55" t="inlineStr"/>
+      <c r="BD55" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE59" t="inlineStr"/>
-      <c r="BF59" t="inlineStr">
+      <c r="BE55" t="inlineStr"/>
+      <c r="BF55" t="inlineStr">
         <is>
           <t>2026-11-04T18:08:58.487714</t>
         </is>
       </c>
-      <c r="BG59" t="inlineStr"/>
-      <c r="BH59" t="inlineStr"/>
-      <c r="BI59" t="inlineStr">
+      <c r="BG55" t="inlineStr"/>
+      <c r="BH55" t="inlineStr"/>
+      <c r="BI55" t="inlineStr">
         <is>
           <t>عکس ها واقعی و متعلق به واحد میباشد
 کف سرامیک 
@@ -13957,6 +13049,180 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NEEDS_LOCATION_VERIFICATION</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>no usable coordinates (MISSING)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>gakbEsrC</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://divar.ir/v/gakbEsrC</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>لویزان ۶۸ متر دو خواب</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>لویزان</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>لویزان</t>
+        </is>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>68</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1383</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q56" t="b">
+        <v>0</v>
+      </c>
+      <c r="R56" t="b">
+        <v>0</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>13</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>personal</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>۸ آبان ۱۴۰۵، ۱۰:۵۷</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="inlineStr"/>
+      <c r="AS56" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>‏۲۵۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>‏۱۶,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>ودیعه: ۲۵۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>اجاره: ۱۶,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr"/>
+      <c r="BA56" t="inlineStr"/>
+      <c r="BB56" t="inlineStr"/>
+      <c r="BC56" t="inlineStr"/>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="BE56" t="inlineStr"/>
+      <c r="BF56" t="inlineStr">
+        <is>
+          <t>2026-11-30T10:57:29.752729</t>
+        </is>
+      </c>
+      <c r="BG56" t="inlineStr"/>
+      <c r="BH56" t="inlineStr"/>
+      <c r="BI56" t="inlineStr">
+        <is>
+          <t>واحد واقع در لویزان 
+۶۸ متر دو‌ خواب 
+قدیمی ساز 
+طبقه سوم 
+پارکینگ و آسانسور ندارد 
+سرمایش کولر آبی 
+گرمایش بخاری 
+تخلیه آخر ماه 
+مشاورین املاک تلاش 
+محمد شیدایی</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/needs_location_verification.xlsx
+++ b/needs_location_verification.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI56"/>
+  <dimension ref="A1:BI55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1194,63 +1194,63 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pin is ~1560 m estimated walk (1182 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و خطوط اتوبوس رانی/مراکز خرید</t>
+          <t>pin is ~1561 m estimated walk (1182 m straight-line) from nearest target station; text mentions target metro osm_n9149513248: مترو رضایی غرق در امکانات محلی به ا</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gaczn9-8</t>
+          <t>gaXTBgqD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://divar.ir/v/gaczn9-8</t>
+          <t>https://divar.ir/v/gaXTBgqD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>اجاره آپارتمان ۳۰متری نقلی/نوسازی شده/تخلیه</t>
+          <t>اجاره اپارتمان در انابک</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>وصفنارد</t>
+          <t>مینابی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>خ فتح المبین</t>
+          <t>خ مردانی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>وصفنارد</t>
+          <t>مینابی</t>
         </is>
       </c>
       <c r="I4" t="b">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>100000000</v>
+        <v>400000000</v>
       </c>
       <c r="K4" t="n">
-        <v>15000000</v>
+        <v>7000000</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1385</v>
+        <v>1390</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>زیرهمکف از 3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q4" t="b">
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1272,37 +1272,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>۲ آبان ۱۴۰۵، ۱۳:۱۰</t>
+          <t>۳ آبان ۱۴۰۵، ۱۷:۲۷</t>
         </is>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>35.64764564271721</v>
+        <v>35.647871499671</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.35353046990217</v>
+        <v>51.457130783629</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>FUZZY</t>
+          <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>APPROXIMATE</t>
+          <t>VALID</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>api_approximate</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>500</v>
-      </c>
+          <t>api_exact_pin</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
+          <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
@@ -1310,7 +1308,7 @@
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="AJ4" t="n">
         <v>20.8</v>
@@ -1323,7 +1321,7 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>osm_n14089610125</t>
+          <t>osm_n6444462277</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1339,36 +1337,40 @@
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>osm_n9149513248</t>
+        </is>
+      </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>مترو و خطوط اتوبوس رانی/مراکز خرید</t>
+          <t>مترو رضایی غرق در امکانات محلی به ا</t>
         </is>
       </c>
       <c r="AS4" t="n">
-        <v>100000000</v>
+        <v>400000000</v>
       </c>
       <c r="AT4" t="n">
-        <v>15000000</v>
+        <v>7000000</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>‏۱۰۰,۰۰۰,۰۰۰ تومان</t>
+          <t>‏۴۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>‏۱۵,۰۰۰,۰۰۰ تومان</t>
+          <t>‏۷,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>ودیعه: ۱۰۰,۰۰۰,۰۰۰ تومان</t>
+          <t>ودیعه: ۴۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>اجاره: ۱۵,۰۰۰,۰۰۰ تومان</t>
+          <t>اجاره: ۷,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1384,16 +1386,229 @@
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2026-11-24T13:10:57.636107</t>
+          <t>2026-11-25T17:27:08.385023</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>{"osm_n6444462277": 1182, "osm_n9149513248": 1213, "osm_n8273593826": 1819, "osm_n12659430599": 2209, "osm_n14059828792": 2293, "osm_n13284688255": 2510, "osm_n14075125225": 2737, "osm_n14059862414": 3060, "osm_n6390530105": 3292, "osm_n14071125007": 3491, "osm_n11750922029": 3623, "osm_n13380425818": 3706, "osm_n13380425728": 3908, "osm_n8243426038": 3967, "osm_n13380425834": 4018, "osm_n5183513583": 4257, "osm_n6737096941": 4333, "osm_n5162855447": 4615, "osm_n2169732971": 4737, "osm_n6390530109": 4776, "osm_n14075125227": 4893, "osm_n4396461099": 4939, "osm_n13817588094": 5180, "osm_n5162910430": 5196, "osm_n14058409025": 5272, "osm_n5186262276": 5352, "osm_n14058409026": 5397, "osm_n13380418873": 5411, "osm_n3635251445": 5521, "mahdieh": 5642, "osm_n5162910441": 5724, "saadi": 5854, "osm_n5188341403": 5961, "osm_n14058145515": 6007, "osm_n13426743990": 6149, "moniriyeh": 6231, "osm_w1041344025": 6394, "darvazeh_dowlat": 6600, "osm_n8907277818": 6675, "helal_ahmar": 6701, "osm_n14058409027": 6815, "osm_n5162910442": 6833, "osm_n14058145514": 6845, "osm_n13202066659": 6884, "osm_n14060820580": 6923, "taleghani": 7181, "beryanak": 7442, "teatr_shahr": 7562, "osm_n14084275564": 7567, "osm_n14071125009": 7700, "osm_n14058146709": 7836, "osm_n14058409028": 7866, "osm_n5190423570": 7894, "osm_n14084275565": 8018, "haft_tir": 8032, "osm_n5165422504": 8296, "osm_n5162910431": 8324, "vali_asr": 8406, "osm_n13279314257": 8421, "osm_w1169531671": 8782, "osm_n5165422503": 8801, "osm_n14089610125": 8846, "osm_n14058409029": 8912, "mofatteh": 8917, "jahad": 9201, "osm_w671794339": 9248, "osm_n3778821747": 9348, "sohrevardi": 9444, "shahid_beheshti": 9592, "mirza_shirazi": 9613, "osm_n10746895093": 9638, "osm_n14075053790": 9669, "osm_n14072135588": 9751, "osm_n14058409030": 9802, "osm_n5165462147": 10053, "osm_n5183625750": 10186, "osm_n14058409031": 10346, "osm_n14058409032": 10552, "osm_n13381123730": 10620, "osm_n3778861787": 10639, "osm_n14065977511": 10834, "osm_n5163103599": 10882, "osm_n5190423568": 10965, "osm_n11281445852": 11085, "osm_n5165462148": 11245, "osm_n14058145512": 11311, "osm_n5163103601": 11433, "osm_n14075284474": 11498, "osm_n660658572": 11572, "osm_w1314615868": 11710, "osm_n14072135584": 12167, "osm_n5163103600": 12206, "osm_n11417054143": 12327, "osm_n13381123745": 12422, "osm_n14072135590": 12562, "osm_n5186234550": 12631, "osm_n13381123758": 12643, "osm_n14058145513": 12756, "osm_n13381123759": 12858, "osm_n11417054161": 12946, "osm_n5162855462": 13043, "osm_n8890549263": 13054, "osm_n12157511978": 13140, "osm_n5183520307": 13472, "osm_n5194776019": 13728, "osm_n5604727197": 13784, "osm_n3778822187": 13887, "osm_n14072135585": 13929, "osm_n2169380700": 13986, "osm_n14075284475": 14323, "osm_n14072135591": 14703, "osm_n13230313218": 14945, "osm_n14072135586": 15040, "osm_n13381123770": 15379, "osm_n14075284476": 15581, "osm_n14065945232": 15858, "osm_n14061094940": 15965, "osm_n5602579936": 16008, "osm_n13381264373": 16306, "osm_n10861347776": 16394, "osm_n14075284477": 17052, "osm_n8738914819": 17163, "osm_n5163103597": 17297, "osm_n14064336782": 17533, "osm_n13381264374": 17566, "osm_n5163103598": 17747, "osm_n14072135587": 18255, "osm_n14064708968": 19337, "osm_n14064708967": 20225, "osm_n5604726917": 20737, "osm_n13230283736": 21089}</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>اجاره آپارتمان در اتابک خانه قدیمی مرتب محل لوستر فروش ها دسترسی به اتوبان بعثت و مترو رضایی غرق در امکانات محلی به اتباع داده میشود املاک تماس نگیرند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NEEDS_LOCATION_VERIFICATION</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pin is ~1560 m estimated walk (1182 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و خطوط اتوبوس رانی/مراکز خرید</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>gaczn9-8</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://divar.ir/v/gaczn9-8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>اجاره آپارتمان ۳۰متری نقلی/نوسازی شده/تخلیه</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>وصفنارد</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>خ فتح المبین</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>شاهد قدیمی; مبارک‌آباد بهشتی قدیمی; سبلان قدیمی; دولت‌آباد قدیمی; وصفنارد; شهید آوینی قدیمی; ملک‌آباد قدیمی; ظهیرآباد قدیمی</t>
+        </is>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1385</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>زیرهمکف از 3</t>
+        </is>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>personal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>۲ آبان ۱۴۰۵، ۱۳:۱۰</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>35.64764564271721</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>51.35353046990217</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>FUZZY</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>APPROXIMATE</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>api_approximate</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>1560</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Excluded (&gt;1500 m)</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>osm_n14089610125</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1182</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>not routed (estimate only)</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>مترو و خطوط اتوبوس رانی/مراکز خرید</t>
+        </is>
+      </c>
+      <c r="AS5" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>‏۱۰۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>‏۱۵,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>ودیعه: ۱۰۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>اجاره: ۱۵,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2026-11-24T13:10:57.636107</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr">
+        <is>
           <t>{"osm_n14089610125": 1182, "osm_n14084275565": 1406, "osm_n5165462147": 1644, "osm_n14084275564": 1893, "osm_n5165462148": 2782, "osm_w1041344025": 3362, "beryanak": 3752, "helal_ahmar": 3770, "osm_n3635251445": 4205, "osm_n5190423570": 4448, "mahdieh": 4676, "osm_n5165422504": 5040, "osm_n11417054143": 5056, "osm_n13380425728": 5587, "osm_n13380425834": 5592, "osm_n11417054161": 5675, "osm_n13380425818": 5682, "moniriyeh": 5723, "osm_n5165422503": 5731, "osm_n14058146709": 5739, "osm_n14065977511": 5860, "osm_w1314615868": 5904, "osm_n5183625750": 5955, "osm_n5183513583": 5965, "osm_n14058145514": 6041, "osm_n6737096941": 6057, "osm_n5186234550": 6104, "osm_w671794339": 6357, "osm_n5162855447": 6368, "osm_n5183520307": 6424, "osm_n14058145512": 6460, "osm_n14058145515": 6671, "osm_n4396461099": 6694, "osm_n14075053790": 6860, "osm_n5162910431": 6912, "osm_n14071125007": 7214, "osm_n13380418873": 7279, "osm_n5186262276": 7414, "teatr_shahr": 7575, "osm_n13230313218": 7654, "osm_n14058145513": 7660, "osm_w1169531671": 7751, "osm_n14059862414": 7887, "osm_n14058409025": 8015, "osm_n5604727197": 8064, "osm_n10746895093": 8161, "saadi": 8175, "osm_n6444462277": 8234, "osm_n9149513248": 8242, "osm_n13202066659": 8426, "osm_n8907277818": 8543, "osm_n12659430599": 8550, "vali_asr": 8593, "osm_n13284688255": 8650, "osm_n14058409026": 8743, "osm_n8273593826": 8747, "darvazeh_dowlat": 8879, "osm_n5190423568": 8949, "osm_n5602579936": 9059, "taleghani": 9275, "osm_n8243426038": 9283, "osm_n13279314257": 9310, "osm_n14072135584": 9471, "osm_n5188341403": 9478, "jahad": 9505, "osm_n8890549263": 9664, "osm_n6390530109": 9706, "osm_n14072135585": 9712, "osm_n14075284474": 9747, "haft_tir": 10000, "osm_n14072135586": 10060, "osm_n14059828792": 10100, "osm_n10861347776": 10166, "osm_n13426743990": 10322, "osm_n14065945232": 10378, "osm_n2169732971": 10474, "osm_n6390530105": 10498, "osm_n14060820580": 10580, "osm_n11281445852": 10596, "mirza_shirazi": 10629, "mofatteh": 10857, "osm_n14071125009": 10860, "osm_n14075125225": 10984, "osm_n14058409027": 11281, "osm_n12157511978": 11314, "shahid_beheshti": 11368, "osm_n14075125227": 11398, "osm_n5162855462": 11461, "osm_n14064336782": 11466, "osm_n5194776019": 11539, "osm_n14075284475": 11943, "sohrevardi": 11949, "osm_n14072135587": 12125, "osm_n5162910430": 12206, "osm_n13381123730": 12290, "osm_n3778821747": 12431, "osm_n11750922029": 12509, "osm_n5604726917": 12550, "osm_n14058409028": 12733, "osm_n660658572": 13035, "osm_n5162910441": 13152, "osm_n14064708968": 13243, "osm_n14075284476": 13335, "osm_n14072135588": 13610, "osm_n13381123745": 13784, "osm_n14058409029": 14097, "osm_n14064708967": 14304, "osm_n13817588094": 14320, "osm_n5162910442": 14376, "osm_n14075284477": 14418, "osm_n13381123758": 14443, "osm_n3778861787": 14480, "osm_n14058409030": 15156, "osm_n13381123759": 15213, "osm_n13230283736": 15233, "osm_n2169380700": 15864, "osm_n14058409031": 16085, "osm_n14072135590": 16146, "osm_n14058409032": 16740, "osm_n13381123770": 17002, "osm_n5163103599": 17531, "osm_n3778822187": 17554, "osm_n13381264373": 17802, "osm_n14072135591": 18463, "osm_n5163103601": 18574, "osm_n13381264374": 18901, "osm_n14061094940": 19515, "osm_n5163103600": 19722, "osm_n8738914819": 20719, "osm_n5163103597": 21764, "osm_n5163103598": 22601}</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>✨️به نام خدا✨️
 اجاره فوری 
@@ -1406,221 +1621,6 @@
 ✔️جای پارک موتور
 ✔️دسترسی به مترو و خطوط اتوبوس رانی/مراکز خرید فروشگاه های زنجیره ای، استخر،کتابخونه و فضای سبز
 جهت اطلاعات بیشتر تماس بگیرید☎️</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NEEDS_LOCATION_VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>pin is ~1561 m estimated walk (1182 m straight-line) from nearest target station; text mentions target metro osm_n9149513248: مترو رضایی غرق در امکانات محلی به ا</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>gaXTBgqD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://divar.ir/v/gaXTBgqD</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>اجاره اپارتمان در انابک</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>مینابی</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>خ مردانی</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>مینابی</t>
-        </is>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>400000000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>60</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1390</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q5" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>personal</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>۳ آبان ۱۴۰۵، ۱۷:۲۷</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="n">
-        <v>35.647871499671</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>51.457130783629</v>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>EXACT_DATA_UNTYPED</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>api_exact_pin</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>sections[6].widgets[0].data.location.exact_data.point</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="n">
-        <v>1561</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Excluded (&gt;1500 m)</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>osm_n6444462277</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1182</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Acceptable</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>not routed (estimate only)</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>osm_n9149513248</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>مترو رضایی غرق در امکانات محلی به ا</t>
-        </is>
-      </c>
-      <c r="AS5" t="n">
-        <v>400000000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>‏۴۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>‏۷,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>ودیعه: ۴۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>اجاره: ۷,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>2026-11-25T17:27:08.385023</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>{"osm_n6444462277": 1182, "osm_n9149513248": 1213, "osm_n8273593826": 1819, "osm_n12659430599": 2209, "osm_n14059828792": 2293, "osm_n13284688255": 2510, "osm_n14075125225": 2737, "osm_n14059862414": 3060, "osm_n6390530105": 3292, "osm_n14071125007": 3491, "osm_n11750922029": 3623, "osm_n13380425818": 3706, "osm_n13380425728": 3908, "osm_n8243426038": 3967, "osm_n13380425834": 4018, "osm_n5183513583": 4257, "osm_n6737096941": 4333, "osm_n5162855447": 4615, "osm_n2169732971": 4737, "osm_n6390530109": 4776, "osm_n14075125227": 4893, "osm_n4396461099": 4939, "osm_n13817588094": 5180, "osm_n5162910430": 5196, "osm_n14058409025": 5272, "osm_n5186262276": 5352, "osm_n14058409026": 5397, "osm_n13380418873": 5411, "osm_n3635251445": 5521, "mahdieh": 5642, "osm_n5162910441": 5724, "saadi": 5854, "osm_n5188341403": 5961, "osm_n14058145515": 6007, "osm_n13426743990": 6149, "moniriyeh": 6231, "osm_w1041344025": 6394, "darvazeh_dowlat": 6600, "osm_n8907277818": 6675, "helal_ahmar": 6701, "osm_n14058409027": 6815, "osm_n5162910442": 6833, "osm_n14058145514": 6845, "osm_n13202066659": 6884, "osm_n14060820580": 6923, "taleghani": 7181, "beryanak": 7442, "teatr_shahr": 7562, "osm_n14084275564": 7567, "osm_n14071125009": 7700, "osm_n14058146709": 7836, "osm_n14058409028": 7866, "osm_n5190423570": 7894, "osm_n14084275565": 8018, "haft_tir": 8032, "osm_n5165422504": 8296, "osm_n5162910431": 8324, "vali_asr": 8406, "osm_n13279314257": 8421, "osm_w1169531671": 8782, "osm_n5165422503": 8801, "osm_n14089610125": 8846, "osm_n14058409029": 8912, "mofatteh": 8917, "jahad": 9201, "osm_w671794339": 9248, "osm_n3778821747": 9348, "sohrevardi": 9444, "shahid_beheshti": 9592, "mirza_shirazi": 9613, "osm_n10746895093": 9638, "osm_n14075053790": 9669, "osm_n14072135588": 9751, "osm_n14058409030": 9802, "osm_n5165462147": 10053, "osm_n5183625750": 10186, "osm_n14058409031": 10346, "osm_n14058409032": 10552, "osm_n13381123730": 10620, "osm_n3778861787": 10639, "osm_n14065977511": 10834, "osm_n5163103599": 10882, "osm_n5190423568": 10965, "osm_n11281445852": 11085, "osm_n5165462148": 11245, "osm_n14058145512": 11311, "osm_n5163103601": 11433, "osm_n14075284474": 11498, "osm_n660658572": 11572, "osm_w1314615868": 11710, "osm_n14072135584": 12167, "osm_n5163103600": 12206, "osm_n11417054143": 12327, "osm_n13381123745": 12422, "osm_n14072135590": 12562, "osm_n5186234550": 12631, "osm_n13381123758": 12643, "osm_n14058145513": 12756, "osm_n13381123759": 12858, "osm_n11417054161": 12946, "osm_n5162855462": 13043, "osm_n8890549263": 13054, "osm_n12157511978": 13140, "osm_n5183520307": 13472, "osm_n5194776019": 13728, "osm_n5604727197": 13784, "osm_n3778822187": 13887, "osm_n14072135585": 13929, "osm_n2169380700": 13986, "osm_n14075284475": 14323, "osm_n14072135591": 14703, "osm_n13230313218": 14945, "osm_n14072135586": 15040, "osm_n13381123770": 15379, "osm_n14075284476": 15581, "osm_n14065945232": 15858, "osm_n14061094940": 15965, "osm_n5602579936": 16008, "osm_n13381264373": 16306, "osm_n10861347776": 16394, "osm_n14075284477": 17052, "osm_n8738914819": 17163, "osm_n5163103597": 17297, "osm_n14064336782": 17533, "osm_n13381264374": 17566, "osm_n5163103598": 17747, "osm_n14072135587": 18255, "osm_n14064708968": 19337, "osm_n14064708967": 20225, "osm_n5604726917": 20737, "osm_n13230283736": 21089}</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>اجاره آپارتمان در اتابک خانه قدیمی مرتب محل لوستر فروش ها دسترسی به اتوبان بعثت و مترو رضایی غرق در امکانات محلی به اتباع داده میشود املاک تماس نگیرند.</t>
         </is>
       </c>
     </row>
@@ -7523,17 +7523,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>gaXjB6TN</t>
+          <t>gae_fJGv</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://divar.ir/v/gaXjB6TN</t>
+          <t>https://divar.ir/v/gae_fJGv</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>آپارتمان50متر/پارکینگ موتور/انباری/بالکن/خوش نقشه</t>
+          <t>آپارتمان65متر/پارکینگ‌ماشین/انباری/بالکن/دو خواب</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -7551,26 +7551,26 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>500000000</v>
+        <v>300000000</v>
       </c>
       <c r="K31" t="n">
-        <v>3000000</v>
+        <v>15000000</v>
       </c>
       <c r="L31" t="b">
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2 از 3</t>
+          <t>3 از 5</t>
         </is>
       </c>
       <c r="Q31" t="b">
@@ -7583,7 +7583,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -7592,37 +7592,35 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>۲۸ مهر ۱۴۰۵، ۱۱:۲۰</t>
+          <t>۴ آبان ۱۴۰۵، ۱۰:۵۱</t>
         </is>
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
-        <v>35.68074511533867</v>
+        <v>35.680718725842</v>
       </c>
       <c r="Y31" t="n">
-        <v>51.36467145447642</v>
+        <v>51.364677072172</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>FUZZY</t>
+          <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>APPROXIMATE</t>
+          <t>VALID</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>api_approximate</t>
-        </is>
-      </c>
-      <c r="AC31" t="n">
-        <v>500</v>
-      </c>
+          <t>api_exact_pin</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
+          <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
@@ -7666,34 +7664,34 @@
         </is>
       </c>
       <c r="AS31" t="n">
-        <v>500000000</v>
+        <v>300000000</v>
       </c>
       <c r="AT31" t="n">
-        <v>3000000</v>
+        <v>15000000</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>RENT_SLIDER credit.value=500000000</t>
+          <t>RENT_SLIDER credit.value=300000000</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>RENT_SLIDER rent.value=3000000</t>
+          <t>RENT_SLIDER rent.value=15000000</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
+          <t>ودیعه: ۳۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>اجاره: ۳,۰۰۰,۰۰۰ تومان</t>
+          <t>اجاره: ۱۵,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>credit 600000000 / rent None</t>
+          <t>credit 400000000 / rent 12000000</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr"/>
@@ -7708,16 +7706,259 @@
       <c r="BE31" t="inlineStr"/>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2026-11-20T11:20:19.107716</t>
+          <t>2026-11-26T10:51:24.915676</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr"/>
       <c r="BH31" t="inlineStr">
         <is>
+          <t>{"osm_n5190423570": 1392, "osm_n5165422504": 1552, "beryanak": 1687, "osm_n5165422503": 2029, "osm_n5183625750": 2190, "osm_n14065977511": 2313, "osm_n14058146709": 2414, "helal_ahmar": 2486, "osm_w671794339": 2587, "osm_w1314615868": 2825, "osm_n14058145512": 2940, "osm_n14075053790": 3060, "osm_w1041344025": 3159, "osm_n14058145514": 3195, "osm_n11417054143": 3228, "osm_n14084275564": 3230, "moniriyeh": 3338, "osm_n5162910431": 3385, "mahdieh": 3478, "osm_n5186234550": 3581, "osm_n3635251445": 3805, "osm_n11417054161": 3832, "osm_n14084275565": 4072, "osm_w1169531671": 4144, "osm_n14058145515": 4153, "teatr_shahr": 4319, "osm_n5183520307": 4368, "osm_n14058145513": 4368, "osm_n10746895093": 4420, "osm_n14089610125": 4727, "osm_n4396461099": 4761, "osm_n5162855447": 4767, "osm_n6737096941": 4844, "osm_n5186262276": 5098, "osm_n5604727197": 5119, "vali_asr": 5135, "osm_n5190423568": 5137, "osm_n13380425834": 5173, "osm_n13202066659": 5434, "osm_n5165462147": 5453, "saadi": 5577, "osm_n14058409025": 5670, "osm_n14072135584": 5693, "osm_n13380425818": 5721, "osm_n13230313218": 5840, "osm_n13279314257": 5907, "osm_n14071125007": 5933, "osm_n14075284474": 5934, "jahad": 5937, "osm_n8890549263": 5990, "darvazeh_dowlat": 6006, "taleghani": 6230, "osm_n14072135585": 6241, "osm_n14058409026": 6319, "osm_n13380425728": 6342, "osm_n5165462148": 6486, "osm_n14059862414": 6603, "haft_tir": 6766, "osm_n5188341403": 6865, "osm_n14072135586": 6881, "osm_n5602579936": 6984, "mirza_shirazi": 7084, "osm_n5183513583": 7316, "osm_n8243426038": 7426, "osm_n14065945232": 7439, "osm_n13284688255": 7451, "mofatteh": 7490, "osm_n12659430599": 7507, "osm_n12157511978": 7514, "osm_n6390530109": 7545, "osm_n10861347776": 7627, "osm_n13426743990": 7713, "osm_n14060820580": 7743, "osm_n14071125009": 7819, "osm_n9149513248": 7904, "shahid_beheshti": 7908, "osm_n14075284475": 8199, "osm_n6444462277": 8248, "osm_n2169732971": 8390, "osm_n14058409027": 8571, "sohrevardi": 8594, "osm_n13381123730": 8734, "osm_n14064336782": 8878, "osm_n14059828792": 8945, "osm_n3778821747": 9165, "osm_n8273593826": 9255, "osm_n13380418873": 9288, "osm_n14075125227": 9389, "osm_n660658572": 9402, "osm_n14072135587": 9592, "osm_n14075284476": 9608, "osm_n14075125225": 9793, "osm_n14058409028": 9931, "osm_n13381123745": 10106, "osm_n5162910430": 10247, "osm_n14072135588": 10429, "osm_n14064708968": 10721, "osm_n14075284477": 10768, "osm_n13381123758": 10800, "osm_n8907277818": 10867, "osm_n3778861787": 11228, "osm_n5162910441": 11228, "osm_n14058409029": 11245, "osm_n6390530105": 11320, "osm_n11750922029": 11433, "osm_n13381123759": 11624, "osm_n5604726917": 11630, "osm_n14064708967": 11716, "osm_n2169380700": 12188, "osm_n14058409030": 12265, "osm_n5162910442": 12364, "osm_n13230283736": 12633, "osm_n14072135590": 12743, "osm_n14058409031": 13246, "osm_n13381123770": 13274, "osm_n13817588094": 13307, "osm_n11281445852": 13791, "osm_n14058409032": 14006, "osm_n13381264373": 14050, "osm_n3778822187": 14112, "osm_n5163103599": 14913, "osm_n5162855462": 14919, "osm_n14072135591": 15008, "osm_n5194776019": 15100, "osm_n13381264374": 15126, "osm_n14061094940": 15993, "osm_n5163103601": 16091, "osm_n8738914819": 17171, "osm_n5163103600": 17349, "osm_n5163103597": 18364, "osm_n5163103598": 19266}</t>
+        </is>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>ـمشاورین کندو___________
+️آپارتمان 65متر خوش نقشه تخلیه️
+ ️دسترسی بی نظیر به مترو و BRT️
+ ملک به شدت خوش نقشه و قابل چیدمان
+  ـ
+‼️زیر قیمت منطقه ‼️
+‼️بی نظیر در این منطقه‼️
+‼️سریعا تماس بگیرید‼️
+ـ
+دسترسی عالی به مراکز خرید و فضای سبز⚡
+دسترسی بی نظیر به اتوبان یادگار امام و نواب⚡
+⭕️فوری!!!⭕️
+عکس ها متعلق به واحد میباشد⚜️
+فول امکانات و اوکازیون ⚜️
+کابینت MDF TORK⚜️
+گازرومیزی⚜️
+هودلمسی⚜️
+پارکینگ ماشین⚜️
+بالکن دلباز⚜️
+درب ضد سرقت⚜️
+تکواحدی⚜️
+سرویس ایرانی ⚜️
+نورگیری فوق العاده⚜️
+کمد دیواری بزرگ⚜️
+سرمایش کولر آبی⚜️
+گرمایش گرمایش⚜️
+کف سرامیک⚜️
+تماس بگیرید⚜️
+آدرس املاک:رودکی،سلسبیل جنوبی،قبل از مرتضوی پلاک87
+دپارتمان بزرگ کندو
+مشاور تخصصی منطقه:جلالی✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NEEDS_LOCATION_VERIFICATION</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>pin is ~1837 m estimated walk (1392 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRT️</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>gaXjB6TN</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://divar.ir/v/gaXjB6TN</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>آپارتمان50متر/پارکینگ موتور/انباری/بالکن/خوش نقشه</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>جیحون</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>جیحون</t>
+        </is>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>50</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1390</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2 از 3</t>
+        </is>
+      </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32" t="b">
+        <v>1</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>7</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>premium-panel</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>۲۸ مهر ۱۴۰۵، ۱۱:۲۰</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="n">
+        <v>35.68074511533867</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>51.36467145447642</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>FUZZY</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>APPROXIMATE</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>api_approximate</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>500</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="n">
+        <v>1837</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Excluded (&gt;1500 m)</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>osm_n5190423570</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>1392</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>not routed (estimate only)</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>مترو و BRT️</t>
+        </is>
+      </c>
+      <c r="AS32" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>RENT_SLIDER credit.value=500000000</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>RENT_SLIDER rent.value=3000000</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>اجاره: ۳,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>credit 600000000 / rent None</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr">
+        <is>
+          <t>2026-11-20T11:20:19.107716</t>
+        </is>
+      </c>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr">
+        <is>
           <t>{"osm_n5190423570": 1392, "osm_n5165422504": 1551, "beryanak": 1689, "osm_n5165422503": 2027, "osm_n5183625750": 2187, "osm_n14065977511": 2310, "osm_n14058146709": 2413, "helal_ahmar": 2488, "osm_w671794339": 2585, "osm_w1314615868": 2823, "osm_n14058145512": 2937, "osm_n14075053790": 3058, "osm_w1041344025": 3161, "osm_n14058145514": 3195, "osm_n11417054143": 3226, "osm_n14084275564": 3233, "moniriyeh": 3338, "osm_n5162910431": 3384, "mahdieh": 3479, "osm_n5186234550": 3578, "osm_n3635251445": 3807, "osm_n11417054161": 3831, "osm_n14084275565": 4075, "osm_w1169531671": 4142, "osm_n14058145515": 4153, "teatr_shahr": 4318, "osm_n14058145513": 4365, "osm_n5183520307": 4366, "osm_n10746895093": 4418, "osm_n14089610125": 4730, "osm_n4396461099": 4762, "osm_n5162855447": 4768, "osm_n6737096941": 4845, "osm_n5186262276": 5099, "osm_n5604727197": 5117, "vali_asr": 5134, "osm_n5190423568": 5134, "osm_n13380425834": 5175, "osm_n13202066659": 5433, "osm_n5165462147": 5456, "saadi": 5576, "osm_n14058409025": 5670, "osm_n14072135584": 5690, "osm_n13380425818": 5724, "osm_n13230313218": 5838, "osm_n13279314257": 5905, "osm_n14075284474": 5931, "osm_n14071125007": 5934, "jahad": 5935, "osm_n8890549263": 5987, "darvazeh_dowlat": 6005, "taleghani": 6229, "osm_n14072135585": 6238, "osm_n14058409026": 6319, "osm_n13380425728": 6344, "osm_n5165462148": 6488, "osm_n14059862414": 6604, "haft_tir": 6764, "osm_n5188341403": 6864, "osm_n14072135586": 6878, "osm_n5602579936": 6981, "mirza_shirazi": 7082, "osm_n5183513583": 7318, "osm_n8243426038": 7427, "osm_n14065945232": 7436, "osm_n13284688255": 7452, "mofatteh": 7488, "osm_n12659430599": 7508, "osm_n12157511978": 7511, "osm_n6390530109": 7545, "osm_n10861347776": 7624, "osm_n13426743990": 7712, "osm_n14060820580": 7742, "osm_n14071125009": 7818, "shahid_beheshti": 7906, "osm_n9149513248": 7906, "osm_n14075284475": 8197, "osm_n6444462277": 8250, "osm_n2169732971": 8390, "osm_n14058409027": 8570, "sohrevardi": 8592, "osm_n13381123730": 8732, "osm_n14064336782": 8875, "osm_n14059828792": 8946, "osm_n3778821747": 9164, "osm_n8273593826": 9257, "osm_n13380418873": 9290, "osm_n14075125227": 9389, "osm_n660658572": 9400, "osm_n14072135587": 9590, "osm_n14075284476": 9605, "osm_n14075125225": 9794, "osm_n14058409028": 9931, "osm_n13381123745": 10104, "osm_n5162910430": 10247, "osm_n14072135588": 10428, "osm_n14064708968": 10719, "osm_n14075284477": 10765, "osm_n13381123758": 10798, "osm_n8907277818": 10870, "osm_n3778861787": 11227, "osm_n5162910441": 11229, "osm_n14058409029": 11244, "osm_n6390530105": 11323, "osm_n11750922029": 11434, "osm_n13381123759": 11622, "osm_n5604726917": 11628, "osm_n14064708967": 11714, "osm_n2169380700": 12185, "osm_n14058409030": 12264, "osm_n5162910442": 12364, "osm_n13230283736": 12630, "osm_n14072135590": 12741, "osm_n14058409031": 13245, "osm_n13381123770": 13271, "osm_n13817588094": 13308, "osm_n11281445852": 13794, "osm_n14058409032": 14006, "osm_n13381264373": 14047, "osm_n3778822187": 14110, "osm_n5163103599": 14912, "osm_n5162855462": 14922, "osm_n14072135591": 15006, "osm_n5194776019": 15103, "osm_n13381264374": 15123, "osm_n14061094940": 15991, "osm_n5163103601": 16091, "osm_n8738914819": 17169, "osm_n5163103600": 17348, "osm_n5163103597": 18362, "osm_n5163103598": 19264}</t>
         </is>
       </c>
-      <c r="BI31" t="inlineStr">
+      <c r="BI32" t="inlineStr">
         <is>
           <t>ـمشاورین کندو___________
 ️آپارتمان ۵۰متر خوش نقشه تخلیه️
@@ -7754,247 +7995,6 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>NEEDS_LOCATION_VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>pin is ~1837 m estimated walk (1392 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRT️</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>gae_fJGv</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://divar.ir/v/gae_fJGv</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>آپارتمان65متر/پارکینگ‌ماشین/انباری/بالکن/دو خواب</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>جیحون</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>جیحون</t>
-        </is>
-      </c>
-      <c r="I32" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="K32" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="L32" t="b">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>65</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1391</v>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>3 از 5</t>
-        </is>
-      </c>
-      <c r="Q32" t="b">
-        <v>0</v>
-      </c>
-      <c r="R32" t="b">
-        <v>1</v>
-      </c>
-      <c r="S32" t="b">
-        <v>1</v>
-      </c>
-      <c r="T32" t="n">
-        <v>6</v>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>premium-panel</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>۴ آبان ۱۴۰۵، ۱۰:۵۱</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="n">
-        <v>35.680718725842</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>51.364677072172</v>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>EXACT_DATA_UNTYPED</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>api_exact_pin</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>sections[6].widgets[0].data.location.exact_data.point</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="n">
-        <v>1837</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Excluded (&gt;1500 m)</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>osm_n5190423570</t>
-        </is>
-      </c>
-      <c r="AN32" t="n">
-        <v>1392</v>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Secondary</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>not routed (estimate only)</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>مترو و BRT️</t>
-        </is>
-      </c>
-      <c r="AS32" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>RENT_SLIDER credit.value=300000000</t>
-        </is>
-      </c>
-      <c r="AV32" t="inlineStr">
-        <is>
-          <t>RENT_SLIDER rent.value=15000000</t>
-        </is>
-      </c>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>ودیعه: ۳۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>اجاره: ۱۵,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>credit 400000000 / rent 12000000</t>
-        </is>
-      </c>
-      <c r="AZ32" t="inlineStr"/>
-      <c r="BA32" t="inlineStr"/>
-      <c r="BB32" t="inlineStr"/>
-      <c r="BC32" t="inlineStr"/>
-      <c r="BD32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="BE32" t="inlineStr"/>
-      <c r="BF32" t="inlineStr">
-        <is>
-          <t>2026-11-26T10:51:24.915676</t>
-        </is>
-      </c>
-      <c r="BG32" t="inlineStr"/>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>{"osm_n5190423570": 1392, "osm_n5165422504": 1552, "beryanak": 1687, "osm_n5165422503": 2029, "osm_n5183625750": 2190, "osm_n14065977511": 2313, "osm_n14058146709": 2414, "helal_ahmar": 2486, "osm_w671794339": 2587, "osm_w1314615868": 2825, "osm_n14058145512": 2940, "osm_n14075053790": 3060, "osm_w1041344025": 3159, "osm_n14058145514": 3195, "osm_n11417054143": 3228, "osm_n14084275564": 3230, "moniriyeh": 3338, "osm_n5162910431": 3385, "mahdieh": 3478, "osm_n5186234550": 3581, "osm_n3635251445": 3805, "osm_n11417054161": 3832, "osm_n14084275565": 4072, "osm_w1169531671": 4144, "osm_n14058145515": 4153, "teatr_shahr": 4319, "osm_n5183520307": 4368, "osm_n14058145513": 4368, "osm_n10746895093": 4420, "osm_n14089610125": 4727, "osm_n4396461099": 4761, "osm_n5162855447": 4767, "osm_n6737096941": 4844, "osm_n5186262276": 5098, "osm_n5604727197": 5119, "vali_asr": 5135, "osm_n5190423568": 5137, "osm_n13380425834": 5173, "osm_n13202066659": 5434, "osm_n5165462147": 5453, "saadi": 5577, "osm_n14058409025": 5670, "osm_n14072135584": 5693, "osm_n13380425818": 5721, "osm_n13230313218": 5840, "osm_n13279314257": 5907, "osm_n14071125007": 5933, "osm_n14075284474": 5934, "jahad": 5937, "osm_n8890549263": 5990, "darvazeh_dowlat": 6006, "taleghani": 6230, "osm_n14072135585": 6241, "osm_n14058409026": 6319, "osm_n13380425728": 6342, "osm_n5165462148": 6486, "osm_n14059862414": 6603, "haft_tir": 6766, "osm_n5188341403": 6865, "osm_n14072135586": 6881, "osm_n5602579936": 6984, "mirza_shirazi": 7084, "osm_n5183513583": 7316, "osm_n8243426038": 7426, "osm_n14065945232": 7439, "osm_n13284688255": 7451, "mofatteh": 7490, "osm_n12659430599": 7507, "osm_n12157511978": 7514, "osm_n6390530109": 7545, "osm_n10861347776": 7627, "osm_n13426743990": 7713, "osm_n14060820580": 7743, "osm_n14071125009": 7819, "osm_n9149513248": 7904, "shahid_beheshti": 7908, "osm_n14075284475": 8199, "osm_n6444462277": 8248, "osm_n2169732971": 8390, "osm_n14058409027": 8571, "sohrevardi": 8594, "osm_n13381123730": 8734, "osm_n14064336782": 8878, "osm_n14059828792": 8945, "osm_n3778821747": 9165, "osm_n8273593826": 9255, "osm_n13380418873": 9288, "osm_n14075125227": 9389, "osm_n660658572": 9402, "osm_n14072135587": 9592, "osm_n14075284476": 9608, "osm_n14075125225": 9793, "osm_n14058409028": 9931, "osm_n13381123745": 10106, "osm_n5162910430": 10247, "osm_n14072135588": 10429, "osm_n14064708968": 10721, "osm_n14075284477": 10768, "osm_n13381123758": 10800, "osm_n8907277818": 10867, "osm_n3778861787": 11228, "osm_n5162910441": 11228, "osm_n14058409029": 11245, "osm_n6390530105": 11320, "osm_n11750922029": 11433, "osm_n13381123759": 11624, "osm_n5604726917": 11630, "osm_n14064708967": 11716, "osm_n2169380700": 12188, "osm_n14058409030": 12265, "osm_n5162910442": 12364, "osm_n13230283736": 12633, "osm_n14072135590": 12743, "osm_n14058409031": 13246, "osm_n13381123770": 13274, "osm_n13817588094": 13307, "osm_n11281445852": 13791, "osm_n14058409032": 14006, "osm_n13381264373": 14050, "osm_n3778822187": 14112, "osm_n5163103599": 14913, "osm_n5162855462": 14919, "osm_n14072135591": 15008, "osm_n5194776019": 15100, "osm_n13381264374": 15126, "osm_n14061094940": 15993, "osm_n5163103601": 16091, "osm_n8738914819": 17171, "osm_n5163103600": 17349, "osm_n5163103597": 18364, "osm_n5163103598": 19266}</t>
-        </is>
-      </c>
-      <c r="BI32" t="inlineStr">
-        <is>
-          <t>ـمشاورین کندو___________
-️آپارتمان 65متر خوش نقشه تخلیه️
- ️دسترسی بی نظیر به مترو و BRT️
- ملک به شدت خوش نقشه و قابل چیدمان
-  ـ
-‼️زیر قیمت منطقه ‼️
-‼️بی نظیر در این منطقه‼️
-‼️سریعا تماس بگیرید‼️
-ـ
-دسترسی عالی به مراکز خرید و فضای سبز⚡
-دسترسی بی نظیر به اتوبان یادگار امام و نواب⚡
-⭕️فوری!!!⭕️
-عکس ها متعلق به واحد میباشد⚜️
-فول امکانات و اوکازیون ⚜️
-کابینت MDF TORK⚜️
-گازرومیزی⚜️
-هودلمسی⚜️
-پارکینگ ماشین⚜️
-بالکن دلباز⚜️
-درب ضد سرقت⚜️
-تکواحدی⚜️
-سرویس ایرانی ⚜️
-نورگیری فوق العاده⚜️
-کمد دیواری بزرگ⚜️
-سرمایش کولر آبی⚜️
-گرمایش گرمایش⚜️
-کف سرامیک⚜️
-تماس بگیرید⚜️
-آدرس املاک:رودکی،سلسبیل جنوبی،قبل از مرتضوی پلاک87
-دپارتمان بزرگ کندو
-مشاور تخصصی منطقه:جلالی✅</t>
-        </is>
-      </c>
-    </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -8726,12 +8726,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>gah786Yu</t>
+          <t>galP5Irx</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://divar.ir/v/gah786Yu</t>
+          <t>https://divar.ir/v/galP5Irx</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -8799,15 +8799,15 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>۶ آبان ۱۴۰۵، ۱۵:۵۵</t>
+          <t>۹ آبان ۱۴۰۵، ۱۱:۱۷</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
-        <v>35.6834902140664</v>
+        <v>35.6834907479812</v>
       </c>
       <c r="Y36" t="n">
-        <v>51.3644888994061</v>
+        <v>51.36449072406505</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -8911,13 +8911,13 @@
       <c r="BE36" t="inlineStr"/>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>2026-11-28T15:55:22.384303</t>
+          <t>2026-12-01T11:17:32.052004</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>{"osm_n5190423570": 1427, "osm_n5165422504": 1438, "osm_n5165422503": 1812, "beryanak": 1875, "osm_n5183625750": 1882, "osm_n14065977511": 2019, "osm_n14058146709": 2303, "osm_w671794339": 2331, "osm_w1314615868": 2584, "osm_n14058145512": 2645, "helal_ahmar": 2690, "osm_n14075053790": 2785, "osm_n11417054143": 3136, "osm_n14058145514": 3154, "osm_n5162910431": 3200, "moniriyeh": 3365, "osm_n5186234550": 3392, "osm_w1041344025": 3407, "osm_n14084275564": 3533, "mahdieh": 3636, "osm_n11417054161": 3716, "osm_w1169531671": 3930, "osm_n3635251445": 4016, "osm_n14058145513": 4085, "osm_n14058145515": 4137, "osm_n10746895093": 4167, "teatr_shahr": 4179, "osm_n5183520307": 4213, "osm_n14084275565": 4381, "osm_n4396461099": 4805, "osm_n5162855447": 4847, "osm_n5190423568": 4848, "osm_n5604727197": 4863, "vali_asr": 4948, "osm_n6737096941": 4961, "osm_n14089610125": 5033, "osm_n5186262276": 5090, "osm_n13202066659": 5326, "osm_n13380425834": 5348, "osm_n14072135584": 5388, "saadi": 5524, "osm_n14075284474": 5644, "osm_n14058409025": 5649, "osm_n8890549263": 5682, "osm_n13230313218": 5686, "jahad": 5723, "osm_n13279314257": 5725, "osm_n5165462147": 5744, "darvazeh_dowlat": 5910, "osm_n13380425818": 5919, "osm_n14072135585": 5940, "osm_n14071125007": 6023, "taleghani": 6106, "osm_n14058409026": 6280, "osm_n13380425728": 6573, "osm_n14072135586": 6598, "haft_tir": 6608, "osm_n14059862414": 6683, "osm_n5165462148": 6761, "osm_n5602579936": 6793, "osm_n5188341403": 6796, "mirza_shirazi": 6870, "osm_n14065945232": 7172, "osm_n12157511978": 7213, "mofatteh": 7307, "osm_n10861347776": 7392, "osm_n8243426038": 7441, "osm_n6390530109": 7526, "osm_n13284688255": 7530, "osm_n5183513583": 7568, "osm_n12659430599": 7599, "osm_n13426743990": 7638, "osm_n14060820580": 7639, "osm_n14071125009": 7685, "shahid_beheshti": 7707, "osm_n14075284475": 7892, "osm_n9149513248": 8050, "osm_n2169732971": 8373, "sohrevardi": 8409, "osm_n6444462277": 8416, "osm_n14058409027": 8478, "osm_n13381123730": 8514, "osm_n14064336782": 8634, "osm_n3778821747": 8993, "osm_n14059828792": 9016, "osm_n660658572": 9166, "osm_n14075284476": 9300, "osm_n14072135587": 9351, "osm_n14075125227": 9373, "osm_n8273593826": 9449, "osm_n13380418873": 9559, "osm_n14058409028": 9821, "osm_n14075125225": 9855, "osm_n13381123745": 9859, "osm_n5162910430": 10232, "osm_n14072135588": 10266, "osm_n14075284477": 10460, "osm_n14064708968": 10478, "osm_n13381123758": 10560, "osm_n3778861787": 11053, "osm_n14058409029": 11124, "osm_n8907277818": 11146, "osm_n5162910441": 11213, "osm_n13381123759": 11394, "osm_n14064708967": 11466, "osm_n11750922029": 11496, "osm_n5604726917": 11510, "osm_n6390530105": 11524, "osm_n2169380700": 11940, "osm_n14058409030": 12136, "osm_n5162910442": 12334, "osm_n13230283736": 12380, "osm_n14072135590": 12542, "osm_n13381123770": 13013, "osm_n14058409031": 13122, "osm_n13817588094": 13369, "osm_n13381264373": 13783, "osm_n14058409032": 13893, "osm_n3778822187": 13903, "osm_n11281445852": 14095, "osm_n14072135591": 14797, "osm_n5163103599": 14812, "osm_n13381264374": 14852, "osm_n5162855462": 15227, "osm_n5194776019": 15409, "osm_n14061094940": 15770, "osm_n5163103601": 16003, "osm_n8738914819": 16944, "osm_n5163103600": 17270, "osm_n5163103597": 18158, "osm_n5163103598": 19070}</t>
+          <t>{"osm_n5190423570": 1427, "osm_n5165422504": 1438, "osm_n5165422503": 1812, "beryanak": 1875, "osm_n5183625750": 1882, "osm_n14065977511": 2019, "osm_n14058146709": 2303, "osm_w671794339": 2331, "osm_w1314615868": 2584, "osm_n14058145512": 2645, "helal_ahmar": 2689, "osm_n14075053790": 2785, "osm_n11417054143": 3136, "osm_n14058145514": 3154, "osm_n5162910431": 3199, "moniriyeh": 3364, "osm_n5186234550": 3392, "osm_w1041344025": 3407, "osm_n14084275564": 3533, "mahdieh": 3636, "osm_n11417054161": 3716, "osm_w1169531671": 3930, "osm_n3635251445": 4016, "osm_n14058145513": 4085, "osm_n14058145515": 4137, "osm_n10746895093": 4167, "teatr_shahr": 4179, "osm_n5183520307": 4214, "osm_n14084275565": 4381, "osm_n4396461099": 4805, "osm_n5162855447": 4847, "osm_n5190423568": 4848, "osm_n5604727197": 4864, "vali_asr": 4948, "osm_n6737096941": 4960, "osm_n14089610125": 5033, "osm_n5186262276": 5090, "osm_n13202066659": 5326, "osm_n13380425834": 5348, "osm_n14072135584": 5388, "saadi": 5524, "osm_n14075284474": 5644, "osm_n14058409025": 5649, "osm_n8890549263": 5682, "osm_n13230313218": 5686, "jahad": 5722, "osm_n13279314257": 5725, "osm_n5165462147": 5744, "darvazeh_dowlat": 5909, "osm_n13380425818": 5919, "osm_n14072135585": 5940, "osm_n14071125007": 6023, "taleghani": 6106, "osm_n14058409026": 6280, "osm_n13380425728": 6573, "osm_n14072135586": 6598, "haft_tir": 6608, "osm_n14059862414": 6683, "osm_n5165462148": 6761, "osm_n5602579936": 6793, "osm_n5188341403": 6796, "mirza_shirazi": 6870, "osm_n14065945232": 7172, "osm_n12157511978": 7213, "mofatteh": 7307, "osm_n10861347776": 7392, "osm_n8243426038": 7441, "osm_n6390530109": 7526, "osm_n13284688255": 7530, "osm_n5183513583": 7568, "osm_n12659430599": 7599, "osm_n13426743990": 7638, "osm_n14060820580": 7638, "osm_n14071125009": 7685, "shahid_beheshti": 7707, "osm_n14075284475": 7892, "osm_n9149513248": 8050, "osm_n2169732971": 8373, "sohrevardi": 8409, "osm_n6444462277": 8416, "osm_n14058409027": 8478, "osm_n13381123730": 8514, "osm_n14064336782": 8634, "osm_n3778821747": 8993, "osm_n14059828792": 9016, "osm_n660658572": 9166, "osm_n14075284476": 9300, "osm_n14072135587": 9351, "osm_n14075125227": 9373, "osm_n8273593826": 9449, "osm_n13380418873": 9559, "osm_n14058409028": 9821, "osm_n14075125225": 9855, "osm_n13381123745": 9859, "osm_n5162910430": 10232, "osm_n14072135588": 10266, "osm_n14075284477": 10460, "osm_n14064708968": 10478, "osm_n13381123758": 10560, "osm_n3778861787": 11052, "osm_n14058409029": 11123, "osm_n8907277818": 11146, "osm_n5162910441": 11212, "osm_n13381123759": 11394, "osm_n14064708967": 11466, "osm_n11750922029": 11496, "osm_n5604726917": 11511, "osm_n6390530105": 11524, "osm_n2169380700": 11939, "osm_n14058409030": 12136, "osm_n5162910442": 12334, "osm_n13230283736": 12380, "osm_n14072135590": 12542, "osm_n13381123770": 13013, "osm_n14058409031": 13122, "osm_n13817588094": 13369, "osm_n13381264373": 13783, "osm_n14058409032": 13893, "osm_n3778822187": 13903, "osm_n11281445852": 14095, "osm_n14072135591": 14797, "osm_n5163103599": 14811, "osm_n13381264374": 14852, "osm_n5162855462": 15227, "osm_n5194776019": 15409, "osm_n14061094940": 15770, "osm_n5163103601": 16003, "osm_n8738914819": 16944, "osm_n5163103600": 17270, "osm_n5163103597": 18158, "osm_n5163103598": 19069}</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
@@ -8966,72 +8966,76 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>pin is ~2026 m estimated walk (1535 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRT</t>
+          <t>pin is ~2019 m estimated walk (1529 m straight-line) from nearest target station; text mentions target metro osm_n14058409028: ایستگاه بی آر تی سبلان و خیابان دماوند</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>gaDjfQcR</t>
+          <t>gacDNliD</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://divar.ir/v/gaDjfQcR</t>
+          <t>https://divar.ir/v/gacDNliD</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>58 متری امام خمینی جیحون</t>
+          <t>40متر سوییت-خیابان دماوند-خیابان اشراقی</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>هاشمی</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>قاسم‌آباد</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>خ اشراقی</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>هاشمی</t>
+          <t>جوانمرد قصاب قدیمی; مبارک‌آباد بهشتی قدیمی; سبلان قدیمی; اراج قدیمی; پاتریس لومومبا قدیمی; سیزده آبان قدیمی; دولت‌آباد قدیمی; فیروزآبادی قدیمی; سرتخت قدیمی; شهید آوینی قدیمی; دیلمان قدیمی; قاسم‌آباد; شهادت قدیمی; طوس قدیمی; منصوریه (پل سیمان) قدیمی; ملک‌آباد قدیمی; ابن بابویه قدیمی; صفائیه (چشمه علی) قدیمی; شبیری قدیمی; صالح‌آباد شرقی قدیمی; ظهیرآباد قدیمی; حسن‌آباد باقرفر قدیمی</t>
         </is>
       </c>
       <c r="I37" t="b">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>500000000</v>
+        <v>80000000</v>
       </c>
       <c r="K37" t="n">
-        <v>14000000</v>
+        <v>13000000</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>1396</v>
+        <v>1372</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2 از 4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -9040,35 +9044,41 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>۱۳ مهر ۱۴۰۵، ۲۲:۵۳</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr"/>
+          <t>۲ آبان ۱۴۰۵، ۱۹:۰۷</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>۹ آبان ۱۴۰۵، ۱۳:۰۹</t>
+        </is>
+      </c>
       <c r="X37" t="n">
-        <v>35.686547897133</v>
+        <v>35.70657667616874</v>
       </c>
       <c r="Y37" t="n">
-        <v>51.357473328431</v>
+        <v>51.47313823230235</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>EXACT_DATA_UNTYPED</t>
+          <t>FUZZY</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>APPROXIMATE</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>api_exact_pin</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr"/>
+          <t>api_approximate</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>500</v>
+      </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>sections[6].widgets[0].data.location.exact_data.point</t>
+          <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
@@ -9076,10 +9086,10 @@
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="AJ37" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
@@ -9089,11 +9099,11 @@
       <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>osm_n14065977511</t>
+          <t>osm_n14058409028</t>
         </is>
       </c>
       <c r="AN37" t="n">
-        <v>1535</v>
+        <v>1529</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -9105,36 +9115,40 @@
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>osm_n14058409028</t>
+        </is>
+      </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>مترو و BRT</t>
+          <t>ایستگاه بی آر تی سبلان و خیابان دماوند</t>
         </is>
       </c>
       <c r="AS37" t="n">
-        <v>500000000</v>
+        <v>80000000</v>
       </c>
       <c r="AT37" t="n">
-        <v>14000000</v>
+        <v>13000000</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
+          <t>‏۸۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>‏۱۴,۰۰۰,۰۰۰ تومان</t>
+          <t>‏۱۳,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
+          <t>ودیعه: ۸۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>اجاره: ۱۴,۰۰۰,۰۰۰ تومان</t>
+          <t>اجاره: ۱۳,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -9150,16 +9164,238 @@
       <c r="BE37" t="inlineStr"/>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>2026-11-05T22:53:11.985088</t>
+          <t>2026-11-24T19:07:00.382395</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr"/>
       <c r="BH37" t="inlineStr">
         <is>
+          <t>{"osm_n14058409028": 1529, "osm_n5162910430": 1706, "osm_n14075125227": 1796, "osm_n14058409027": 1845, "osm_n5162910441": 2045, "osm_n14058409029": 2237, "osm_n2169732971": 2320, "osm_n13426743990": 2512, "osm_n5162910442": 2565, "osm_n14060820580": 2735, "osm_n6390530109": 2959, "osm_n14058409030": 3127, "osm_n14071125009": 3175, "osm_n5188341403": 3346, "osm_n14072135588": 3487, "osm_n8243426038": 3572, "osm_n3778821747": 3759, "osm_n14058409031": 3787, "osm_n14058409026": 3942, "osm_n14075125225": 4153, "osm_n3778861787": 4221, "osm_n14058409032": 4227, "sohrevardi": 4274, "darvazeh_dowlat": 4291, "taleghani": 4300, "haft_tir": 4363, "osm_n14059828792": 4393, "mofatteh": 4551, "saadi": 4638, "osm_n14058409025": 4653, "osm_n11750922029": 4710, "osm_n13284688255": 4904, "osm_n13202066659": 4910, "osm_n5163103599": 4911, "shahid_beheshti": 4943, "osm_n12659430599": 5211, "osm_n5186262276": 5260, "osm_n14059862414": 5269, "osm_n13279314257": 5386, "osm_n13381123730": 5563, "mirza_shirazi": 5582, "osm_n14071125007": 5767, "osm_n13817588094": 5769, "osm_n4396461099": 5943, "osm_n5163103601": 5949, "vali_asr": 5997, "jahad": 6044, "osm_n14072135590": 6045, "osm_n14058145515": 6123, "teatr_shahr": 6157, "osm_n5162855447": 6313, "osm_n660658572": 6325, "osm_n9149513248": 6614, "osm_n6737096941": 6741, "osm_n13381123759": 6802, "osm_n13381123758": 6918, "osm_n13381123745": 7007, "osm_n14058145514": 7019, "moniriyeh": 7050, "osm_w1169531671": 7055, "osm_n5163103600": 7156, "osm_n3778822187": 7283, "osm_n5162910431": 7312, "osm_n6444462277": 7333, "osm_n10746895093": 7604, "osm_n13380425834": 7627, "osm_n14058146709": 7855, "mahdieh": 7974, "osm_n2169380700": 8004, "osm_n13380425818": 8044, "osm_n14072135591": 8061, "osm_n8273593826": 8471, "osm_n5190423568": 8536, "osm_w671794339": 8570, "osm_n3635251445": 8590, "osm_n14075284474": 8610, "osm_n5165422503": 8618, "osm_n14075053790": 8621, "osm_n5165422504": 8709, "osm_n5190423570": 8861, "helal_ahmar": 8887, "osm_n13380425728": 9019, "beryanak": 9131, "osm_w1041344025": 9322, "osm_n14061094940": 9328, "osm_n13381123770": 9354, "osm_n12157511978": 9665, "osm_n14072135584": 9674, "osm_n6390530105": 9792, "osm_n5183625750": 9810, "osm_n5183513583": 10005, "osm_n13381264373": 10250, "osm_n8738914819": 10506, "osm_n14065977511": 10597, "osm_n5163103597": 10625, "osm_n8890549263": 10718, "osm_n14058145512": 10744, "osm_n14084275564": 10812, "osm_n14075284475": 10881, "osm_n5163103598": 11128, "osm_n13381264374": 11477, "osm_w1314615868": 11622, "osm_n14084275565": 11720, "osm_n14075284476": 11745, "osm_n14058145513": 11747, "osm_n13380418873": 11778, "osm_n14072135585": 11894, "osm_n5186234550": 12691, "osm_n14089610125": 12731, "osm_n5604727197": 12879, "osm_n11417054143": 13032, "osm_n14075284477": 13189, "osm_n8907277818": 13236, "osm_n14072135586": 13243, "osm_n11417054161": 13450, "osm_n5183520307": 13651, "osm_n5165462147": 13960, "osm_n14065945232": 14233, "osm_n13230313218": 14941, "osm_n10861347776": 15226, "osm_n5165462148": 15246, "osm_n5602579936": 15496, "osm_n14064336782": 16026, "osm_n14072135587": 16676, "osm_n14064708968": 17570, "osm_n11281445852": 17616, "osm_n14064708967": 18202, "osm_n13230283736": 18911, "osm_n5162855462": 19498, "osm_n5194776019": 20108, "osm_n5604726917": 20732}</t>
+        </is>
+      </c>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>*خیابان دماوند*         *خیابان اشراقی*
+لطفا اطلاعات آگهی را بخوانید اگر سوال دیگه بود در خدمتتون هستم
+40متر سوییت
+80متر پشت بام( در اختیار واحد)
+طبقه ۳
+رنگ و نقاشی شده
+مناسب دانشجو و یا مجرد موجه
+جای پارک موتور دارد
+دسترسی عالی به ایستگاه بی آر تی سبلان و خیابان دماوند
+دسترسی عالی به مراکز خرید
+قیمت:80میلیون پیش: 13میلیون اجاره( برای 1نفر)
+قیمت:80میلیون+15میلیون( برای 2 نفر)
+قابل تبدیل جزیی
+کمیسیون 12میلیون تومان
+( مشاور املاک)
+لطفا جهت بازدید از واحد تماس بگیرید</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NEEDS_LOCATION_VERIFICATION</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>pin is ~2026 m estimated walk (1535 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>gaDjfQcR</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://divar.ir/v/gaDjfQcR</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>58 متری امام خمینی جیحون</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>هاشمی</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>هاشمی</t>
+        </is>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="K38" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>58</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1396</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2 از 4</t>
+        </is>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>personal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>۱۳ مهر ۱۴۰۵، ۲۲:۵۳</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="n">
+        <v>35.686547897133</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>51.357473328431</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>EXACT_DATA_UNTYPED</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>api_exact_pin</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>sections[6].widgets[0].data.location.exact_data.point</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Excluded (&gt;1500 m)</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>osm_n14065977511</t>
+        </is>
+      </c>
+      <c r="AN38" t="n">
+        <v>1535</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Excluded (&gt;1500 m)</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>not routed (estimate only)</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>مترو و BRT</t>
+        </is>
+      </c>
+      <c r="AS38" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>‏۱۴,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>اجاره: ۱۴,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr">
+        <is>
+          <t>2026-11-05T22:53:11.985088</t>
+        </is>
+      </c>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr">
+        <is>
           <t>{"osm_n14065977511": 1535, "osm_n5183625750": 1677, "osm_w1314615868": 1913, "osm_n5165422504": 1996, "osm_n5190423570": 2121, "osm_n5165422503": 2138, "osm_n14058145512": 2155, "osm_n11417054143": 2457, "osm_w671794339": 2493, "beryanak": 2586, "osm_n5186234550": 2675, "osm_n14058146709": 2828, "osm_n14075053790": 2841, "osm_n11417054161": 3014, "helal_ahmar": 3396, "osm_n5183520307": 3496, "osm_n14058145513": 3514, "osm_n5162910431": 3552, "osm_n14058145514": 3759, "moniriyeh": 4033, "osm_n14084275564": 4047, "osm_w1041344025": 4076, "osm_w1169531671": 4190, "osm_n5604727197": 4214, "osm_n10746895093": 4286, "mahdieh": 4355, "teatr_shahr": 4616, "osm_n3635251445": 4719, "osm_n14058145515": 4760, "osm_n5190423568": 4776, "osm_n14084275565": 4810, "osm_n13230313218": 4968, "osm_n14072135584": 5157, "vali_asr": 5267, "osm_n8890549263": 5327, "osm_n14089610125": 5361, "osm_n14072135585": 5461, "osm_n4396461099": 5481, "osm_n5162855447": 5546, "osm_n14075284474": 5552, "osm_n6737096941": 5674, "osm_n5186262276": 5717, "osm_n13202066659": 5811, "osm_n5165462147": 5941, "jahad": 5957, "osm_n14072135586": 6020, "osm_n13279314257": 6050, "osm_n13380425834": 6065, "osm_n5602579936": 6078, "saadi": 6095, "osm_n14058409025": 6260, "darvazeh_dowlat": 6412, "osm_n14065945232": 6544, "taleghani": 6557, "osm_n13380425818": 6629, "osm_n10861347776": 6709, "osm_n14071125007": 6726, "osm_n5165462148": 6864, "osm_n14058409026": 6866, "haft_tir": 6986, "osm_n12157511978": 7023, "mirza_shirazi": 7098, "osm_n13380425728": 7260, "osm_n5188341403": 7339, "osm_n14059862414": 7380, "osm_n14075284475": 7605, "mofatteh": 7619, "osm_n14064336782": 7963, "shahid_beheshti": 7969, "osm_n8243426038": 8086, "osm_n14071125009": 8110, "osm_n14060820580": 8119, "osm_n6390530109": 8133, "osm_n13426743990": 8169, "osm_n13284688255": 8226, "osm_n5183513583": 8230, "osm_n12659430599": 8302, "osm_n14072135587": 8677, "sohrevardi": 8711, "osm_n13381123730": 8714, "osm_n9149513248": 8768, "osm_n14058409027": 8976, "osm_n2169732971": 8981, "osm_n14075284476": 8995, "osm_n6444462277": 9135, "osm_n660658572": 9309, "osm_n3778821747": 9325, "osm_n14059828792": 9705, "osm_n14064708968": 9806, "osm_n13381123745": 9961, "osm_n14075125227": 9982, "osm_n14075284477": 10092, "osm_n8273593826": 10161, "osm_n13380418873": 10185, "osm_n14058409028": 10284, "osm_n14075125225": 10537, "osm_n14072135588": 10616, "osm_n13381123758": 10685, "osm_n5604726917": 10801, "osm_n14064708967": 10805, "osm_n5162910430": 10840, "osm_n3778861787": 11371, "osm_n13381123759": 11551, "osm_n14058409029": 11563, "osm_n13230283736": 11723, "osm_n8907277818": 11751, "osm_n5162910441": 11819, "osm_n2169380700": 12031, "osm_n11750922029": 12179, "osm_n6390530105": 12232, "osm_n14058409030": 12559, "osm_n14072135590": 12790, "osm_n5162910442": 12922, "osm_n13381123770": 13052, "osm_n14058409031": 13552, "osm_n13381264373": 13793, "osm_n13817588094": 14050, "osm_n3778822187": 14126, "osm_n14058409032": 14344, "osm_n11281445852": 14579, "osm_n13381264374": 14827, "osm_n14072135591": 15010, "osm_n5163103599": 15283, "osm_n5162855462": 15645, "osm_n5194776019": 15792, "osm_n14061094940": 15946, "osm_n5163103601": 16497, "osm_n8738914819": 17102, "osm_n5163103600": 17780, "osm_n5163103597": 18385, "osm_n5163103598": 19321}</t>
         </is>
       </c>
-      <c r="BI37" t="inlineStr">
+      <c r="BI38" t="inlineStr">
         <is>
           <t>تخلیه جهت تحویل
 خ امام خمینی- بین یادگار امام و خ جیحون
@@ -9180,216 +9416,216 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>pin is ~2068 m estimated walk (1566 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و بی ارتی</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>gaIrfAUI</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaIrfAUI</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>آپارتمان۶۲متر۲خواب طبقه۳تمیزبازسازی سلیمانی حسینی</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>سلیمانی</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>خ حسینی</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>سلیمانی</t>
         </is>
       </c>
-      <c r="I38" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
         <v>400000000</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K39" t="n">
         <v>9700000</v>
       </c>
-      <c r="L38" t="b">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>62</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N39" t="n">
         <v>2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O39" t="n">
         <v>1387</v>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>3 از 4</t>
         </is>
       </c>
-      <c r="Q38" t="b">
-        <v>0</v>
-      </c>
-      <c r="R38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S38" t="b">
-        <v>1</v>
-      </c>
-      <c r="T38" t="n">
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
+      <c r="R39" t="b">
+        <v>0</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
         <v>4</v>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>personal</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>۱۸ مهر ۱۴۰۵، ۱۱:۰۲</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>۲۱ مهر ۱۴۰۵، ۱۱:۴۷</t>
         </is>
       </c>
-      <c r="X38" t="n">
+      <c r="X39" t="n">
         <v>35.669854119404</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Y39" t="n">
         <v>51.363940077382</v>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>api_exact_pin</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr">
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="n">
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="n">
         <v>2068</v>
       </c>
-      <c r="AJ38" t="n">
+      <c r="AJ39" t="n">
         <v>27.6</v>
       </c>
-      <c r="AK38" t="inlineStr">
+      <c r="AK39" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr">
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr">
         <is>
           <t>beryanak</t>
         </is>
       </c>
-      <c r="AN38" t="n">
+      <c r="AN39" t="n">
         <v>1566</v>
       </c>
-      <c r="AO38" t="inlineStr">
+      <c r="AO39" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP38" t="inlineStr">
+      <c r="AP39" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr">
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr">
         <is>
           <t>مترو و بی ارتی</t>
         </is>
       </c>
-      <c r="AS38" t="n">
+      <c r="AS39" t="n">
         <v>400000000</v>
       </c>
-      <c r="AT38" t="n">
+      <c r="AT39" t="n">
         <v>9700000</v>
       </c>
-      <c r="AU38" t="inlineStr">
+      <c r="AU39" t="inlineStr">
         <is>
           <t>‏۴۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV38" t="inlineStr">
+      <c r="AV39" t="inlineStr">
         <is>
           <t>‏۹,۷۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AW38" t="inlineStr">
+      <c r="AW39" t="inlineStr">
         <is>
           <t>ودیعه: ۴۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
+      <c r="AX39" t="inlineStr">
         <is>
           <t>اجاره: ۹,۷۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr"/>
-      <c r="BA38" t="inlineStr"/>
-      <c r="BB38" t="inlineStr"/>
-      <c r="BC38" t="inlineStr"/>
-      <c r="BD38" t="inlineStr">
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE38" t="inlineStr"/>
-      <c r="BF38" t="inlineStr">
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr">
         <is>
           <t>2026-11-10T11:02:57.843605</t>
         </is>
       </c>
-      <c r="BG38" t="inlineStr"/>
-      <c r="BH38" t="inlineStr">
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr">
         <is>
           <t>{"beryanak": 1566, "osm_n5190423570": 1937, "helal_ahmar": 2106, "osm_n14084275564": 2109, "osm_n5165422504": 2438, "osm_w1041344025": 2449, "osm_n14084275565": 2879, "osm_n5165422503": 3093, "osm_n14058146709": 3208, "mahdieh": 3215, "osm_n3635251445": 3262, "osm_n5183625750": 3399, "osm_n14065977511": 3460, "osm_n14089610125": 3518, "moniriyeh": 3628, "osm_n11417054143": 3703, "osm_w671794339": 3715, "osm_n14058145514": 3727, "osm_w1314615868": 3802, "osm_n14058145512": 4087, "osm_n14075053790": 4221, "osm_n5165462147": 4287, "osm_n5162910431": 4331, "osm_n11417054161": 4361, "osm_n5186234550": 4365, "osm_n14058145515": 4552, "osm_n6737096941": 4696, "osm_n13380425834": 4750, "osm_n5162855447": 4774, "osm_n4396461099": 4911, "osm_n5183520307": 5008, "teatr_shahr": 5111, "osm_w1169531671": 5148, "osm_n13380425818": 5178, "osm_n5165462148": 5374, "osm_n5186262276": 5433, "osm_n14058145513": 5457, "osm_n10746895093": 5523, "osm_n13380425728": 5617, "osm_n14071125007": 5862, "osm_n14058409025": 6035, "vali_asr": 6053, "saadi": 6056, "osm_n5604727197": 6103, "osm_n13202066659": 6103, "osm_n5190423568": 6318, "osm_n13230313218": 6446, "osm_n5183513583": 6471, "osm_n14059862414": 6555, "darvazeh_dowlat": 6624, "osm_n14058409026": 6734, "osm_n13279314257": 6798, "osm_n14072135584": 6902, "jahad": 6924, "taleghani": 6936, "osm_n14075284474": 7118, "osm_n8890549263": 7191, "osm_n5188341403": 7374, "osm_n13284688255": 7395, "osm_n12659430599": 7395, "osm_n14072135585": 7397, "osm_n9149513248": 7559, "haft_tir": 7572, "osm_n8243426038": 7623, "osm_n5602579936": 7706, "osm_n6444462277": 7799, "osm_n6390530109": 7869, "osm_n14072135586": 7958, "mirza_shirazi": 8062, "osm_n13426743990": 8232, "osm_n13380418873": 8331, "osm_n14060820580": 8366, "mofatteh": 8371, "osm_n14065945232": 8447, "osm_n10861347776": 8511, "osm_n14071125009": 8538, "osm_n8273593826": 8679, "osm_n2169732971": 8695, "osm_n12157511978": 8717, "shahid_beheshti": 8840, "osm_n14059828792": 8903, "osm_n14058409027": 9144, "osm_n14075284475": 9409, "sohrevardi": 9473, "osm_n14075125227": 9677, "osm_n13381123730": 9722, "osm_n14075125225": 9777, "osm_n14064336782": 9790, "osm_n8907277818": 9859, "osm_n3778821747": 10002, "osm_n660658572": 10437, "osm_n14072135587": 10493, "osm_n5162910430": 10525, "osm_n14058409028": 10556, "osm_n6390530105": 10686, "osm_n14075284476": 10817, "osm_n13381123745": 11169, "osm_n14072135588": 11229, "osm_n11750922029": 11396, "osm_n5162910441": 11501, "osm_n14064708968": 11626, "osm_n13381123758": 11842, "osm_n14058409029": 11899, "osm_n14075284477": 11969, "osm_n5604726917": 12042, "osm_n3778861787": 12065, "osm_n11281445852": 12635, "osm_n13381123759": 12636, "osm_n14064708967": 12647, "osm_n5162910442": 12680, "osm_n14058409030": 12941, "osm_n2169380700": 13252, "osm_n13817588094": 13266, "osm_n13230283736": 13571, "osm_n14072135590": 13658, "osm_n5162855462": 13727, "osm_n5194776019": 13898, "osm_n14058409031": 13903, "osm_n13381123770": 14372, "osm_n14058409032": 14621, "osm_n3778822187": 15049, "osm_n13381264373": 15165, "osm_n5163103599": 15483, "osm_n14072135591": 15952, "osm_n13381264374": 16260, "osm_n5163103601": 16610, "osm_n14061094940": 16973, "osm_n5163103600": 17829, "osm_n8738914819": 18165, "osm_n5163103597": 19284, "osm_n5163103598": 20157}</t>
         </is>
       </c>
-      <c r="BI38" t="inlineStr">
+      <c r="BI39" t="inlineStr">
         <is>
           <t>املاک
 همکار زنگ نزن
@@ -9439,218 +9675,218 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>pin is ~2089 m estimated walk (1583 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRTکمتر از 10دقیقه</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>gaCvBQsh</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaCvBQsh</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>۴۵متر/۱خواب/خوش نقشه/بالکن</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>سلیمانی</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>خ کاظمی</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>سلیمانی</t>
         </is>
       </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
         <v>500000000</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K40" t="n">
         <v>4000000</v>
       </c>
-      <c r="L39" t="b">
-        <v>1</v>
-      </c>
-      <c r="M39" t="n">
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
         <v>45</v>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
         <v>1388</v>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q39" t="b">
-        <v>0</v>
-      </c>
-      <c r="R39" t="b">
-        <v>0</v>
-      </c>
-      <c r="S39" t="b">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" t="inlineStr">
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
+      <c r="R40" t="b">
+        <v>0</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="inlineStr">
         <is>
           <t>premium-panel</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>۱۲ مهر ۱۴۰۵، ۱۸:۴۶</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="n">
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="n">
         <v>35.67519959430987</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="Y40" t="n">
         <v>51.36349141614174</v>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>FUZZY</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>APPROXIMATE</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>api_approximate</t>
         </is>
       </c>
-      <c r="AC39" t="n">
+      <c r="AC40" t="n">
         <v>500</v>
       </c>
-      <c r="AD39" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
         </is>
       </c>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="n">
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="n">
         <v>2089</v>
       </c>
-      <c r="AJ39" t="n">
+      <c r="AJ40" t="n">
         <v>27.9</v>
       </c>
-      <c r="AK39" t="inlineStr">
+      <c r="AK40" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr">
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr">
         <is>
           <t>beryanak</t>
         </is>
       </c>
-      <c r="AN39" t="n">
+      <c r="AN40" t="n">
         <v>1583</v>
       </c>
-      <c r="AO39" t="inlineStr">
+      <c r="AO40" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP39" t="inlineStr">
+      <c r="AP40" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ39" t="inlineStr"/>
-      <c r="AR39" t="inlineStr">
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr">
         <is>
           <t>مترو و BRTکمتر از 10دقیقه</t>
         </is>
       </c>
-      <c r="AS39" t="n">
+      <c r="AS40" t="n">
         <v>500000000</v>
       </c>
-      <c r="AT39" t="n">
+      <c r="AT40" t="n">
         <v>4000000</v>
       </c>
-      <c r="AU39" t="inlineStr">
+      <c r="AU40" t="inlineStr">
         <is>
           <t>RENT_SLIDER credit.value=500000000</t>
         </is>
       </c>
-      <c r="AV39" t="inlineStr">
+      <c r="AV40" t="inlineStr">
         <is>
           <t>RENT_SLIDER rent.value=4000000</t>
         </is>
       </c>
-      <c r="AW39" t="inlineStr">
+      <c r="AW40" t="inlineStr">
         <is>
           <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>اجاره: ۴,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr">
+      <c r="AY40" t="inlineStr">
         <is>
           <t>credit 600000000 / rent None</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr"/>
-      <c r="BA39" t="inlineStr"/>
-      <c r="BB39" t="inlineStr"/>
-      <c r="BC39" t="inlineStr"/>
-      <c r="BD39" t="inlineStr">
+      <c r="AZ40" t="inlineStr"/>
+      <c r="BA40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE39" t="inlineStr"/>
-      <c r="BF39" t="inlineStr">
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr">
         <is>
           <t>2026-11-04T18:46:52.775659</t>
         </is>
       </c>
-      <c r="BG39" t="inlineStr"/>
-      <c r="BH39" t="inlineStr">
+      <c r="BG40" t="inlineStr"/>
+      <c r="BH40" t="inlineStr">
         <is>
           <t>{"beryanak": 1583, "osm_n5190423570": 1645, "osm_n5165422504": 2011, "helal_ahmar": 2288, "osm_n5165422503": 2592, "osm_n14084275564": 2675, "osm_n5183625750": 2806, "osm_w1041344025": 2812, "osm_n14058146709": 2838, "osm_n14065977511": 2871, "osm_w671794339": 3183, "osm_w1314615868": 3263, "osm_n11417054143": 3359, "mahdieh": 3362, "osm_n14084275565": 3473, "osm_n14058145514": 3490, "osm_n14058145512": 3499, "moniriyeh": 3507, "osm_n3635251445": 3551, "osm_n14075053790": 3671, "osm_n5162910431": 3896, "osm_n5186234550": 3900, "osm_n11417054161": 4001, "osm_n14089610125": 4107, "osm_n14058145515": 4388, "osm_n5183520307": 4605, "osm_w1169531671": 4686, "teatr_shahr": 4757, "osm_n6737096941": 4803, "osm_n5162855447": 4805, "osm_n5165462147": 4835, "osm_n4396461099": 4873, "osm_n14058145513": 4887, "osm_n13380425834": 4993, "osm_n10746895093": 5008, "osm_n5186262276": 5308, "osm_n13380425818": 5482, "osm_n5604727197": 5569, "vali_asr": 5638, "osm_n5190423568": 5755, "osm_n13202066659": 5815, "saadi": 5862, "osm_n5165462148": 5884, "osm_n14058409025": 5898, "osm_n14071125007": 5939, "osm_n13380425728": 6011, "osm_n13230313218": 6065, "osm_n14072135584": 6314, "darvazeh_dowlat": 6364, "osm_n13279314257": 6399, "jahad": 6475, "osm_n14075284474": 6554, "osm_n14058409026": 6575, "osm_n8890549263": 6596, "osm_n14059862414": 6624, "taleghani": 6632, "osm_n14072135585": 6809, "osm_n5183513583": 6923, "osm_n5188341403": 7170, "haft_tir": 7218, "osm_n5602579936": 7279, "osm_n14072135586": 7394, "osm_n13284688255": 7471, "osm_n12659430599": 7498, "osm_n8243426038": 7575, "mirza_shirazi": 7619, "osm_n6390530109": 7759, "osm_n9149513248": 7776, "osm_n14065945232": 7907, "mofatteh": 7980, "osm_n10861347776": 8019, "osm_n13426743990": 8025, "osm_n6444462277": 8067, "osm_n14060820580": 8108, "osm_n12157511978": 8137, "osm_n14071125009": 8231, "shahid_beheshti": 8422, "osm_n2169732971": 8597, "osm_n14075284475": 8817, "osm_n13380418873": 8836, "osm_n14058409027": 8912, "osm_n14059828792": 8976, "osm_n8273593826": 9009, "sohrevardi": 9084, "osm_n13381123730": 9275, "osm_n14064336782": 9288, "osm_n14075125227": 9589, "osm_n3778821747": 9636, "osm_n14075125225": 9839, "osm_n660658572": 9964, "osm_n14072135587": 9996, "osm_n14075284476": 10224, "osm_n14058409028": 10300, "osm_n8907277818": 10387, "osm_n5162910430": 10444, "osm_n13381123745": 10681, "osm_n14072135588": 10884, "osm_n6390530105": 11046, "osm_n14064708968": 11128, "osm_n13381123758": 11366, "osm_n14075284477": 11374, "osm_n5162910441": 11424, "osm_n11750922029": 11471, "osm_n14058409029": 11630, "osm_n3778861787": 11701, "osm_n5604726917": 11758, "osm_n14064708967": 12139, "osm_n13381123759": 12177, "osm_n5162910442": 12582, "osm_n14058409030": 12661, "osm_n2169380700": 12763, "osm_n13230283736": 13061, "osm_n11281445852": 13220, "osm_n14072135590": 13253, "osm_n13817588094": 13346, "osm_n14058409031": 13634, "osm_n13381123770": 13864, "osm_n5162855462": 14322, "osm_n14058409032": 14374, "osm_n5194776019": 14493, "osm_n3778822187": 14632, "osm_n13381264373": 14647, "osm_n5163103599": 15260, "osm_n14072135591": 15532, "osm_n13381264374": 15730, "osm_n5163103601": 16414, "osm_n14061094940": 16533, "osm_n5163103600": 17653, "osm_n8738914819": 17718, "osm_n5163103597": 18878, "osm_n5163103598": 19767}</t>
         </is>
       </c>
-      <c r="BI39" t="inlineStr">
+      <c r="BI40" t="inlineStr">
         <is>
           <t>...هوالرزاق...
 رهن و اجاره آپارتمان:
@@ -9666,222 +9902,222 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>pin is ~2153 m estimated walk (1631 m straight-line) from nearest target station; text mentions target metro jahad: مترو جهاد</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>ga2m-38Q</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>https://divar.ir/v/ga2m-38Q</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>تا 80 متر/یوسف‌آباد/امیرآباد/فاطمی</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>یوسف‌آباد</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>خ جهان‌آرا</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>یوسف‌آباد</t>
         </is>
       </c>
-      <c r="I40" t="b">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
         <v>300000000</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K41" t="n">
         <v>1000</v>
       </c>
-      <c r="L40" t="b">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>70</v>
       </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" t="n">
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
         <v>1380</v>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>1 از 5</t>
         </is>
       </c>
-      <c r="Q40" t="b">
-        <v>1</v>
-      </c>
-      <c r="R40" t="b">
-        <v>1</v>
-      </c>
-      <c r="S40" t="b">
-        <v>1</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" t="inlineStr">
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="b">
+        <v>1</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="inlineStr">
         <is>
           <t>premium-panel</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>۴ مهر ۱۴۰۵، ۱۶:۱۷</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>۴ آبان ۱۴۰۵، ۰۹:۵۸</t>
         </is>
       </c>
-      <c r="X40" t="n">
+      <c r="X41" t="n">
         <v>35.737869963268</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="Y41" t="n">
         <v>51.403844842472</v>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>FUZZY</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>APPROXIMATE</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>api_approximate</t>
         </is>
       </c>
-      <c r="AC40" t="n">
+      <c r="AC41" t="n">
         <v>500</v>
       </c>
-      <c r="AD40" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
         </is>
       </c>
-      <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="n">
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="n">
         <v>2153</v>
       </c>
-      <c r="AJ40" t="n">
+      <c r="AJ41" t="n">
         <v>28.7</v>
       </c>
-      <c r="AK40" t="inlineStr">
+      <c r="AK41" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr">
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr">
         <is>
           <t>mirza_shirazi</t>
         </is>
       </c>
-      <c r="AN40" t="n">
+      <c r="AN41" t="n">
         <v>1631</v>
       </c>
-      <c r="AO40" t="inlineStr">
+      <c r="AO41" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP40" t="inlineStr">
+      <c r="AP41" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ40" t="inlineStr">
+      <c r="AQ41" t="inlineStr">
         <is>
           <t>jahad</t>
         </is>
       </c>
-      <c r="AR40" t="inlineStr">
+      <c r="AR41" t="inlineStr">
         <is>
           <t>مترو جهاد</t>
         </is>
       </c>
-      <c r="AS40" t="n">
+      <c r="AS41" t="n">
         <v>300000000</v>
       </c>
-      <c r="AT40" t="n">
+      <c r="AT41" t="n">
         <v>1000</v>
       </c>
-      <c r="AU40" t="inlineStr">
+      <c r="AU41" t="inlineStr">
         <is>
           <t>‏۳۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV40" t="inlineStr">
+      <c r="AV41" t="inlineStr">
         <is>
           <t>‏۱,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AW40" t="inlineStr">
+      <c r="AW41" t="inlineStr">
         <is>
           <t>ودیعه: ۳۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
+      <c r="AX41" t="inlineStr">
         <is>
           <t>اجاره: ۱,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr"/>
-      <c r="BA40" t="inlineStr"/>
-      <c r="BB40" t="inlineStr"/>
-      <c r="BC40" t="inlineStr"/>
-      <c r="BD40" t="inlineStr">
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE40" t="inlineStr"/>
-      <c r="BF40" t="inlineStr">
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr">
         <is>
           <t>2026-11-26T16:17:44.514498</t>
         </is>
       </c>
-      <c r="BG40" t="inlineStr"/>
-      <c r="BH40" t="inlineStr">
+      <c r="BG41" t="inlineStr"/>
+      <c r="BH41" t="inlineStr">
         <is>
           <t>{"mirza_shirazi": 1631, "jahad": 1969, "osm_n14075284474": 1990, "osm_n13381123730": 2167, "shahid_beheshti": 2247, "osm_n660658572": 2368, "osm_n5190423568": 2493, "osm_n12157511978": 2512, "mofatteh": 2626, "osm_n13279314257": 2697, "osm_n10746895093": 2856, "osm_n13381123745": 2901, "vali_asr": 2939, "sohrevardi": 3063, "osm_n14072135584": 3083, "haft_tir": 3191, "osm_w1169531671": 3344, "osm_n13381123758": 3656, "osm_n14075284475": 3723, "osm_n3778821747": 3766, "taleghani": 3938, "osm_n8890549263": 4023, "teatr_shahr": 4073, "osm_n14071125009": 4078, "osm_n5162910431": 4208, "osm_n14075053790": 4247, "osm_n13202066659": 4270, "darvazeh_dowlat": 4505, "osm_n13381123759": 4583, "osm_n14075284476": 4683, "osm_w671794339": 4686, "osm_n14060820580": 4770, "osm_n14072135588": 4929, "osm_n2169380700": 4955, "osm_n14072135585": 5228, "osm_n5188341403": 5272, "osm_n5165422503": 5284, "saadi": 5290, "osm_n3778861787": 5296, "osm_n14058146709": 5416, "osm_n5183625750": 5458, "osm_n14058409027": 5468, "osm_n13426743990": 5468, "osm_n14058145514": 5625, "osm_n14058409026": 5714, "osm_n14058145512": 5735, "osm_n14058145515": 5781, "osm_n14058409025": 5881, "osm_n14058409028": 5882, "osm_n14058145513": 5958, "osm_n5186262276": 5980, "osm_n5165422504": 5990, "osm_n13381123770": 6001, "osm_n14065977511": 6006, "osm_n14072135590": 6142, "osm_n14075284477": 6165, "moniriyeh": 6311, "osm_n14072135586": 6571, "osm_n14058409029": 6603, "osm_n6390530109": 6611, "osm_n5190423570": 6642, "osm_n4396461099": 6735, "osm_w1314615868": 6786, "osm_n13381264373": 6789, "osm_n5604727197": 6928, "osm_n2169732971": 7116, "osm_n14058409030": 7264, "osm_n8243426038": 7274, "osm_n5162855447": 7287, "osm_n3778822187": 7323, "beryanak": 7498, "osm_n14065945232": 7572, "osm_n5186234550": 7676, "osm_n14075125227": 7782, "mahdieh": 7872, "osm_n6737096941": 7877, "osm_n13381264374": 7902, "helal_ahmar": 7940, "osm_n14071125007": 7958, "osm_n14059862414": 8134, "osm_n14072135591": 8155, "osm_n14058409031": 8213, "osm_n5162910430": 8395, "osm_n5183520307": 8516, "osm_n11417054143": 8565, "osm_n13284688255": 8595, "osm_n11417054161": 8675, "osm_n3635251445": 8731, "osm_n10861347776": 8759, "osm_w1041344025": 8843, "osm_n12659430599": 8898, "osm_n14061094940": 8973, "osm_n13380425834": 8994, "osm_n5162910441": 9112, "osm_n14058409032": 9136, "osm_n14064336782": 9300, "osm_n13230313218": 9397, "osm_n14059828792": 9398, "osm_n5602579936": 9463, "osm_n5162910442": 9700, "osm_n13380425818": 9736, "osm_n14075125225": 9814, "osm_n14084275564": 9869, "osm_n14072135587": 9880, "osm_n8738914819": 10087, "osm_n5163103599": 10214, "osm_n9149513248": 10254, "osm_n14064708968": 10656, "osm_n13380425728": 10842, "osm_n14084275565": 10890, "osm_n6444462277": 10980, "osm_n11750922029": 11115, "osm_n14064708967": 11182, "osm_n5163103597": 11533, "osm_n5163103601": 11579, "osm_n14089610125": 11752, "osm_n13230283736": 11837, "osm_n5183513583": 12082, "osm_n8273593826": 12339, "osm_n5163103598": 12545, "osm_n13817588094": 12626, "osm_n5165462147": 12654, "osm_n5163103600": 12957, "osm_n5165462148": 13746, "osm_n13380418873": 14283, "osm_n6390530105": 14315, "osm_n5604726917": 14627, "osm_n8907277818": 15980, "osm_n11281445852": 19789, "osm_n5162855462": 21270, "osm_n5194776019": 21616}</t>
         </is>
       </c>
-      <c r="BI40" t="inlineStr">
+      <c r="BI41" t="inlineStr">
         <is>
           <t>⏫️فرصتی محدود برای تجربه حس آرامش⏫️    
     ✳️  املاک ارگ ، معمار رویاهای شما ✳️
@@ -9902,212 +10138,212 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>pin is ~2160 m estimated walk (1637 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و مراکز خرید عالی نورگیر فوقال</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>gafziAqx</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gafziAqx</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>رهن اجاره ۴۰ متر آپارتمان حاجیان انتهای جیحون</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>سلیمانی</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>خ خواجه زاده</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>سلیمانی</t>
         </is>
       </c>
-      <c r="I41" t="b">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
         <v>400000000</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K42" t="n">
         <v>10000000</v>
       </c>
-      <c r="L41" t="b">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
+      <c r="L42" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>40</v>
       </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" t="n">
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
         <v>1385</v>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>همکف از 3</t>
         </is>
       </c>
-      <c r="Q41" t="b">
-        <v>0</v>
-      </c>
-      <c r="R41" t="b">
-        <v>0</v>
-      </c>
-      <c r="S41" t="b">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
         <v>7</v>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>premium-panel</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>۴ آبان ۱۴۰۵، ۱۶:۳۲</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="n">
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="n">
         <v>35.678418180103</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="Y42" t="n">
         <v>51.362307036737</v>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>api_exact_pin</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr">
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
-      <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="n">
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="n">
         <v>2160</v>
       </c>
-      <c r="AJ41" t="n">
+      <c r="AJ42" t="n">
         <v>28.8</v>
       </c>
-      <c r="AK41" t="inlineStr">
+      <c r="AK42" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr">
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr">
         <is>
           <t>osm_n5190423570</t>
         </is>
       </c>
-      <c r="AN41" t="n">
+      <c r="AN42" t="n">
         <v>1637</v>
       </c>
-      <c r="AO41" t="inlineStr">
+      <c r="AO42" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP41" t="inlineStr">
+      <c r="AP42" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ41" t="inlineStr"/>
-      <c r="AR41" t="inlineStr">
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr">
         <is>
           <t>مترو و مراکز خرید عالی نورگیر فوقال</t>
         </is>
       </c>
-      <c r="AS41" t="n">
+      <c r="AS42" t="n">
         <v>400000000</v>
       </c>
-      <c r="AT41" t="n">
+      <c r="AT42" t="n">
         <v>10000000</v>
       </c>
-      <c r="AU41" t="inlineStr">
+      <c r="AU42" t="inlineStr">
         <is>
           <t>‏۴۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV41" t="inlineStr">
+      <c r="AV42" t="inlineStr">
         <is>
           <t>‏۱۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AW41" t="inlineStr">
+      <c r="AW42" t="inlineStr">
         <is>
           <t>ودیعه: ۴۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
+      <c r="AX42" t="inlineStr">
         <is>
           <t>اجاره: ۱۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr"/>
-      <c r="BA41" t="inlineStr"/>
-      <c r="BB41" t="inlineStr"/>
-      <c r="BC41" t="inlineStr"/>
-      <c r="BD41" t="inlineStr">
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE41" t="inlineStr"/>
-      <c r="BF41" t="inlineStr">
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr">
         <is>
           <t>2026-11-26T16:32:03.398844</t>
         </is>
       </c>
-      <c r="BG41" t="inlineStr"/>
-      <c r="BH41" t="inlineStr">
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="inlineStr">
         <is>
           <t>{"osm_n5190423570": 1637, "beryanak": 1774, "osm_n5165422504": 1869, "osm_n5165422503": 2363, "osm_n5183625750": 2456, "osm_n14065977511": 2498, "helal_ahmar": 2535, "osm_n14058146709": 2726, "osm_w1314615868": 2904, "osm_w671794339": 2915, "osm_n14084275564": 3048, "osm_n11417054143": 3111, "osm_w1041344025": 3126, "osm_n14058145512": 3126, "osm_n14075053790": 3380, "osm_n14058145514": 3469, "moniriyeh": 3564, "mahdieh": 3574, "osm_n5186234550": 3577, "osm_n5162910431": 3716, "osm_n11417054161": 3739, "osm_n3635251445": 3829, "osm_n14084275565": 3843, "osm_n5183520307": 4315, "osm_n14058145515": 4408, "osm_n14089610125": 4457, "osm_w1169531671": 4477, "osm_n14058145513": 4515, "teatr_shahr": 4637, "osm_n10746895093": 4750, "osm_n5162855447": 4941, "osm_n4396461099": 4968, "osm_n6737096941": 4981, "osm_n5165462147": 5148, "osm_n5604727197": 5209, "osm_n13380425834": 5240, "osm_n5186262276": 5345, "osm_n5190423568": 5445, "vali_asr": 5466, "osm_n13202066659": 5739, "osm_n13380425818": 5757, "osm_n13230313218": 5782, "saadi": 5851, "osm_n14058409025": 5924, "osm_n14072135584": 5971, "osm_n14071125007": 6094, "osm_n5165462148": 6165, "osm_n8890549263": 6233, "osm_n13279314257": 6236, "osm_n14075284474": 6241, "jahad": 6271, "darvazeh_dowlat": 6304, "osm_n13380425728": 6324, "osm_n14072135585": 6436, "taleghani": 6540, "osm_n14058409026": 6584, "osm_n14059862414": 6772, "osm_n5602579936": 6968, "osm_n14072135586": 7023, "haft_tir": 7088, "osm_n5188341403": 7147, "osm_n5183513583": 7259, "mirza_shirazi": 7417, "osm_n14065945232": 7544, "osm_n13284688255": 7621, "osm_n8243426038": 7652, "osm_n12659430599": 7663, "osm_n10861347776": 7676, "osm_n6390530109": 7796, "osm_n12157511978": 7803, "mofatteh": 7819, "osm_n13426743990": 7998, "osm_n9149513248": 8002, "osm_n14060820580": 8044, "osm_n14071125009": 8133, "shahid_beheshti": 8240, "osm_n6444462277": 8319, "osm_n14075284475": 8465, "osm_n2169732971": 8639, "osm_n14058409027": 8865, "sohrevardi": 8923, "osm_n14064336782": 8940, "osm_n13381123730": 9068, "osm_n14059828792": 9121, "osm_n13380418873": 9191, "osm_n8273593826": 9290, "osm_n3778821747": 9492, "osm_n14075125227": 9636, "osm_n14072135587": 9650, "osm_n660658572": 9735, "osm_n14075284476": 9869, "osm_n14075125225": 9976, "osm_n14058409028": 10234, "osm_n13381123745": 10437, "osm_n5162910430": 10493, "osm_n8907277818": 10750, "osm_n14072135588": 10753, "osm_n14064708968": 10782, "osm_n14075284477": 11010, "osm_n13381123758": 11133, "osm_n6390530105": 11340, "osm_n5162910441": 11474, "osm_n5604726917": 11522, "osm_n14058409029": 11552, "osm_n3778861787": 11555, "osm_n11750922029": 11613, "osm_n14064708967": 11788, "osm_n13381123759": 11958, "osm_n2169380700": 12519, "osm_n14058409030": 12576, "osm_n5162910442": 12618, "osm_n13230283736": 12709, "osm_n14072135590": 13075, "osm_n13817588094": 13488, "osm_n14058409031": 13555, "osm_n11281445852": 13593, "osm_n13381123770": 13601, "osm_n14058409032": 14310, "osm_n13381264373": 14375, "osm_n3778822187": 14445, "osm_n5162855462": 14690, "osm_n5194776019": 14857, "osm_n5163103599": 15211, "osm_n14072135591": 15341, "osm_n13381264374": 15447, "osm_n14061094940": 16327, "osm_n5163103601": 16382, "osm_n8738914819": 17505, "osm_n5163103600": 17634, "osm_n5163103597": 18696, "osm_n5163103598": 19597}</t>
         </is>
       </c>
-      <c r="BI41" t="inlineStr">
+      <c r="BI42" t="inlineStr">
         <is>
           <t>۳ طبقه ۲ واحدی
 ۱ خواب مستر
@@ -10121,216 +10357,216 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>pin is ~2164 m estimated walk (1639 m straight-line) from nearest target station; text mentions target metro osm_n8907277818: مترو و میدان شهرری</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>gaTjTH1c</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaTjTH1c</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>45متر/ بیات(شهرری)/داماک</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>شهرری</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>خ بیات</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>شهرری; ظهیرآباد قدیمی</t>
         </is>
       </c>
-      <c r="I42" t="b">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>400000000</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K43" t="n">
         <v>11000000</v>
       </c>
-      <c r="L42" t="b">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
+      <c r="L43" t="b">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>45</v>
       </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
         <v>1396</v>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q42" t="b">
-        <v>0</v>
-      </c>
-      <c r="R42" t="b">
-        <v>0</v>
-      </c>
-      <c r="S42" t="b">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" t="inlineStr">
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
+      <c r="R43" t="b">
+        <v>0</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="inlineStr">
         <is>
           <t>premium-panel</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>۲۵ مهر ۱۴۰۵، ۱۲:۳۱</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="n">
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="n">
         <v>35.591002247027</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="Y43" t="n">
         <v>51.43977131839</v>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>api_exact_pin</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr">
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="n">
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="n">
         <v>2164</v>
       </c>
-      <c r="AJ42" t="n">
+      <c r="AJ43" t="n">
         <v>28.9</v>
       </c>
-      <c r="AK42" t="inlineStr">
+      <c r="AK43" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr">
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr">
         <is>
           <t>osm_n8907277818</t>
         </is>
       </c>
-      <c r="AN42" t="n">
+      <c r="AN43" t="n">
         <v>1639</v>
       </c>
-      <c r="AO42" t="inlineStr">
+      <c r="AO43" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP42" t="inlineStr">
+      <c r="AP43" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ42" t="inlineStr">
+      <c r="AQ43" t="inlineStr">
         <is>
           <t>osm_n8907277818</t>
         </is>
       </c>
-      <c r="AR42" t="inlineStr">
+      <c r="AR43" t="inlineStr">
         <is>
           <t>مترو و میدان شهرری</t>
         </is>
       </c>
-      <c r="AS42" t="n">
+      <c r="AS43" t="n">
         <v>400000000</v>
       </c>
-      <c r="AT42" t="n">
+      <c r="AT43" t="n">
         <v>11000000</v>
       </c>
-      <c r="AU42" t="inlineStr">
+      <c r="AU43" t="inlineStr">
         <is>
           <t>‏۴۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV42" t="inlineStr">
+      <c r="AV43" t="inlineStr">
         <is>
           <t>‏۱۱,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AW42" t="inlineStr">
+      <c r="AW43" t="inlineStr">
         <is>
           <t>ودیعه: ۴۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
+      <c r="AX43" t="inlineStr">
         <is>
           <t>اجاره: ۱۱,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr"/>
-      <c r="BA42" t="inlineStr"/>
-      <c r="BB42" t="inlineStr"/>
-      <c r="BC42" t="inlineStr"/>
-      <c r="BD42" t="inlineStr">
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
+      <c r="BA43" t="inlineStr"/>
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="inlineStr"/>
+      <c r="BD43" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE42" t="inlineStr"/>
-      <c r="BF42" t="inlineStr">
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="inlineStr">
         <is>
           <t>2026-11-17T12:31:06.449723</t>
         </is>
       </c>
-      <c r="BG42" t="inlineStr"/>
-      <c r="BH42" t="inlineStr">
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr">
         <is>
           <t>{"osm_n8907277818": 1639, "osm_n13380418873": 2803, "osm_n6390530105": 3797, "osm_n8273593826": 4743, "osm_n5183513583": 4815, "osm_n11281445852": 5028, "osm_n13380425728": 5977, "osm_n6444462277": 6002, "osm_n9149513248": 6774, "osm_n13380425818": 6990, "osm_n5162855462": 7080, "osm_n13380425834": 7738, "osm_n5194776019": 7906, "osm_n12659430599": 8289, "osm_n3635251445": 8512, "osm_n13284688255": 8632, "osm_n14084275565": 8748, "osm_n14059862414": 8755, "osm_n14071125007": 8756, "osm_n6737096941": 8799, "osm_n14059828792": 8808, "osm_n14089610125": 8935, "osm_w1041344025": 8940, "osm_n14084275564": 9093, "osm_n14075125225": 9179, "mahdieh": 9223, "osm_n5162855447": 9373, "osm_n11750922029": 9545, "osm_n5165462147": 9621, "helal_ahmar": 9773, "osm_n4396461099": 9917, "osm_n8243426038": 10201, "osm_n5165462148": 10285, "osm_n13817588094": 10391, "beryanak": 10568, "moniriyeh": 10599, "osm_n5186262276": 10688, "osm_n14058409025": 10889, "osm_n14058145515": 10911, "osm_n6390530109": 11040, "osm_n2169732971": 11167, "osm_n14058409026": 11283, "osm_n14058145514": 11335, "osm_n5190423570": 11402, "osm_n14075125227": 11406, "saadi": 11462, "osm_n5162910430": 11692, "osm_n5188341403": 12011, "osm_n14058146709": 12032, "osm_n5165422504": 12058, "osm_n5162910441": 12131, "darvazeh_dowlat": 12358, "osm_n13426743990": 12399, "osm_n13202066659": 12431, "teatr_shahr": 12650, "osm_n5165422503": 12802, "osm_n5162910431": 12976, "taleghani": 12977, "osm_n14060820580": 13131, "osm_n5162910442": 13138, "osm_n14058409027": 13182, "osm_w671794339": 13438, "osm_w1169531671": 13692, "vali_asr": 13729, "osm_n14071125009": 13863, "haft_tir": 13906, "osm_n5183625750": 13927, "osm_n14075053790": 13978, "osm_n13279314257": 13998, "osm_n14065977511": 14316, "osm_n14058409028": 14336, "osm_n10746895093": 14510, "jahad": 14682, "osm_n11417054143": 14714, "mofatteh": 14877, "osm_w1314615868": 14880, "osm_n14058145512": 14921, "mirza_shirazi": 15371, "osm_n11417054161": 15376, "osm_n14058409029": 15422, "osm_n5186234550": 15492, "shahid_beheshti": 15566, "sohrevardi": 15589, "osm_n3778821747": 15611, "osm_n5190423568": 15797, "osm_n5183520307": 16076, "osm_n14072135588": 16162, "osm_n14058409030": 16317, "osm_n14058145513": 16399, "osm_n14075284474": 16491, "osm_n13381123730": 16641, "osm_n14058409031": 16844, "osm_n14072135584": 16848, "osm_n14058409032": 17004, "osm_n3778861787": 17073, "osm_n5604727197": 17183, "osm_n5163103599": 17244, "osm_n13230313218": 17454, "osm_n8890549263": 17520, "osm_n660658572": 17598, "osm_n5163103601": 17638, "osm_n14072135585": 18090, "osm_n5163103600": 18227, "osm_n12157511978": 18242, "osm_n13381123745": 18467, "osm_n5602579936": 18785, "osm_n13381123758": 18798, "osm_n14072135586": 18903, "osm_n14072135590": 19007, "osm_n13381123759": 19131, "osm_n14075284475": 19293, "osm_n14065945232": 19503, "osm_n10861347776": 19639, "osm_n2169380700": 20205, "osm_n3778822187": 20360, "osm_n14075284476": 20671, "osm_n14064336782": 20913, "osm_n14072135591": 21191, "osm_n13381123770": 21587, "osm_n14072135587": 21620, "osm_n14075284477": 22059, "osm_n14061094940": 22449, "osm_n13381264373": 22512, "osm_n5604726917": 22571, "osm_n14064708968": 22753, "osm_n8738914819": 23655, "osm_n14064708967": 23766, "osm_n13381264374": 23768, "osm_n5163103597": 23810, "osm_n5163103598": 24245, "osm_n13230283736": 24687}</t>
         </is>
       </c>
-      <c r="BI42" t="inlineStr">
+      <c r="BI43" t="inlineStr">
         <is>
           <t>کار خوبه خدا درست کنه........
 آپارتمان نقلی و تمیز برای شما عزیزان 
@@ -10343,216 +10579,216 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>pin is ~2309 m estimated walk (1749 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و اتوبوس و سواری</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>gaDzeQZr</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>https://divar.ir/v/gaDzeQZr</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>مرتضوی ۵۵ متر</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>هاشمی</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>خ مرتضوی</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>هاشمی</t>
         </is>
       </c>
-      <c r="I43" t="b">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
         <v>360000000</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K44" t="n">
         <v>15500000</v>
       </c>
-      <c r="L43" t="b">
-        <v>1</v>
-      </c>
-      <c r="M43" t="n">
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
         <v>55</v>
       </c>
-      <c r="N43" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" t="n">
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
         <v>1385</v>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>3 از 4</t>
         </is>
       </c>
-      <c r="Q43" t="b">
-        <v>0</v>
-      </c>
-      <c r="R43" t="b">
-        <v>0</v>
-      </c>
-      <c r="S43" t="b">
-        <v>1</v>
-      </c>
-      <c r="T43" t="n">
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
+      <c r="R44" t="b">
+        <v>0</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
         <v>3</v>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>personal</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>۱۳ مهر ۱۴۰۵، ۲۱:۵۸</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="n">
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="n">
         <v>35.683196891759</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="Y44" t="n">
         <v>51.360837831994</v>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>EXACT_DATA_UNTYPED</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>api_exact_pin</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr">
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.exact_data.point</t>
         </is>
       </c>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="n">
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="n">
         <v>2309</v>
       </c>
-      <c r="AJ43" t="n">
+      <c r="AJ44" t="n">
         <v>30.8</v>
       </c>
-      <c r="AK43" t="inlineStr">
+      <c r="AK44" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr">
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr">
         <is>
           <t>osm_n5190423570</t>
         </is>
       </c>
-      <c r="AN43" t="n">
+      <c r="AN44" t="n">
         <v>1749</v>
       </c>
-      <c r="AO43" t="inlineStr">
+      <c r="AO44" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP43" t="inlineStr">
+      <c r="AP44" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ43" t="inlineStr"/>
-      <c r="AR43" t="inlineStr">
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr">
         <is>
           <t>مترو و اتوبوس و سواری</t>
         </is>
       </c>
-      <c r="AS43" t="n">
+      <c r="AS44" t="n">
         <v>360000000</v>
       </c>
-      <c r="AT43" t="n">
+      <c r="AT44" t="n">
         <v>15500000</v>
       </c>
-      <c r="AU43" t="inlineStr">
+      <c r="AU44" t="inlineStr">
         <is>
           <t>RENT_SLIDER credit.value=360000000</t>
         </is>
       </c>
-      <c r="AV43" t="inlineStr">
+      <c r="AV44" t="inlineStr">
         <is>
           <t>RENT_SLIDER rent.value=15500000</t>
         </is>
       </c>
-      <c r="AW43" t="inlineStr">
+      <c r="AW44" t="inlineStr">
         <is>
           <t>ودیعه: ۳۶۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
+      <c r="AX44" t="inlineStr">
         <is>
           <t>اجاره: ۱۵,۵۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr">
+      <c r="AY44" t="inlineStr">
         <is>
           <t>credit 760000000 / rent 1000000</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr"/>
-      <c r="BA43" t="inlineStr"/>
-      <c r="BB43" t="inlineStr"/>
-      <c r="BC43" t="inlineStr"/>
-      <c r="BD43" t="inlineStr">
+      <c r="AZ44" t="inlineStr"/>
+      <c r="BA44" t="inlineStr"/>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="inlineStr"/>
+      <c r="BD44" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE43" t="inlineStr"/>
-      <c r="BF43" t="inlineStr">
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="inlineStr">
         <is>
           <t>2026-11-05T21:58:52.818879</t>
         </is>
       </c>
-      <c r="BG43" t="inlineStr"/>
-      <c r="BH43" t="inlineStr">
+      <c r="BG44" t="inlineStr"/>
+      <c r="BH44" t="inlineStr">
         <is>
           <t>{"osm_n5190423570": 1749, "osm_n5165422504": 1762, "osm_n5183625750": 1947, "osm_n14065977511": 1951, "osm_n5165422503": 2080, "beryanak": 2127, "osm_w1314615868": 2393, "osm_w671794339": 2550, "osm_n14058145512": 2579, "osm_n14058146709": 2625, "osm_n11417054143": 2821, "helal_ahmar": 2929, "osm_n14075053790": 2969, "osm_n5186234550": 3138, "osm_n11417054161": 3412, "osm_n5162910431": 3484, "osm_n14058145514": 3485, "osm_n14084275564": 3593, "osm_w1041344025": 3596, "moniriyeh": 3691, "mahdieh": 3911, "osm_n5183520307": 3932, "osm_n14058145513": 3973, "osm_w1169531671": 4190, "osm_n3635251445": 4248, "osm_n10746895093": 4381, "osm_n14084275565": 4388, "osm_n14058145515": 4468, "teatr_shahr": 4487, "osm_n5604727197": 4693, "osm_n14089610125": 4984, "osm_n5190423568": 4992, "osm_n4396461099": 5129, "osm_n5162855447": 5161, "vali_asr": 5228, "osm_n6737096941": 5260, "osm_n13230313218": 5405, "osm_n5186262276": 5421, "osm_n14072135584": 5464, "osm_n13380425834": 5611, "osm_n5165462147": 5632, "osm_n13202066659": 5645, "osm_n8890549263": 5698, "osm_n14075284474": 5781, "saadi": 5854, "osm_n14072135585": 5888, "jahad": 5979, "osm_n14058409025": 5980, "osm_n13279314257": 6007, "osm_n13380425818": 6164, "darvazeh_dowlat": 6231, "osm_n14071125007": 6334, "taleghani": 6419, "osm_n14072135586": 6484, "osm_n5602579936": 6541, "osm_n5165462148": 6609, "osm_n14058409026": 6611, "osm_n13380425728": 6783, "haft_tir": 6905, "osm_n14059862414": 6998, "osm_n14065945232": 7020, "osm_n5188341403": 7123, "mirza_shirazi": 7125, "osm_n10861347776": 7189, "osm_n12157511978": 7310, "mofatteh": 7587, "osm_n5183513583": 7749, "osm_n8243426038": 7771, "osm_n13284688255": 7845, "osm_n6390530109": 7857, "osm_n12659430599": 7909, "osm_n14075284475": 7945, "osm_n14060820580": 7957, "osm_n13426743990": 7964, "shahid_beheshti": 7973, "osm_n14071125009": 7993, "osm_n9149513248": 8334, "osm_n14064336782": 8443, "osm_n6444462277": 8686, "sohrevardi": 8687, "osm_n2169732971": 8704, "osm_n13381123730": 8762, "osm_n14058409027": 8800, "osm_n14072135587": 9157, "osm_n3778821747": 9280, "osm_n14059828792": 9334, "osm_n14075284476": 9345, "osm_n660658572": 9396, "osm_n8273593826": 9697, "osm_n14075125227": 9705, "osm_n13380418873": 9707, "osm_n13381123745": 10075, "osm_n14058409028": 10137, "osm_n14075125225": 10175, "osm_n14064708968": 10287, "osm_n14075284477": 10473, "osm_n14072135588": 10558, "osm_n5162910430": 10563, "osm_n13381123758": 10785, "osm_n5604726917": 11210, "osm_n8907277818": 11276, "osm_n14064708967": 11285, "osm_n3778861787": 11336, "osm_n14058409029": 11436, "osm_n5162910441": 11544, "osm_n13381123759": 11629, "osm_n6390530105": 11763, "osm_n11750922029": 11816, "osm_n2169380700": 12153, "osm_n13230283736": 12203, "osm_n14058409030": 12445, "osm_n5162910442": 12666, "osm_n14072135590": 12807, "osm_n13381123770": 13208, "osm_n14058409031": 13432, "osm_n13817588094": 13690, "osm_n13381264373": 13967, "osm_n11281445852": 14141, "osm_n3778822187": 14161, "osm_n14058409032": 14208, "osm_n13381264374": 15023, "osm_n14072135591": 15052, "osm_n5163103599": 15130, "osm_n5162855462": 15234, "osm_n5194776019": 15396, "osm_n14061094940": 16013, "osm_n5163103601": 16325, "osm_n8738914819": 17181, "osm_n5163103600": 17595, "osm_n5163103597": 18418, "osm_n5163103598": 19336}</t>
         </is>
       </c>
-      <c r="BI43" t="inlineStr">
+      <c r="BI44" t="inlineStr">
         <is>
           <t>بهترین موقعیت مکانی به مترو و اتوبوس و سواری 
 بر خیابان اصلی
@@ -10571,218 +10807,218 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>NEEDS_LOCATION_VERIFICATION</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>pin is ~2451 m estimated walk (1857 m straight-line) from nearest target station; text mentions target metro osm_n13381123759,osm_n14084275565: مترو شهرک شریعتی</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>ga-SE8m9</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>https://divar.ir/v/ga-SE8m9</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>اجاره واحد نقلی و شیک با قیمت باورنکردنی</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>شهرک شریعتی</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>خ صمدی</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>شهرک شریعتی</t>
         </is>
       </c>
-      <c r="I44" t="b">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
         <v>200000000</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K45" t="n">
         <v>14000000</v>
       </c>
-      <c r="L44" t="b">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
+      <c r="L45" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>55</v>
       </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" t="n">
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
         <v>1390</v>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q44" t="b">
-        <v>0</v>
-      </c>
-      <c r="R44" t="b">
-        <v>0</v>
-      </c>
-      <c r="S44" t="b">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
         <v>10</v>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>personal</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>۹ مهر ۱۴۰۵، ۱۵:۰۳</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="n">
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="n">
         <v>35.63064752797965</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="Y45" t="n">
         <v>51.38046095550556</v>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>FUZZY</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>APPROXIMATE</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>api_approximate</t>
         </is>
       </c>
-      <c r="AC44" t="n">
+      <c r="AC45" t="n">
         <v>500</v>
       </c>
-      <c r="AD44" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>sections[6].widgets[0].data.location.fuzzy_data.point</t>
         </is>
       </c>
-      <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="n">
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="n">
         <v>2451</v>
       </c>
-      <c r="AJ44" t="n">
+      <c r="AJ45" t="n">
         <v>32.7</v>
       </c>
-      <c r="AK44" t="inlineStr">
+      <c r="AK45" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr">
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr">
         <is>
           <t>osm_n14084275565</t>
         </is>
       </c>
-      <c r="AN44" t="n">
+      <c r="AN45" t="n">
         <v>1857</v>
       </c>
-      <c r="AO44" t="inlineStr">
+      <c r="AO45" t="inlineStr">
         <is>
           <t>Excluded (&gt;1500 m)</t>
         </is>
       </c>
-      <c r="AP44" t="inlineStr">
+      <c r="AP45" t="inlineStr">
         <is>
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ44" t="inlineStr">
+      <c r="AQ45" t="inlineStr">
         <is>
           <t>osm_n13381123759,osm_n14084275565</t>
         </is>
       </c>
-      <c r="AR44" t="inlineStr">
+      <c r="AR45" t="inlineStr">
         <is>
           <t>مترو شهرک شریعتی</t>
         </is>
       </c>
-      <c r="AS44" t="n">
+      <c r="AS45" t="n">
         <v>200000000</v>
       </c>
-      <c r="AT44" t="n">
+      <c r="AT45" t="n">
         <v>14000000</v>
       </c>
-      <c r="AU44" t="inlineStr">
+      <c r="AU45" t="inlineStr">
         <is>
           <t>‏۲۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AV44" t="inlineStr">
+      <c r="AV45" t="inlineStr">
         <is>
           <t>‏۱۴,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AW44" t="inlineStr">
+      <c r="AW45" t="inlineStr">
         <is>
           <t>ودیعه: ۲۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
+      <c r="AX45" t="inlineStr">
         <is>
           <t>اجاره: ۱۴,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
-      <c r="AZ44" t="inlineStr"/>
-      <c r="BA44" t="inlineStr"/>
-      <c r="BB44" t="inlineStr"/>
-      <c r="BC44" t="inlineStr"/>
-      <c r="BD44" t="inlineStr">
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
+      <c r="BA45" t="inlineStr"/>
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="inlineStr"/>
+      <c r="BD45" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="BE44" t="inlineStr"/>
-      <c r="BF44" t="inlineStr">
+      <c r="BE45" t="inlineStr"/>
+      <c r="BF45" t="inlineStr">
         <is>
           <t>2026-11-01T15:03:21.557936</t>
         </is>
       </c>
-      <c r="BG44" t="inlineStr"/>
-      <c r="BH44" t="inlineStr">
+      <c r="BG45" t="inlineStr"/>
+      <c r="BH45" t="inlineStr">
         <is>
           <t>{"osm_n14084275565": 1857, "osm_n14089610125": 2044, "osm_n14084275564": 2517, "osm_n5165462147": 3022, "osm_n5183513583": 3187, "osm_w1041344025": 3267, "osm_n13380425728": 3299, "osm_n3635251445": 3568, "osm_n13380425818": 3943, "osm_n5165462148": 4101, "helal_ahmar": 4171, "osm_n13380418873": 4204, "osm_n13380425834": 4264, "mahdieh": 4406, "beryanak": 4719, "osm_n6737096941": 5217, "osm_n8907277818": 5484, "osm_n5190423570": 5637, "osm_n5162855447": 5747, "moniriyeh": 5932, "osm_n6444462277": 6006, "osm_n14071125007": 6125, "osm_n8273593826": 6168, "osm_n9149513248": 6255, "osm_n4396461099": 6257, "osm_n5165422504": 6351, "osm_n14058145514": 6534, "osm_n14059862414": 6670, "osm_n14058146709": 6728, "osm_n14058145515": 6728, "osm_n12659430599": 7042, "osm_n5186262276": 7140, "osm_n5165422503": 7149, "osm_n13284688255": 7248, "osm_n14058409025": 7659, "osm_n6390530105": 7677, "osm_w671794339": 7837, "osm_n5183625750": 7886, "osm_n11417054143": 7913, "osm_n5162910431": 7917, "saadi": 8023, "osm_n11281445852": 8046, "osm_n14065977511": 8053, "teatr_shahr": 8165, "osm_n8243426038": 8326, "osm_n14058409026": 8350, "osm_w1314615868": 8388, "osm_n14075053790": 8398, "osm_n14059828792": 8497, "osm_n11417054161": 8563, "osm_n13202066659": 8621, "osm_n14058145512": 8682, "osm_w1169531671": 8774, "osm_n5186234550": 8821, "darvazeh_dowlat": 8896, "osm_n6390530109": 8960, "osm_n5188341403": 9171, "osm_n5162855462": 9264, "osm_n5183520307": 9291, "vali_asr": 9312, "osm_n14075125225": 9331, "osm_n10746895093": 9410, "taleghani": 9428, "osm_n5194776019": 9537, "osm_n2169732971": 9582, "osm_n13279314257": 9889, "osm_n13426743990": 9925, "osm_n14058145513": 10065, "haft_tir": 10303, "jahad": 10313, "osm_n14075125227": 10363, "osm_n14060820580": 10389, "osm_n5190423568": 10480, "osm_n13230313218": 10609, "osm_n5604727197": 10670, "osm_n11750922029": 10673, "osm_n14071125009": 10869, "osm_n14058409027": 10904, "osm_n5162910430": 11071, "osm_n14075284474": 11268, "mofatteh": 11271, "osm_n14072135584": 11272, "mirza_shirazi": 11325, "osm_n8890549263": 11694, "shahid_beheshti": 11886, "osm_n5162910441": 11930, "osm_n5602579936": 11982, "osm_n14072135585": 11988, "sohrevardi": 12281, "osm_n13817588094": 12354, "osm_n14058409028": 12355, "osm_n14072135586": 12562, "osm_n3778821747": 12614, "osm_n13381123730": 12920, "osm_n10861347776": 12970, "osm_n12157511978": 12977, "osm_n14065945232": 13018, "osm_n5162910442": 13166, "osm_n14072135588": 13624, "osm_n14058409029": 13702, "osm_n660658572": 13784, "osm_n14075284475": 13808, "osm_n14064336782": 14266, "osm_n3778861787": 14552, "osm_n13381123745": 14610, "osm_n14058409030": 14759, "osm_n14072135587": 14951, "osm_n13381123758": 15167, "osm_n14075284476": 15226, "osm_n14058409031": 15595, "osm_n5604726917": 15632, "osm_n13381123759": 15800, "osm_n14064708968": 16081, "osm_n14058409032": 16115, "osm_n14072135590": 16381, "osm_n14075284477": 16458, "osm_n2169380700": 16631, "osm_n5163103599": 16762, "osm_n14064708967": 17125, "osm_n5163103601": 17640, "osm_n3778822187": 17816, "osm_n13381123770": 17893, "osm_n13230283736": 18054, "osm_n5163103600": 18655, "osm_n14072135591": 18724, "osm_n13381264373": 18759, "osm_n14061094940": 19875, "osm_n13381264374": 19940, "osm_n8738914819": 21108, "osm_n5163103597": 21873, "osm_n5163103598": 22593}</t>
         </is>
       </c>
-      <c r="BI44" t="inlineStr">
+      <c r="BI45" t="inlineStr">
         <is>
           <t>یک واحد آپارتمان نقلی و تمیز واقع در شهرک شریعتی 
 خوش نقشه
@@ -10796,225 +11032,6 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>NEEDS_LOCATION_VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>pin is ~2502 m estimated walk (1896 m straight-line) from nearest target station; text mentions target metro osm_n8907277818: مترو و میدان شهرری و مرکز خرید و</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>gaP78RSH</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>https://divar.ir/v/gaP78RSH</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>آپارتمان نقلی  ۴۵ متری</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>شهرری</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>خ یوسفی نژاد</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>شهرری; ظهیرآباد قدیمی</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="K45" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="L45" t="b">
-        <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>45</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1396</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>3 از 3</t>
-        </is>
-      </c>
-      <c r="Q45" t="b">
-        <v>0</v>
-      </c>
-      <c r="R45" t="b">
-        <v>0</v>
-      </c>
-      <c r="S45" t="b">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2</v>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>personal</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>۲۲ مهر ۱۴۰۵، ۲۲:۱۷</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="n">
-        <v>35.589479654655</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>51.442158251762</v>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>EXACT_DATA_UNTYPED</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>api_exact_pin</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>sections[6].widgets[0].data.location.exact_data.point</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="n">
-        <v>2502</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Excluded (&gt;1500 m)</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>osm_n8907277818</t>
-        </is>
-      </c>
-      <c r="AN45" t="n">
-        <v>1896</v>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Excluded (&gt;1500 m)</t>
-        </is>
-      </c>
-      <c r="AP45" t="inlineStr">
-        <is>
-          <t>not routed (estimate only)</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>osm_n8907277818</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>مترو و میدان شهرری و مرکز خرید و</t>
-        </is>
-      </c>
-      <c r="AS45" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>RENT_SLIDER credit.value=500000000</t>
-        </is>
-      </c>
-      <c r="AV45" t="inlineStr">
-        <is>
-          <t>RENT_SLIDER rent.value=8000000</t>
-        </is>
-      </c>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>اجاره: ۸,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>credit 400000000 / rent 11000000</t>
-        </is>
-      </c>
-      <c r="AZ45" t="inlineStr"/>
-      <c r="BA45" t="inlineStr"/>
-      <c r="BB45" t="inlineStr"/>
-      <c r="BC45" t="inlineStr"/>
-      <c r="BD45" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="BE45" t="inlineStr"/>
-      <c r="BF45" t="inlineStr">
-        <is>
-          <t>2026-11-14T22:17:40.758013</t>
-        </is>
-      </c>
-      <c r="BG45" t="inlineStr"/>
-      <c r="BH45" t="inlineStr">
-        <is>
-          <t>{"osm_n8907277818": 1896, "osm_n13380418873": 3073, "osm_n6390530105": 3820, "osm_n8273593826": 4879, "osm_n5183513583": 5065, "osm_n11281445852": 5076, "osm_n6444462277": 6160, "osm_n13380425728": 6217, "osm_n9149513248": 6933, "osm_n5162855462": 7127, "osm_n13380425818": 7218, "osm_n13380425834": 7965, "osm_n5194776019": 7966, "osm_n12659430599": 8447, "osm_n3635251445": 8761, "osm_n13284688255": 8790, "osm_n14059828792": 8926, "osm_n14059862414": 8934, "osm_n14071125007": 8950, "osm_n6737096941": 9018, "osm_n14084275565": 9021, "osm_w1041344025": 9198, "osm_n14089610125": 9209, "osm_n14075125225": 9274, "osm_n14084275564": 9363, "mahdieh": 9464, "osm_n5162855447": 9587, "osm_n11750922029": 9595, "osm_n5165462147": 9893, "helal_ahmar": 10026, "osm_n4396461099": 10128, "osm_n8243426038": 10359, "osm_n13817588094": 10395, "osm_n5165462148": 10550, "beryanak": 10824, "moniriyeh": 10831, "osm_n5186262276": 10892, "osm_n14058409025": 11082, "osm_n14058145515": 11129, "osm_n6390530109": 11198, "osm_n2169732971": 11307, "osm_n14058409026": 11465, "osm_n14075125227": 11525, "osm_n14058145514": 11566, "osm_n5190423570": 11654, "saadi": 11658, "osm_n5162910430": 11794, "osm_n5188341403": 12186, "osm_n5162910441": 12214, "osm_n14058146709": 12272, "osm_n5165422504": 12307, "darvazeh_dowlat": 12550, "osm_n13426743990": 12561, "osm_n13202066659": 12632, "teatr_shahr": 12868, "osm_n5165422503": 13049, "taleghani": 13168, "osm_n5162910442": 13205, "osm_n5162910431": 13208, "osm_n14060820580": 13297, "osm_n14058409027": 13333, "osm_w671794339": 13682, "osm_w1169531671": 13919, "vali_asr": 13942, "osm_n14071125009": 14034, "haft_tir": 14095, "osm_n5183625750": 14180, "osm_n13279314257": 14201, "osm_n14075053790": 14221, "osm_n14058409028": 14472, "osm_n14065977511": 14575, "osm_n10746895093": 14739, "jahad": 14890, "osm_n11417054143": 14984, "mofatteh": 15063, "osm_w1314615868": 15143, "osm_n14058145512": 15178, "osm_n14058409029": 15544, "mirza_shirazi": 15568, "osm_n11417054161": 15646, "shahid_beheshti": 15752, "osm_n5186234550": 15759, "sohrevardi": 15764, "osm_n3778821747": 15776, "osm_n5190423568": 16029, "osm_n14072135588": 16309, "osm_n5183520307": 16345, "osm_n14058409030": 16430, "osm_n14058145513": 16658, "osm_n14075284474": 16720, "osm_n13381123730": 16825, "osm_n14058409031": 16944, "osm_n14072135584": 17086, "osm_n14058409032": 17090, "osm_n3778861787": 17217, "osm_n5163103599": 17314, "osm_n5604727197": 17445, "osm_n5163103601": 17688, "osm_n13230313218": 17725, "osm_n8890549263": 17764, "osm_n660658572": 17783, "osm_n5163103600": 18258, "osm_n14072135585": 18341, "osm_n12157511978": 18469, "osm_n13381123745": 18651, "osm_n13381123758": 18974, "osm_n5602579936": 19055, "osm_n14072135590": 19150, "osm_n14072135586": 19160, "osm_n13381123759": 19297, "osm_n14075284475": 19525, "osm_n14065945232": 19764, "osm_n10861347776": 19905, "osm_n2169380700": 20377, "osm_n3778822187": 20497, "osm_n14075284476": 20901, "osm_n14064336782": 21178, "osm_n14072135591": 21324, "osm_n13381123770": 21760, "osm_n14072135587": 21885, "osm_n14075284477": 22293, "osm_n14061094940": 22583, "osm_n13381264373": 22686, "osm_n5604726917": 22846, "osm_n14064708968": 23018, "osm_n8738914819": 23787, "osm_n5163103597": 23919, "osm_n13381264374": 23943, "osm_n14064708967": 24030, "osm_n5163103598": 24343, "osm_n13230283736": 24951}</t>
-        </is>
-      </c>
-      <c r="BI45" t="inlineStr">
-        <is>
-          <t>آپارتمان نقلی در بهترین لوکیشن شهرری با دسترسی آسان به مترو و میدان شهرری و مرکز خرید و...</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -11023,33 +11040,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pin is ~2554 m estimated walk (1935 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRT️✅</t>
+          <t>pin is ~2502 m estimated walk (1896 m straight-line) from nearest target station; text mentions target metro osm_n8907277818: مترو و میدان شهرری و مرکز خرید و</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>gaAv6nsI</t>
+          <t>gaP78RSH</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://divar.ir/v/gaAv6nsI</t>
+          <t>https://divar.ir/v/gaP78RSH</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>اجاره ۵۵متر/انباری /بالکن /pموتور/ تک واحدی</t>
+          <t>آپارتمان نقلی  ۴۵ متری</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>سلیمانی</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>شهرری</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>خ یوسفی نژاد</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>سلیمانی; شبیری قدیمی</t>
+          <t>شهرری; ظهیرآباد قدیمی</t>
         </is>
       </c>
       <c r="I46" t="b">
@@ -11059,53 +11080,53 @@
         <v>500000000</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="L46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N46" t="n">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>1389</v>
+        <v>1396</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 از 3</t>
         </is>
       </c>
       <c r="Q46" t="b">
         <v>0</v>
       </c>
       <c r="R46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>premium-panel</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>۱۱ مهر ۱۴۰۵، ۱۰:۵۳</t>
+          <t>۲۲ مهر ۱۴۰۵، ۲۲:۱۷</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
-        <v>35.671277607959</v>
+        <v>35.589479654655</v>
       </c>
       <c r="Y46" t="n">
-        <v>51.359515433265</v>
+        <v>51.442158251762</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -11133,10 +11154,10 @@
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>2554</v>
+        <v>2502</v>
       </c>
       <c r="AJ46" t="n">
-        <v>34.1</v>
+        <v>33.4</v>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
@@ -11146,11 +11167,11 @@
       <c r="AL46" t="inlineStr"/>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>beryanak</t>
+          <t>osm_n8907277818</t>
         </is>
       </c>
       <c r="AN46" t="n">
-        <v>1935</v>
+        <v>1896</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -11162,26 +11183,30 @@
           <t>not routed (estimate only)</t>
         </is>
       </c>
-      <c r="AQ46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>osm_n8907277818</t>
+        </is>
+      </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>مترو و BRT️✅</t>
+          <t>مترو و میدان شهرری و مرکز خرید و</t>
         </is>
       </c>
       <c r="AS46" t="n">
         <v>500000000</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
+          <t>RENT_SLIDER credit.value=500000000</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>رایگان</t>
+          <t>RENT_SLIDER rent.value=8000000</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
@@ -11191,10 +11216,14 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>رهن کامل</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>اجاره: ۸,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>credit 400000000 / rent 11000000</t>
+        </is>
+      </c>
       <c r="AZ46" t="inlineStr"/>
       <c r="BA46" t="inlineStr"/>
       <c r="BB46" t="inlineStr"/>
@@ -11207,16 +11236,223 @@
       <c r="BE46" t="inlineStr"/>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>2026-11-03T10:53:41.236539</t>
+          <t>2026-11-14T22:17:40.758013</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr"/>
       <c r="BH46" t="inlineStr">
         <is>
+          <t>{"osm_n8907277818": 1896, "osm_n13380418873": 3073, "osm_n6390530105": 3820, "osm_n8273593826": 4879, "osm_n5183513583": 5065, "osm_n11281445852": 5076, "osm_n6444462277": 6160, "osm_n13380425728": 6217, "osm_n9149513248": 6933, "osm_n5162855462": 7127, "osm_n13380425818": 7218, "osm_n13380425834": 7965, "osm_n5194776019": 7966, "osm_n12659430599": 8447, "osm_n3635251445": 8761, "osm_n13284688255": 8790, "osm_n14059828792": 8926, "osm_n14059862414": 8934, "osm_n14071125007": 8950, "osm_n6737096941": 9018, "osm_n14084275565": 9021, "osm_w1041344025": 9198, "osm_n14089610125": 9209, "osm_n14075125225": 9274, "osm_n14084275564": 9363, "mahdieh": 9464, "osm_n5162855447": 9587, "osm_n11750922029": 9595, "osm_n5165462147": 9893, "helal_ahmar": 10026, "osm_n4396461099": 10128, "osm_n8243426038": 10359, "osm_n13817588094": 10395, "osm_n5165462148": 10550, "beryanak": 10824, "moniriyeh": 10831, "osm_n5186262276": 10892, "osm_n14058409025": 11082, "osm_n14058145515": 11129, "osm_n6390530109": 11198, "osm_n2169732971": 11307, "osm_n14058409026": 11465, "osm_n14075125227": 11525, "osm_n14058145514": 11566, "osm_n5190423570": 11654, "saadi": 11658, "osm_n5162910430": 11794, "osm_n5188341403": 12186, "osm_n5162910441": 12214, "osm_n14058146709": 12272, "osm_n5165422504": 12307, "darvazeh_dowlat": 12550, "osm_n13426743990": 12561, "osm_n13202066659": 12632, "teatr_shahr": 12868, "osm_n5165422503": 13049, "taleghani": 13168, "osm_n5162910442": 13205, "osm_n5162910431": 13208, "osm_n14060820580": 13297, "osm_n14058409027": 13333, "osm_w671794339": 13682, "osm_w1169531671": 13919, "vali_asr": 13942, "osm_n14071125009": 14034, "haft_tir": 14095, "osm_n5183625750": 14180, "osm_n13279314257": 14201, "osm_n14075053790": 14221, "osm_n14058409028": 14472, "osm_n14065977511": 14575, "osm_n10746895093": 14739, "jahad": 14890, "osm_n11417054143": 14984, "mofatteh": 15063, "osm_w1314615868": 15143, "osm_n14058145512": 15178, "osm_n14058409029": 15544, "mirza_shirazi": 15568, "osm_n11417054161": 15646, "shahid_beheshti": 15752, "osm_n5186234550": 15759, "sohrevardi": 15764, "osm_n3778821747": 15776, "osm_n5190423568": 16029, "osm_n14072135588": 16309, "osm_n5183520307": 16345, "osm_n14058409030": 16430, "osm_n14058145513": 16658, "osm_n14075284474": 16720, "osm_n13381123730": 16825, "osm_n14058409031": 16944, "osm_n14072135584": 17086, "osm_n14058409032": 17090, "osm_n3778861787": 17217, "osm_n5163103599": 17314, "osm_n5604727197": 17445, "osm_n5163103601": 17688, "osm_n13230313218": 17725, "osm_n8890549263": 17764, "osm_n660658572": 17783, "osm_n5163103600": 18258, "osm_n14072135585": 18341, "osm_n12157511978": 18469, "osm_n13381123745": 18651, "osm_n13381123758": 18974, "osm_n5602579936": 19055, "osm_n14072135590": 19150, "osm_n14072135586": 19160, "osm_n13381123759": 19297, "osm_n14075284475": 19525, "osm_n14065945232": 19764, "osm_n10861347776": 19905, "osm_n2169380700": 20377, "osm_n3778822187": 20497, "osm_n14075284476": 20901, "osm_n14064336782": 21178, "osm_n14072135591": 21324, "osm_n13381123770": 21760, "osm_n14072135587": 21885, "osm_n14075284477": 22293, "osm_n14061094940": 22583, "osm_n13381264373": 22686, "osm_n5604726917": 22846, "osm_n14064708968": 23018, "osm_n8738914819": 23787, "osm_n5163103597": 23919, "osm_n13381264374": 23943, "osm_n14064708967": 24030, "osm_n5163103598": 24343, "osm_n13230283736": 24951}</t>
+        </is>
+      </c>
+      <c r="BI46" t="inlineStr">
+        <is>
+          <t>آپارتمان نقلی در بهترین لوکیشن شهرری با دسترسی آسان به مترو و میدان شهرری و مرکز خرید و...</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NEEDS_LOCATION_VERIFICATION</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>pin is ~2554 m estimated walk (1935 m straight-line) from nearest target station; text mentions an unnamed metro: مترو و BRT️✅</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>gaAv6nsI</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://divar.ir/v/gaAv6nsI</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>اجاره ۵۵متر/انباری /بالکن /pموتور/ تک واحدی</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>سلیمانی</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>سلیمانی; شبیری قدیمی</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>60</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1389</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
+      <c r="R47" t="b">
+        <v>1</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>premium-panel</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>۱۱ مهر ۱۴۰۵، ۱۰:۵۳</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="n">
+        <v>35.671277607959</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>51.359515433265</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>EXACT_DATA_UNTYPED</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>api_exact_pin</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>sections[6].widgets[0].data.location.exact_data.point</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="n">
+        <v>2554</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Excluded (&gt;1500 m)</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>beryanak</t>
+        </is>
+      </c>
+      <c r="AN47" t="n">
+        <v>1935</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Excluded (&gt;1500 m)</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>not routed (estimate only)</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>مترو و BRT️✅</t>
+        </is>
+      </c>
+      <c r="AS47" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>رایگان</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>رهن کامل</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
+      <c r="BA47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="inlineStr">
+        <is>
+          <t>2026-11-03T10:53:41.236539</t>
+        </is>
+      </c>
+      <c r="BG47" t="inlineStr"/>
+      <c r="BH47" t="inlineStr">
+        <is>
           <t>{"beryanak": 1935, "osm_n5190423570": 2167, "osm_n14084275564": 2436, "helal_ahmar": 2523, "osm_n5165422504": 2573, "osm_w1041344025": 2876, "osm_n14084275565": 3115, "osm_n5165422503": 3153, "osm_n14065977511": 3243, "osm_n5183625750": 3274, "osm_n11417054143": 3287, "osm_n14058146709": 3391, "osm_w1314615868": 3489, "mahdieh": 3629, "osm_n14089610125": 3658, "osm_n3635251445": 3692, "osm_w671794339": 3733, "osm_n14058145512": 3863, "osm_n11417054161": 3947, "moniriyeh": 3959, "osm_n5186234550": 3992, "osm_n14058145514": 3999, "osm_n14075053790": 4209, "osm_n5165462147": 4316, "osm_n5162910431": 4460, "osm_n5183520307": 4605, "osm_n14058145515": 4865, "osm_n6737096941": 5105, "osm_n5162855447": 5163, "osm_n13380425834": 5178, "osm_n14058145513": 5184, "osm_w1169531671": 5251, "osm_n4396461099": 5278, "teatr_shahr": 5309, "osm_n5165462148": 5337, "osm_n10746895093": 5563, "osm_n13380425818": 5607, "osm_n5186262276": 5766, "osm_n5604727197": 5777, "osm_n13230313218": 6035, "osm_n13380425728": 6036, "vali_asr": 6201, "osm_n14071125007": 6265, "osm_n5190423568": 6278, "osm_n13202066659": 6348, "saadi": 6356, "osm_n14058409025": 6363, "osm_n14072135584": 6792, "osm_n5183513583": 6871, "darvazeh_dowlat": 6887, "osm_n14059862414": 6957, "osm_n13279314257": 6960, "osm_n8890549263": 7022, "jahad": 7040, "osm_n14058409026": 7052, "osm_n14075284474": 7074, "osm_n14072135585": 7164, "taleghani": 7171, "osm_n5602579936": 7309, "osm_n14072135586": 7669, "osm_n5188341403": 7670, "haft_tir": 7772, "osm_n13284688255": 7799, "osm_n12659430599": 7805, "osm_n9149513248": 7987, "osm_n8243426038": 7989, "osm_n14065945232": 8124, "osm_n10861347776": 8147, "mirza_shirazi": 8184, "osm_n6390530109": 8211, "osm_n6444462277": 8229, "osm_n13426743990": 8527, "mofatteh": 8540, "osm_n14060820580": 8631, "osm_n12157511978": 8631, "osm_n13380418873": 8701, "osm_n14071125009": 8772, "shahid_beheshti": 8986, "osm_n2169732971": 9042, "osm_n8273593826": 9107, "osm_n14075284475": 9275, "osm_n14059828792": 9307, "osm_n14058409027": 9425, "osm_n14064336782": 9431, "sohrevardi": 9645, "osm_n13381123730": 9840, "osm_n14075125227": 10029, "osm_n14072135587": 10131, "osm_n14075125225": 10179, "osm_n3778821747": 10193, "osm_n8907277818": 10210, "osm_n660658572": 10528, "osm_n14075284476": 10675, "osm_n14058409028": 10823, "osm_n5162910430": 10880, "osm_n6390530105": 11109, "osm_n13381123745": 11241, "osm_n14064708968": 11264, "osm_n14072135588": 11436, "osm_n5604726917": 11614, "osm_n14075284477": 11793, "osm_n11750922029": 11802, "osm_n5162910441": 11858, "osm_n13381123758": 11929, "osm_n14058409029": 12159, "osm_n3778861787": 12257, "osm_n14064708967": 12291, "osm_n13381123759": 12741, "osm_n11281445852": 12894, "osm_n5162910442": 13029, "osm_n14058409030": 13194, "osm_n13230283736": 13217, "osm_n2169380700": 13323, "osm_n13817588094": 13673, "osm_n14072135590": 13816, "osm_n5162855462": 13939, "osm_n5194776019": 14085, "osm_n14058409031": 14163, "osm_n13381123770": 14418, "osm_n14058409032": 14895, "osm_n3778822187": 15196, "osm_n13381264373": 15197, "osm_n5163103599": 15771, "osm_n14072135591": 16097, "osm_n13381264374": 16274, "osm_n5163103601": 16913, "osm_n14061094940": 17098, "osm_n5163103600": 18142, "osm_n8738914819": 18283, "osm_n5163103597": 19441, "osm_n5163103598": 20328}</t>
         </is>
       </c>
-      <c r="BI46" t="inlineStr">
+      <c r="BI47" t="inlineStr">
         <is>
           <t>✅مشاورین آلفا ✅
         ✅آپارتمان۵۵متر  خوش نقشه تخلیه️✅
@@ -11250,217 +11486,6 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>NEEDS_LOCATION_VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>pin is ~2982 m estimated walk (2259 m straight-line) from nearest target station; text mentions an unnamed metro: مترو اتوبوس نانوایی هایپر و غیره</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>gaibuU9i</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>https://divar.ir/v/gaibuU9i</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>اجاره آپارتمان ۲۵ متری</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>اوقاف</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>کنارگذر مظفری نیا</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>اوقاف</t>
-        </is>
-      </c>
-      <c r="I47" t="b">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="K47" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="L47" t="b">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>25</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1385</v>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q47" t="b">
-        <v>0</v>
-      </c>
-      <c r="R47" t="b">
-        <v>0</v>
-      </c>
-      <c r="S47" t="b">
-        <v>1</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>personal</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>۷ آبان ۱۴۰۵، ۰۹:۵۳</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="n">
-        <v>35.753025904894</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>51.520065764008</v>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>EXACT_DATA_UNTYPED</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>api_exact_pin</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr"/>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>sections[6].widgets[0].data.location.exact_data.point</t>
-        </is>
-      </c>
-      <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="n">
-        <v>2982</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Excluded (&gt;1500 m)</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>osm_n5163103599</t>
-        </is>
-      </c>
-      <c r="AN47" t="n">
-        <v>2259</v>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Excluded (&gt;1500 m)</t>
-        </is>
-      </c>
-      <c r="AP47" t="inlineStr">
-        <is>
-          <t>not routed (estimate only)</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr"/>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>مترو اتوبوس نانوایی هایپر و غیره</t>
-        </is>
-      </c>
-      <c r="AS47" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>‏۱۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AV47" t="inlineStr">
-        <is>
-          <t>‏۱۵,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>ودیعه: ۱۰۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>اجاره: ۱۵,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr"/>
-      <c r="BA47" t="inlineStr"/>
-      <c r="BB47" t="inlineStr"/>
-      <c r="BC47" t="inlineStr"/>
-      <c r="BD47" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="BE47" t="inlineStr"/>
-      <c r="BF47" t="inlineStr">
-        <is>
-          <t>2026-11-29T09:53:31.972577</t>
-        </is>
-      </c>
-      <c r="BG47" t="inlineStr"/>
-      <c r="BH47" t="inlineStr">
-        <is>
-          <t>{"osm_n5163103599": 2259, "osm_n14058409032": 2474, "osm_n5163103601": 2682, "osm_n14058409031": 2982, "osm_n5163103600": 3548, "osm_n14058409030": 3919, "osm_n14072135591": 4713, "osm_n3778822187": 4731, "osm_n14072135590": 4963, "osm_n14058409029": 4970, "osm_n5163103597": 5093, "osm_n5163103598": 5098, "osm_n3778861787": 5337, "osm_n14061094940": 5534, "osm_n14072135588": 5896, "osm_n8738914819": 6182, "osm_n5162910442": 6321, "osm_n14058409028": 6331, "osm_n13381123759": 6946, "osm_n3778821747": 7209, "osm_n5162910441": 7294, "osm_n2169380700": 7713, "osm_n14058409027": 7786, "osm_n13381123758": 7821, "osm_n5162910430": 7842, "sohrevardi": 7901, "osm_n14071125009": 8350, "osm_n14075125227": 8353, "osm_n13381123770": 8381, "osm_n13381123730": 8458, "osm_n660658572": 8474, "osm_n13381123745": 8490, "osm_n14060820580": 8502, "osm_n13426743990": 8754, "shahid_beheshti": 8754, "osm_n13381264373": 8887, "mofatteh": 8916, "osm_n2169732971": 9000, "haft_tir": 9450, "osm_n5188341403": 9589, "osm_n6390530109": 9591, "osm_n13381264374": 9684, "mirza_shirazi": 9689, "osm_n13817588094": 9871, "taleghani": 9944, "osm_n11750922029": 9996, "darvazeh_dowlat": 10237, "osm_n8243426038": 10250, "osm_n14075125225": 10272, "osm_n14058409026": 10348, "osm_n13279314257": 10421, "jahad": 10702, "osm_n13202066659": 10762, "osm_n14059828792": 10787, "saadi": 10889, "osm_n14058409025": 11076, "vali_asr": 11199, "osm_n13284688255": 11549, "osm_n5186262276": 11667, "osm_n12659430599": 11838, "teatr_shahr": 11854, "osm_n14059862414": 11949, "osm_w1169531671": 12316, "osm_n14058145515": 12399, "osm_n14071125007": 12436, "osm_n4396461099": 12455, "osm_n10746895093": 12517, "osm_n14075284474": 12587, "osm_n12157511978": 12784, "osm_n5162910431": 12883, "osm_n5162855447": 12887, "osm_n5190423568": 12908, "osm_n14058145514": 13134, "osm_n9149513248": 13158, "moniriyeh": 13350, "osm_n6737096941": 13361, "osm_n14072135584": 13701, "osm_n14075284475": 13725, "osm_n14058146709": 13757, "osm_n6444462277": 13827, "osm_n14075053790": 13871, "osm_n14075284476": 13945, "osm_w671794339": 14025, "osm_n13380425834": 14294, "osm_n5165422503": 14297, "mahdieh": 14488, "osm_n5165422504": 14617, "osm_n8890549263": 14640, "osm_n13380425818": 14724, "osm_n8273593826": 14819, "osm_n5190423570": 14943, "osm_n14075284477": 15064, "osm_n3635251445": 15171, "osm_n5183625750": 15191, "helal_ahmar": 15296, "beryanak": 15397, "osm_n13380425728": 15691, "osm_n6390530105": 15755, "osm_n14072135585": 15835, "osm_w1041344025": 15842, "osm_n14058145512": 15873, "osm_n14065977511": 15925, "osm_n14058145513": 16454, "osm_n5183513583": 16645, "osm_w1314615868": 16886, "osm_n14072135586": 17158, "osm_n14084275564": 17312, "osm_n5604727197": 17493, "osm_n5186234550": 17904, "osm_n14065945232": 18148, "osm_n14084275565": 18266, "osm_n13380418873": 18312, "osm_n11417054143": 18537, "osm_n11417054161": 18817, "osm_n5183520307": 18826, "osm_n14089610125": 19277, "osm_n10861347776": 19370, "osm_n8907277818": 19672, "osm_n14064336782": 19821, "osm_n13230313218": 19886, "osm_n5602579936": 20070, "osm_n14072135587": 20346, "osm_n5165462147": 20480, "osm_n14064708968": 20991, "osm_n14064708967": 21338, "osm_n5165462148": 21757, "osm_n13230283736": 21838, "osm_n11281445852": 24081, "osm_n5604726917": 25250, "osm_n5162855462": 26017, "osm_n5194776019": 26667}</t>
-        </is>
-      </c>
-      <c r="BI47" t="inlineStr">
-        <is>
-          <t>آپارتمان نقلی سوئیت ۲۵ متری نبش خیابان سراج بعد از پل طرف استقلال پنجره بزرگ موقعیت عالی به مترو اتوبوس نانوایی هایپر و غیره</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
@@ -12676,43 +12701,43 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>no usable coordinates; text mentions an unnamed metro: مترو و BRT️✅</t>
+          <t>no usable coordinates (MISSING)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ga8a8R1G</t>
+          <t>gaCTG_5X</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://divar.ir/v/ga8a8R1G</t>
+          <t>https://divar.ir/v/gaCTG_5X</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>اجاره ۶۰متر /pموتور /بالکن /بازسازی شده</t>
+          <t>اجاره آپارتمان ۶۰ متری</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>جیحون</t>
+          <t>شهرک ولیعصر شمالی</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>جیحون</t>
+          <t>شهرک ولیعصر شمالی</t>
         </is>
       </c>
       <c r="I54" t="b">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>300000000</v>
+        <v>500000000</v>
       </c>
       <c r="K54" t="n">
-        <v>16000000</v>
+        <v>0</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
@@ -12724,36 +12749,40 @@
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>1387</v>
+        <v>1395</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4 از 4</t>
         </is>
       </c>
       <c r="Q54" t="b">
         <v>0</v>
       </c>
       <c r="R54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="b">
         <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>premium-panel</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>۸ مهر ۱۴۰۵، ۱۱:۵۲</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr"/>
+          <t>۱۲ مهر ۱۴۰۵، ۱۸:۰۸</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>۱۷ مهر ۱۴۰۵، ۱۲:۲۸</t>
+        </is>
+      </c>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
@@ -12782,35 +12811,31 @@
       <c r="AO54" t="inlineStr"/>
       <c r="AP54" t="inlineStr"/>
       <c r="AQ54" t="inlineStr"/>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>مترو و BRT️✅</t>
-        </is>
-      </c>
+      <c r="AR54" t="inlineStr"/>
       <c r="AS54" t="n">
-        <v>300000000</v>
+        <v>500000000</v>
       </c>
       <c r="AT54" t="n">
-        <v>16000000</v>
+        <v>0</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>‏۳۰۰,۰۰۰,۰۰۰ تومان</t>
+          <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>‏۱۶,۰۰۰,۰۰۰ تومان</t>
+          <t>رایگان</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>ودیعه: ۳۰۰,۰۰۰,۰۰۰ تومان</t>
+          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>اجاره: ۱۶,۰۰۰,۰۰۰ تومان</t>
+          <t>رهن کامل</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -12826,42 +12851,29 @@
       <c r="BE54" t="inlineStr"/>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>2026-10-31T11:52:47.452916</t>
+          <t>2026-11-04T18:08:58.487714</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr"/>
       <c r="BH54" t="inlineStr"/>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>✅مشاورین آلفا ✅
-        ✅آپارتمان۶۰متر  خوش نقشه تخلیه️✅
-        ✅دسترسی بی نظیر به مترو و BRT️✅
-    ✅ملک به شدت خوش نقشه و قابل چیدمان✅
-‼️زیر قیمت منطقه ‼️
-‼️بی نظیر در این منطقه‼️
-‼️سریعا تماس بگیرید‼️
-ـ
-دسترسی عالی به مراکز خرید و فضای سبز〽️
-دسترسی بی نظیر به اتوبان یادگار امام و نواب〽️
-⭕️فوری!!!⭕️
-✅عکس ها متعلق به واحد میباشد
-✅فول امکانات و اوکازیون 
-✅کابینت MDF TORK
-✅گازرومیزی
-✅هودلمسی
-✅پارکینگ موتور
-✅انباری 
-✅بالکن دلباز
-✅درب ضد سرقت
-✅تک واحدی 
-✅سرویس ایرانی 
-✅نورگیری فوق العاده
-✅کمد دیواری بزرگ
-✅سرمایش کولر آبی
-✅گرمایش بخاری 
-✅کف سرامیک
-✅تماس بگیرید
-مشاور تخصصی منطقه:راد</t>
+          <t>عکس ها واقعی و متعلق به واحد میباشد
+کف سرامیک 
+نور گیر ۲ طرفه 
+دارای تراس 
+آیفون تصویری
+فول بازسازی شده 
+کابینت ام دی اف  
+کف سرامیک  
+تمیز 
+مناسب خوانواده 
+طبقه ۴  
+تک واحدی 
+بدون آسانسور 
+بدون پارکینگ 
+آگهی شخصی میباشد 
+واحد تخلیه</t>
         </is>
       </c>
     </row>
@@ -12878,54 +12890,54 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>gaCTG_5X</t>
+          <t>gakbEsrC</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://divar.ir/v/gaCTG_5X</t>
+          <t>https://divar.ir/v/gakbEsrC</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>اجاره آپارتمان ۶۰ متری</t>
+          <t>لویزان ۶۸ متر دو خواب</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>شهرک ولیعصر شمالی</t>
+          <t>لویزان</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>شهرک ولیعصر شمالی</t>
+          <t>لویزان</t>
         </is>
       </c>
       <c r="I55" t="b">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>500000000</v>
+        <v>250000000</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>16000000</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O55" t="n">
-        <v>1395</v>
+        <v>1383</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>4 از 4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q55" t="b">
@@ -12935,10 +12947,10 @@
         <v>0</v>
       </c>
       <c r="S55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -12947,14 +12959,10 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>۱۲ مهر ۱۴۰۵، ۱۸:۰۸</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>۱۷ مهر ۱۴۰۵، ۱۲:۲۸</t>
-        </is>
-      </c>
+          <t>۸ آبان ۱۴۰۵، ۱۰:۵۷</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
@@ -12985,29 +12993,29 @@
       <c r="AQ55" t="inlineStr"/>
       <c r="AR55" t="inlineStr"/>
       <c r="AS55" t="n">
-        <v>500000000</v>
+        <v>250000000</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>16000000</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>‏۵۰۰,۰۰۰,۰۰۰ تومان</t>
+          <t>‏۲۵۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>رایگان</t>
+          <t>‏۱۶,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>ودیعه: ۵۰۰,۰۰۰,۰۰۰ تومان</t>
+          <t>ودیعه: ۲۵۰,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>رهن کامل</t>
+          <t>اجاره: ۱۶,۰۰۰,۰۰۰ تومان</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -13023,192 +13031,12 @@
       <c r="BE55" t="inlineStr"/>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>2026-11-04T18:08:58.487714</t>
+          <t>2026-11-30T10:57:29.752729</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr"/>
       <c r="BH55" t="inlineStr"/>
       <c r="BI55" t="inlineStr">
-        <is>
-          <t>عکس ها واقعی و متعلق به واحد میباشد
-کف سرامیک 
-نور گیر ۲ طرفه 
-دارای تراس 
-آیفون تصویری
-فول بازسازی شده 
-کابینت ام دی اف  
-کف سرامیک  
-تمیز 
-مناسب خوانواده 
-طبقه ۴  
-تک واحدی 
-بدون آسانسور 
-بدون پارکینگ 
-آگهی شخصی میباشد 
-واحد تخلیه</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NEEDS_LOCATION_VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>no usable coordinates (MISSING)</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>gakbEsrC</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://divar.ir/v/gakbEsrC</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>لویزان ۶۸ متر دو خواب</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>لویزان</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>لویزان</t>
-        </is>
-      </c>
-      <c r="I56" t="b">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>250000000</v>
-      </c>
-      <c r="K56" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="L56" t="b">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>68</v>
-      </c>
-      <c r="N56" t="n">
-        <v>2</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1383</v>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q56" t="b">
-        <v>0</v>
-      </c>
-      <c r="R56" t="b">
-        <v>0</v>
-      </c>
-      <c r="S56" t="b">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>13</v>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>personal</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>۸ آبان ۱۴۰۵، ۱۰:۵۷</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
-      <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr"/>
-      <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
-      <c r="AO56" t="inlineStr"/>
-      <c r="AP56" t="inlineStr"/>
-      <c r="AQ56" t="inlineStr"/>
-      <c r="AR56" t="inlineStr"/>
-      <c r="AS56" t="n">
-        <v>250000000</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>‏۲۵۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AV56" t="inlineStr">
-        <is>
-          <t>‏۱۶,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>ودیعه: ۲۵۰,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>اجاره: ۱۶,۰۰۰,۰۰۰ تومان</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr"/>
-      <c r="BA56" t="inlineStr"/>
-      <c r="BB56" t="inlineStr"/>
-      <c r="BC56" t="inlineStr"/>
-      <c r="BD56" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="BE56" t="inlineStr"/>
-      <c r="BF56" t="inlineStr">
-        <is>
-          <t>2026-11-30T10:57:29.752729</t>
-        </is>
-      </c>
-      <c r="BG56" t="inlineStr"/>
-      <c r="BH56" t="inlineStr"/>
-      <c r="BI56" t="inlineStr">
         <is>
           <t>واحد واقع در لویزان 
 ۶۸ متر دو‌ خواب 

--- a/needs_location_verification.xlsx
+++ b/needs_location_verification.xlsx
@@ -1439,7 +1439,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>شاهد قدیمی; مبارک‌آباد بهشتی قدیمی; سبلان قدیمی; دولت‌آباد قدیمی; وصفنارد; شهید آوینی قدیمی; ملک‌آباد قدیمی; ظهیرآباد قدیمی</t>
+          <t>دانشگاه تهران قدیمی; شاهد قدیمی; پاتریس لومومبا قدیمی; وصفنارد; وصفنارد; طوس قدیمی; منصوریه (پل سیمان) قدیمی</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>جوانمرد قصاب قدیمی; مبارک‌آباد بهشتی قدیمی; سبلان قدیمی; اراج قدیمی; پاتریس لومومبا قدیمی; سیزده آبان قدیمی; دولت‌آباد قدیمی; فیروزآبادی قدیمی; سرتخت قدیمی; شهید آوینی قدیمی; دیلمان قدیمی; قاسم‌آباد; شهادت قدیمی; طوس قدیمی; منصوریه (پل سیمان) قدیمی; ملک‌آباد قدیمی; ابن بابویه قدیمی; صفائیه (چشمه علی) قدیمی; شبیری قدیمی; صالح‌آباد شرقی قدیمی; ظهیرآباد قدیمی; حسن‌آباد باقرفر قدیمی</t>
+          <t>نواب قدیمی; حمزه‌آباد قدیمی; پیروزی قدیمی; دانشگاه تهران قدیمی; شاهد قدیمی; جوانمرد قصاب قدیمی; مبارک‌آباد بهشتی قدیمی; سبلان قدیمی; اراج قدیمی; پاتریس لومومبا قدیمی; سیزده آبان قدیمی; دولت‌آباد قدیمی; فیروزآبادی قدیمی; سرتخت قدیمی; شهید آوینی قدیمی; دیلمان قدیمی; قاسم‌آباد; شهادت قدیمی; طوس قدیمی; منصوریه (پل سیمان) قدیمی; ملک‌آباد قدیمی; ابن بابویه قدیمی; صفائیه (چشمه علی) قدیمی; شبیری قدیمی; صالح‌آباد شرقی قدیمی; ظهیرآباد قدیمی; حسن‌آباد باقرفر قدیمی</t>
         </is>
       </c>
       <c r="I37" t="b">
